--- a/backend/王侯將相最新版.xlsx
+++ b/backend/王侯將相最新版.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piaget\Desktop\歷史名將\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9515DF51-C0BE-4714-9E28-4B4E7A528194}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45F837A-64D9-45A7-975A-B34D2FB1857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23607111-B237-4551-BBD0-59FB953E8041}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="王侯將相" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="外部資料_1" localSheetId="0" hidden="1">王侯將相!$A$1:$G$428</definedName>
+    <definedName name="外部資料_1" localSheetId="0" hidden="1">王侯將相!$A$1:$G$444</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2996" uniqueCount="2109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="2182">
   <si>
     <t>帝王</t>
   </si>
@@ -6406,6 +6406,226 @@
   </si>
   <si>
     <t>襄樊死戰全魏祚，天人將軍鑄鐵壁。</t>
+  </si>
+  <si>
+    <t>悲歌死將</t>
+  </si>
+  <si>
+    <t>極限抗壓 / 戰略替罪羊</t>
+  </si>
+  <si>
+    <t>在國家後勤崩潰下被迫主動決戰。雖中白起之計遭圍，但斷糧四十六日軍心不潰，逼出秦國極限動員，最終親率精銳突圍戰死。雖敗軍覆國，然軍人風骨與基層統御力不容抹滅。</t>
+  </si>
+  <si>
+    <t>困獸猶能撼虎狼，四旬斷汲陣未亡。</t>
+  </si>
+  <si>
+    <t>潰軍之源</t>
+  </si>
+  <si>
+    <t>棄城遁逃 / 指揮崩塌</t>
+  </si>
+  <si>
+    <t>於南京保衛戰中展現災難級別的軍事統御。以破釜沉舟之名斷絕退路，卻在城破之際未作戰術交接率先逃亡，致使十餘萬守軍指揮鏈瞬間崩潰，為建軍史上極端不負責任之統帥敗筆。</t>
+  </si>
+  <si>
+    <t>破釜沉舟誆萬軍，孤舟獨遁棄金陵。</t>
+  </si>
+  <si>
+    <t>王耀武</t>
+  </si>
+  <si>
+    <t>鐵軍鑄造者</t>
+  </si>
+  <si>
+    <t>抗日鐵鎚 / 務實軍事家</t>
+  </si>
+  <si>
+    <t>第七十四軍核心締造者，幾乎打滿抗戰全場高烈度會戰。上高會戰展現頂級防守反擊戰術，純以軍事實務與火網配置構築絞肉機。濟南戰敗被俘，拒絕無意義之政治殉葬，為近現代極度清醒之戰鬥實幹家。</t>
+  </si>
+  <si>
+    <t>八年血戰鑄鐵軍，上高城外鬼神驚。</t>
+  </si>
+  <si>
+    <t>杜聿明</t>
+  </si>
+  <si>
+    <t>悲情救火隊長</t>
+  </si>
+  <si>
+    <t>裝甲先驅 / 愚忠誤國</t>
+  </si>
+  <si>
+    <t>國軍首支機械化部隊統帥，血戰崑崙關、四平街擊退林彪，具備頂級大兵團與裝甲指揮力。然政治性格極度懦弱，於野人山與淮海戰役中，兩度盲從最高統帥之災難微操，明知死局仍將數十萬精銳葬送，為「愚忠反噬實體」之極致悲劇。</t>
+  </si>
+  <si>
+    <t>崑崙關外揚兵威，中原雪滿將星頹。</t>
+  </si>
+  <si>
+    <t>陳誠</t>
+  </si>
+  <si>
+    <t>土木系 / 瞎指揮</t>
+  </si>
+  <si>
+    <t>土木系絕對核心，具備強大派系建軍力。然戰場微操與戰區宏觀指揮失能，東北剿總任內盲目裁撤偽滿軍隊，將數十萬即戰力推向敵營，釀成不可挽回之大兵團戰略災難。</t>
+  </si>
+  <si>
+    <t>擁兵百萬圖雄據，白山黑水誤全盤。</t>
+  </si>
+  <si>
+    <t>孤島磐石</t>
+  </si>
+  <si>
+    <t>土地改革 / 幣制重塑</t>
+  </si>
+  <si>
+    <t>退守台灣後展現頂級治國實效。以鐵腕推動新台幣發行阻絕惡性通膨；兵不血刃完成三七五減租與耕者有其田，徹底穩固底層社會結構，為台灣經濟奇蹟鑄造絕對之底層基石。</t>
+  </si>
+  <si>
+    <t>孤島風雷驚舊夢，減租放領定基根。</t>
+  </si>
+  <si>
+    <t>胡宗南</t>
+  </si>
+  <si>
+    <t>西北提款機 / 蘑菇戰術受害者</t>
+  </si>
+  <si>
+    <t>擁數十萬最精銳中央軍坐鎮西北，卻在陝北戰場遭彭德懷以絕對劣勢兵力「蘑菇戰術」徹底牽制並殲滅。奪取空城延安僅獲政治虛名，實體軍力卻遭全盤瓦解，為大兵團優勢作戰之絕對反面教材。</t>
+  </si>
+  <si>
+    <t>擁兵四十屯西北，蘑菇戰術化塵埃。</t>
+  </si>
+  <si>
+    <t>張學良</t>
+  </si>
+  <si>
+    <t>散財軍閥</t>
+  </si>
+  <si>
+    <t>丟失東北 / 實體歸零</t>
+  </si>
+  <si>
+    <t>繼承東亞頂級軍工體系與三十萬大軍。九一八事變下達不抵抗命令，將戰略重地與海量軍火拱手讓日，釀成抗戰極端劣勢；西安事變更致使自身軍隊實體遭徹底瓦解，為軍事資源轉化率絕對為零之統帥。</t>
+  </si>
+  <si>
+    <t>瀋陽兵工化劫灰，不發一槍棄重關。</t>
+  </si>
+  <si>
+    <t>傅作義</t>
+  </si>
+  <si>
+    <t>守城飛將</t>
+  </si>
+  <si>
+    <t>防禦大師 / 戰略遲疑</t>
+  </si>
+  <si>
+    <t>涿州孤城抗擊數萬大軍，百靈廟大捷重創日偽，為民國頂級防守反擊大腦。然平津戰役中因欲保全派系實力而戰略猶豫，致使核心主力第 35 軍覆滅，喪失大戰區博弈之最後籌碼。</t>
+  </si>
+  <si>
+    <t>涿州孤城揚威名，百靈廟前鎮胡塵。</t>
+  </si>
+  <si>
+    <t>實幹孤臣</t>
+  </si>
+  <si>
+    <t>保全古都 / 治水總管</t>
+  </si>
+  <si>
+    <t>於北平死局中摒棄愚忠，促成和平解放，實質保全千年古都之文明實體與百萬生靈。建國後任水利部長二十三年，踏遍大江大河推動實體基礎建設，以技術官僚之姿洗刷降將之名。</t>
+  </si>
+  <si>
+    <t>和平一局存燕京，半生戎馬半生水。</t>
+  </si>
+  <si>
+    <t>張作霖</t>
+  </si>
+  <si>
+    <t>東北王</t>
+  </si>
+  <si>
+    <t>軍工實體 / 地緣走鋼索</t>
+  </si>
+  <si>
+    <t>從綠林崛起，於日俄夾縫中締造擁有亞洲頂尖軍工體系與海空軍之奉系霸權。雖戰術思維陳舊敗於北伐，然大是大非前堅拒出賣國家核心主權，於皇姑屯殉身，為舊式軍閥實體建制之巔峰。</t>
+  </si>
+  <si>
+    <t>綠林拔劍起關東，喋血皇姑拒日鋒。</t>
+  </si>
+  <si>
+    <t>閻錫山</t>
+  </si>
+  <si>
+    <t>山西不倒翁</t>
+  </si>
+  <si>
+    <t>實體建軍 / 地緣平衡</t>
+  </si>
+  <si>
+    <t>統治山西三十八年，憑藉表裡山河據險而守。締造太原兵工廠實現軍備自給，於各方勢力中大玩平衡木；然部隊戰術僵化，缺乏外線機動與戰略破局能力，為極致之防禦自保型舊式統帥。</t>
+  </si>
+  <si>
+    <t>據險太原觀虎鬥，表裡山河鑄堅城。</t>
+  </si>
+  <si>
+    <t>模範督軍</t>
+  </si>
+  <si>
+    <t>閉環經濟 / 村本政治</t>
+  </si>
+  <si>
+    <t>於軍閥割據中推行實用主義治理。築窄軌鐵路以自保，建西北實業公司完善輕重工業體系；推行村本政治與六政三事，將山西打造成民國罕見之實體經濟閉環與模範省份。</t>
+  </si>
+  <si>
+    <t>窄軌綿延鎖晉地，實業六政惠三晉。</t>
+  </si>
+  <si>
+    <t>吳佩孚</t>
+  </si>
+  <si>
+    <t>悲情玉帥</t>
+  </si>
+  <si>
+    <t>戰術天才 / 實體虛無</t>
+  </si>
+  <si>
+    <t>直皖與第一次直奉戰爭中展現頂級野戰機動與大兵團指揮，為首位登上《時代》封面之中國軍閥。然極端排斥建立現代工業實體與穩固地緣基本盤；雖晚年拒作漢奸保全民族氣節，但在殘酷之實體絞肉機中，終因缺乏戰略縱深與後勤而全盤覆滅。</t>
+  </si>
+  <si>
+    <t>洛陽虎踞震北洋，空有將才無實疆。</t>
+  </si>
+  <si>
+    <t>陳炯明</t>
+  </si>
+  <si>
+    <t>聯省先驅</t>
+  </si>
+  <si>
+    <t>實體建制 / 廣東大治</t>
+  </si>
+  <si>
+    <t>拒絕武力盲目北伐，推動「聯省自治」。於廣東大舉興辦教育、修築公路、禁絕煙賭並確立現代司法框架，為近現代極具前瞻性之地方實體現代化締造者，惜藍圖遭大一統戰火摧毀。</t>
+  </si>
+  <si>
+    <t>聯省宏圖興百業，羊城舊夢碎干戈。</t>
+  </si>
+  <si>
+    <t>破產軍閥</t>
+  </si>
+  <si>
+    <t>理想碎裂 / 戰略失能</t>
+  </si>
+  <si>
+    <t>早年驅逐桂系統一嶺南。然軍隊組織與戰術思維停滯，於東征戰役中面對具備現代政戰體系之黃埔軍毫無招架之力，喪失根據地，武裝實體遭徹底瓦解，無法為政治理想提供暴力背書。</t>
+  </si>
+  <si>
+    <t>粵海雄兵終化土，空懷壯志恨黃埔。</t>
+  </si>
+  <si>
+    <t>趙括</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6499,7 +6719,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6522,6 +6742,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -6689,9 +6915,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}" name="王侯將相" displayName="王侯將相" ref="A1:G428" tableType="queryTable" totalsRowShown="0" dataDxfId="7">
-  <autoFilter ref="A1:G428" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G427">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}" name="王侯將相" displayName="王侯將相" ref="A1:G444" tableType="queryTable" totalsRowShown="0" dataDxfId="7">
+  <autoFilter ref="A1:G444" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G428">
     <sortCondition ref="A2:A332" customList="帝王,將領,名臣"/>
     <sortCondition ref="C2:C332" customList="S+,S,S-,A+,A,A-,B+,B,B-,C+,C,C-,D"/>
   </sortState>
@@ -7005,7 +7231,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0685D331-C227-4B1A-8854-ADE1AFC8F58E}">
-  <dimension ref="A1:G428"/>
+  <dimension ref="A1:G444"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -12721,27 +12947,27 @@
         <v>2098</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A249" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B249" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C249" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D249" s="1" t="s">
-        <v>946</v>
-      </c>
-      <c r="E249" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="F249" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="G249" s="1" t="s">
-        <v>949</v>
+    <row r="249" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A249" s="8" t="s">
+        <v>472</v>
+      </c>
+      <c r="B249" s="8" t="s">
+        <v>2104</v>
+      </c>
+      <c r="C249" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="D249" s="8" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E249" s="8" t="s">
+        <v>2106</v>
+      </c>
+      <c r="F249" s="8" t="s">
+        <v>2107</v>
+      </c>
+      <c r="G249" s="8" t="s">
+        <v>2108</v>
       </c>
     </row>
     <row r="250" spans="1:7" x14ac:dyDescent="0.3">
@@ -12749,22 +12975,22 @@
         <v>472</v>
       </c>
       <c r="B250" s="1" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
       <c r="C250" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D250" s="1" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
       <c r="E250" s="1" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
       <c r="F250" s="1" t="s">
-        <v>953</v>
+        <v>948</v>
       </c>
       <c r="G250" s="1" t="s">
-        <v>954</v>
+        <v>949</v>
       </c>
     </row>
     <row r="251" spans="1:7" x14ac:dyDescent="0.3">
@@ -12772,22 +12998,22 @@
         <v>472</v>
       </c>
       <c r="B251" s="1" t="s">
-        <v>955</v>
+        <v>950</v>
       </c>
       <c r="C251" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D251" s="1" t="s">
-        <v>956</v>
+        <v>951</v>
       </c>
       <c r="E251" s="1" t="s">
-        <v>957</v>
+        <v>952</v>
       </c>
       <c r="F251" s="1" t="s">
-        <v>958</v>
+        <v>953</v>
       </c>
       <c r="G251" s="1" t="s">
-        <v>959</v>
+        <v>954</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -12795,22 +13021,22 @@
         <v>472</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>961</v>
+        <v>956</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>962</v>
+        <v>957</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>963</v>
+        <v>958</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>964</v>
+        <v>959</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -12818,22 +13044,22 @@
         <v>472</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>965</v>
+        <v>960</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>966</v>
+        <v>961</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>967</v>
+        <v>962</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>968</v>
+        <v>963</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>969</v>
+        <v>964</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -12841,22 +13067,22 @@
         <v>472</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>970</v>
+        <v>965</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>971</v>
+        <v>966</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>972</v>
+        <v>967</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>973</v>
+        <v>968</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>974</v>
+        <v>969</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -12864,22 +13090,22 @@
         <v>472</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>975</v>
+        <v>970</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>976</v>
+        <v>971</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>977</v>
+        <v>972</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>978</v>
+        <v>973</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>979</v>
+        <v>974</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -12887,22 +13113,22 @@
         <v>472</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>980</v>
+        <v>975</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>841</v>
+        <v>976</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -12910,22 +13136,22 @@
         <v>472</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>985</v>
+        <v>841</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>986</v>
+        <v>981</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>987</v>
+        <v>982</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>988</v>
+        <v>983</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -12933,22 +13159,22 @@
         <v>472</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>989</v>
+        <v>984</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>990</v>
+        <v>985</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>991</v>
+        <v>986</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>992</v>
+        <v>987</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>993</v>
+        <v>988</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -12956,22 +13182,22 @@
         <v>472</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>994</v>
+        <v>989</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>995</v>
+        <v>990</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>996</v>
+        <v>991</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>997</v>
+        <v>992</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>998</v>
+        <v>993</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -12979,22 +13205,22 @@
         <v>472</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>999</v>
+        <v>994</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>1000</v>
+        <v>995</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>1001</v>
+        <v>996</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>1002</v>
+        <v>997</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>1003</v>
+        <v>998</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -13002,22 +13228,22 @@
         <v>472</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>1004</v>
+        <v>999</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1005</v>
+        <v>1000</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>1006</v>
+        <v>1001</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1007</v>
+        <v>1002</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1008</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -13025,22 +13251,22 @@
         <v>472</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>242</v>
+        <v>1004</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>245</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -13048,22 +13274,22 @@
         <v>472</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>1012</v>
+        <v>242</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>1016</v>
+        <v>245</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -13071,22 +13297,22 @@
         <v>472</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>1017</v>
+        <v>1012</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1018</v>
+        <v>1013</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1019</v>
+        <v>1014</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1021</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -13094,22 +13320,22 @@
         <v>472</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>1022</v>
+        <v>1017</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1024</v>
+        <v>1019</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1025</v>
+        <v>1020</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1026</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -13117,22 +13343,22 @@
         <v>472</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>1027</v>
+        <v>1022</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1028</v>
+        <v>1023</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>1029</v>
+        <v>1024</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1030</v>
+        <v>1025</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1031</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -13140,22 +13366,22 @@
         <v>472</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1032</v>
+        <v>1027</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1033</v>
+        <v>1028</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1034</v>
+        <v>1029</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1035</v>
+        <v>1030</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1036</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -13163,22 +13389,22 @@
         <v>472</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1037</v>
+        <v>1032</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1038</v>
+        <v>1033</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1039</v>
+        <v>1034</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1040</v>
+        <v>1035</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1041</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -13186,22 +13412,22 @@
         <v>472</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1042</v>
+        <v>1037</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1043</v>
+        <v>1038</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>1044</v>
+        <v>1039</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1045</v>
+        <v>1040</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1046</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -13209,22 +13435,22 @@
         <v>472</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1047</v>
+        <v>1042</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1048</v>
+        <v>1043</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1049</v>
+        <v>1044</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1050</v>
+        <v>1045</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1051</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -13232,45 +13458,45 @@
         <v>472</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1052</v>
+        <v>1047</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D271" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E271" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F271" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G271" s="1" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A272" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B272" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D272" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="E271" s="1" t="s">
+      <c r="E272" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="F271" s="1" t="s">
+      <c r="F272" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="G271" s="1" t="s">
+      <c r="G272" s="1" t="s">
         <v>1056</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A272" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>1616</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D272" s="2" t="s">
-        <v>1617</v>
-      </c>
-      <c r="E272" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F272" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="G272" s="2" t="s">
-        <v>1674</v>
       </c>
     </row>
     <row r="273" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13278,114 +13504,114 @@
         <v>472</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>1630</v>
+        <v>1616</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>1631</v>
+        <v>1617</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>1632</v>
+        <v>1618</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>1633</v>
+        <v>1619</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>1634</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A274" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>1649</v>
+        <v>1630</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>1650</v>
+        <v>1631</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>1651</v>
+        <v>1632</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>1652</v>
+        <v>1633</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>1653</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>1656</v>
+        <v>1651</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>1658</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A276" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>1967</v>
+        <v>1654</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>1968</v>
+        <v>1655</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>1969</v>
+        <v>1656</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1970</v>
+        <v>1657</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A277" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>1977</v>
+        <v>1967</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>1978</v>
+        <v>1968</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>1979</v>
+        <v>1969</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1980</v>
+        <v>1970</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>1981</v>
+        <v>1971</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13393,22 +13619,22 @@
         <v>472</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>2089</v>
+        <v>1977</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>2090</v>
+        <v>1978</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>2091</v>
+        <v>1979</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>2092</v>
+        <v>1980</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>2093</v>
+        <v>1981</v>
       </c>
     </row>
     <row r="279" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13416,45 +13642,45 @@
         <v>472</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>2099</v>
+        <v>2089</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D279" s="2" t="s">
+        <v>2090</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>2091</v>
+      </c>
+      <c r="F279" s="2" t="s">
+        <v>2092</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A280" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B280" s="2" t="s">
+        <v>2099</v>
+      </c>
+      <c r="C280" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D280" s="2" t="s">
         <v>2100</v>
       </c>
-      <c r="E279" s="2" t="s">
+      <c r="E280" s="2" t="s">
         <v>2101</v>
       </c>
-      <c r="F279" s="2" t="s">
+      <c r="F280" s="2" t="s">
         <v>2102</v>
       </c>
-      <c r="G279" s="2" t="s">
+      <c r="G280" s="2" t="s">
         <v>2103</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A280" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B280" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C280" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E280" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F280" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G280" s="1" t="s">
-        <v>1061</v>
       </c>
     </row>
     <row r="281" spans="1:7" x14ac:dyDescent="0.3">
@@ -13462,22 +13688,22 @@
         <v>472</v>
       </c>
       <c r="B281" s="1" t="s">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="C281" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D281" s="1" t="s">
-        <v>1063</v>
+        <v>1058</v>
       </c>
       <c r="E281" s="1" t="s">
-        <v>1064</v>
+        <v>1059</v>
       </c>
       <c r="F281" s="1" t="s">
-        <v>1065</v>
+        <v>1060</v>
       </c>
       <c r="G281" s="1" t="s">
-        <v>1066</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="282" spans="1:7" x14ac:dyDescent="0.3">
@@ -13485,22 +13711,22 @@
         <v>472</v>
       </c>
       <c r="B282" s="1" t="s">
-        <v>1067</v>
+        <v>1062</v>
       </c>
       <c r="C282" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D282" s="1" t="s">
-        <v>1068</v>
+        <v>1063</v>
       </c>
       <c r="E282" s="1" t="s">
-        <v>1069</v>
+        <v>1064</v>
       </c>
       <c r="F282" s="1" t="s">
-        <v>1070</v>
+        <v>1065</v>
       </c>
       <c r="G282" s="1" t="s">
-        <v>1071</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="283" spans="1:7" x14ac:dyDescent="0.3">
@@ -13508,22 +13734,22 @@
         <v>472</v>
       </c>
       <c r="B283" s="1" t="s">
-        <v>1072</v>
+        <v>1067</v>
       </c>
       <c r="C283" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>1073</v>
+        <v>1068</v>
       </c>
       <c r="E283" s="1" t="s">
-        <v>1074</v>
+        <v>1069</v>
       </c>
       <c r="F283" s="1" t="s">
-        <v>1075</v>
+        <v>1070</v>
       </c>
       <c r="G283" s="1" t="s">
-        <v>1076</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="284" spans="1:7" x14ac:dyDescent="0.3">
@@ -13531,22 +13757,22 @@
         <v>472</v>
       </c>
       <c r="B284" s="1" t="s">
-        <v>1077</v>
+        <v>1072</v>
       </c>
       <c r="C284" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>1078</v>
+        <v>1073</v>
       </c>
       <c r="E284" s="1" t="s">
-        <v>1079</v>
+        <v>1074</v>
       </c>
       <c r="F284" s="1" t="s">
-        <v>1080</v>
+        <v>1075</v>
       </c>
       <c r="G284" s="1" t="s">
-        <v>1081</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="285" spans="1:7" x14ac:dyDescent="0.3">
@@ -13554,22 +13780,22 @@
         <v>472</v>
       </c>
       <c r="B285" s="1" t="s">
-        <v>1082</v>
+        <v>1077</v>
       </c>
       <c r="C285" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>1083</v>
+        <v>1078</v>
       </c>
       <c r="E285" s="1" t="s">
-        <v>1084</v>
+        <v>1079</v>
       </c>
       <c r="F285" s="1" t="s">
-        <v>1085</v>
+        <v>1080</v>
       </c>
       <c r="G285" s="1" t="s">
-        <v>1086</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -13577,22 +13803,22 @@
         <v>472</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1087</v>
+        <v>1082</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1088</v>
+        <v>1083</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>1089</v>
+        <v>1084</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1090</v>
+        <v>1085</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1091</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -13600,22 +13826,22 @@
         <v>472</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1092</v>
+        <v>1087</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1093</v>
+        <v>1088</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>1094</v>
+        <v>1089</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1095</v>
+        <v>1090</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1096</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -13623,22 +13849,22 @@
         <v>472</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1097</v>
+        <v>1092</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1098</v>
+        <v>1093</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>1099</v>
+        <v>1094</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1100</v>
+        <v>1095</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1101</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -13646,45 +13872,45 @@
         <v>472</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1102</v>
+        <v>1097</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D289" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E289" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F289" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G289" s="1" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="290" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A290" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B290" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C290" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D290" s="1" t="s">
         <v>1103</v>
       </c>
-      <c r="E289" s="1" t="s">
+      <c r="E290" s="1" t="s">
         <v>1104</v>
       </c>
-      <c r="F289" s="1" t="s">
+      <c r="F290" s="1" t="s">
         <v>1105</v>
       </c>
-      <c r="G289" s="1" t="s">
+      <c r="G290" s="1" t="s">
         <v>1106</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A290" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B290" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D290" s="2" t="s">
-        <v>1612</v>
-      </c>
-      <c r="E290" s="2" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F290" s="2" t="s">
-        <v>1614</v>
-      </c>
-      <c r="G290" s="2" t="s">
-        <v>1615</v>
       </c>
     </row>
     <row r="291" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13692,22 +13918,22 @@
         <v>472</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>1675</v>
+        <v>1611</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>1645</v>
+        <v>1612</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>1646</v>
+        <v>1613</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>1647</v>
+        <v>1614</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>1648</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="292" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13715,68 +13941,68 @@
         <v>472</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>1982</v>
+        <v>1675</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>1983</v>
+        <v>1645</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>1984</v>
+        <v>1646</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>1985</v>
+        <v>1647</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A293" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>1987</v>
+        <v>1982</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D293" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="F293" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>1986</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A294" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B294" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="C294" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D294" s="2" t="s">
         <v>1988</v>
       </c>
-      <c r="E293" s="2" t="s">
+      <c r="E294" s="2" t="s">
         <v>1989</v>
       </c>
-      <c r="F293" s="2" t="s">
+      <c r="F294" s="2" t="s">
         <v>1990</v>
       </c>
-      <c r="G293" s="2" t="s">
+      <c r="G294" s="2" t="s">
         <v>1991</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A294" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B294" s="1" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C294" s="1" t="s">
-        <v>343</v>
-      </c>
-      <c r="D294" s="1" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E294" s="1" t="s">
-        <v>1109</v>
-      </c>
-      <c r="F294" s="1" t="s">
-        <v>1110</v>
-      </c>
-      <c r="G294" s="1" t="s">
-        <v>1111</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -13784,22 +14010,22 @@
         <v>472</v>
       </c>
       <c r="B295" s="1" t="s">
-        <v>1112</v>
+        <v>1107</v>
       </c>
       <c r="C295" s="1" t="s">
-        <v>364</v>
+        <v>343</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>1113</v>
+        <v>1108</v>
       </c>
       <c r="E295" s="1" t="s">
-        <v>1114</v>
+        <v>1109</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>1115</v>
+        <v>1110</v>
       </c>
       <c r="G295" s="1" t="s">
-        <v>1116</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="296" spans="1:7" x14ac:dyDescent="0.3">
@@ -13807,22 +14033,22 @@
         <v>472</v>
       </c>
       <c r="B296" s="1" t="s">
-        <v>1117</v>
+        <v>1112</v>
       </c>
       <c r="C296" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D296" s="1" t="s">
-        <v>1118</v>
+        <v>1113</v>
       </c>
       <c r="E296" s="1" t="s">
-        <v>1119</v>
+        <v>1114</v>
       </c>
       <c r="F296" s="1" t="s">
-        <v>1120</v>
+        <v>1115</v>
       </c>
       <c r="G296" s="1" t="s">
-        <v>1121</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.3">
@@ -13830,22 +14056,22 @@
         <v>472</v>
       </c>
       <c r="B297" s="1" t="s">
-        <v>1122</v>
+        <v>1117</v>
       </c>
       <c r="C297" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D297" s="1" t="s">
-        <v>1123</v>
+        <v>1118</v>
       </c>
       <c r="E297" s="1" t="s">
-        <v>1124</v>
+        <v>1119</v>
       </c>
       <c r="F297" s="1" t="s">
-        <v>1125</v>
+        <v>1120</v>
       </c>
       <c r="G297" s="1" t="s">
-        <v>1126</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.3">
@@ -13853,45 +14079,45 @@
         <v>472</v>
       </c>
       <c r="B298" s="1" t="s">
-        <v>1127</v>
+        <v>1122</v>
       </c>
       <c r="C298" s="1" t="s">
         <v>364</v>
       </c>
       <c r="D298" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="E298" s="1" t="s">
+        <v>1124</v>
+      </c>
+      <c r="F298" s="1" t="s">
+        <v>1125</v>
+      </c>
+      <c r="G298" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A299" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B299" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C299" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="D299" s="1" t="s">
         <v>1128</v>
       </c>
-      <c r="E298" s="1" t="s">
+      <c r="E299" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="F298" s="1" t="s">
+      <c r="F299" s="1" t="s">
         <v>1130</v>
       </c>
-      <c r="G298" s="1" t="s">
+      <c r="G299" s="1" t="s">
         <v>1131</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A299" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D299" s="2" t="s">
-        <v>1636</v>
-      </c>
-      <c r="E299" s="2" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F299" s="2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="G299" s="2" t="s">
-        <v>1639</v>
       </c>
     </row>
     <row r="300" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13899,45 +14125,45 @@
         <v>472</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>2079</v>
+        <v>1635</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>364</v>
       </c>
       <c r="D300" s="2" t="s">
+        <v>1636</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="F300" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="G300" s="2" t="s">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A301" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B301" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C301" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D301" s="2" t="s">
         <v>2080</v>
       </c>
-      <c r="E300" s="2" t="s">
+      <c r="E301" s="2" t="s">
         <v>2081</v>
       </c>
-      <c r="F300" s="2" t="s">
+      <c r="F301" s="2" t="s">
         <v>2082</v>
       </c>
-      <c r="G300" s="2" t="s">
+      <c r="G301" s="2" t="s">
         <v>2083</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A301" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B301" s="1" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C301" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D301" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E301" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F301" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G301" s="1" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.3">
@@ -13945,22 +14171,22 @@
         <v>472</v>
       </c>
       <c r="B302" s="1" t="s">
-        <v>1137</v>
+        <v>1132</v>
       </c>
       <c r="C302" s="1" t="s">
         <v>405</v>
       </c>
       <c r="D302" s="1" t="s">
-        <v>1138</v>
+        <v>1133</v>
       </c>
       <c r="E302" s="1" t="s">
-        <v>1139</v>
+        <v>1134</v>
       </c>
       <c r="F302" s="1" t="s">
-        <v>1140</v>
+        <v>1135</v>
       </c>
       <c r="G302" s="1" t="s">
-        <v>1141</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -13968,22 +14194,22 @@
         <v>472</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1142</v>
+        <v>1137</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>441</v>
+        <v>405</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>1143</v>
+        <v>1138</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1144</v>
+        <v>1139</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1145</v>
+        <v>1140</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>1146</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -13991,45 +14217,45 @@
         <v>472</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1147</v>
+        <v>1142</v>
       </c>
       <c r="C304" s="1" t="s">
         <v>441</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>1148</v>
+        <v>1143</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1149</v>
+        <v>1144</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1150</v>
+        <v>1145</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>1151</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A305" s="1" t="s">
-        <v>1152</v>
+        <v>472</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>2</v>
+        <v>441</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.3">
@@ -14037,22 +14263,22 @@
         <v>1152</v>
       </c>
       <c r="B306" s="1" t="s">
-        <v>1158</v>
+        <v>1153</v>
       </c>
       <c r="C306" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D306" s="1" t="s">
-        <v>1159</v>
+        <v>1154</v>
       </c>
       <c r="E306" s="1" t="s">
-        <v>1160</v>
+        <v>1155</v>
       </c>
       <c r="F306" s="1" t="s">
-        <v>1161</v>
+        <v>1156</v>
       </c>
       <c r="G306" s="1" t="s">
-        <v>1162</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="307" spans="1:7" x14ac:dyDescent="0.3">
@@ -14060,22 +14286,22 @@
         <v>1152</v>
       </c>
       <c r="B307" s="1" t="s">
-        <v>1163</v>
+        <v>1158</v>
       </c>
       <c r="C307" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D307" s="1" t="s">
-        <v>1164</v>
+        <v>1159</v>
       </c>
       <c r="E307" s="1" t="s">
-        <v>1165</v>
+        <v>1160</v>
       </c>
       <c r="F307" s="1" t="s">
-        <v>1166</v>
+        <v>1161</v>
       </c>
       <c r="G307" s="1" t="s">
-        <v>1167</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.3">
@@ -14083,22 +14309,22 @@
         <v>1152</v>
       </c>
       <c r="B308" s="1" t="s">
-        <v>1168</v>
+        <v>1163</v>
       </c>
       <c r="C308" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D308" s="1" t="s">
-        <v>1169</v>
+        <v>1164</v>
       </c>
       <c r="E308" s="1" t="s">
-        <v>1170</v>
+        <v>1165</v>
       </c>
       <c r="F308" s="1" t="s">
-        <v>1171</v>
+        <v>1166</v>
       </c>
       <c r="G308" s="1" t="s">
-        <v>1172</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.3">
@@ -14106,22 +14332,22 @@
         <v>1152</v>
       </c>
       <c r="B309" s="1" t="s">
-        <v>1173</v>
+        <v>1168</v>
       </c>
       <c r="C309" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D309" s="1" t="s">
-        <v>1174</v>
+        <v>1169</v>
       </c>
       <c r="E309" s="1" t="s">
-        <v>1175</v>
+        <v>1170</v>
       </c>
       <c r="F309" s="1" t="s">
-        <v>1176</v>
+        <v>1171</v>
       </c>
       <c r="G309" s="1" t="s">
-        <v>1177</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
@@ -14129,22 +14355,22 @@
         <v>1152</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1178</v>
+        <v>1173</v>
       </c>
       <c r="C310" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>1180</v>
+        <v>1175</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1181</v>
+        <v>1176</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
@@ -14152,22 +14378,22 @@
         <v>1152</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1183</v>
+        <v>1178</v>
       </c>
       <c r="C311" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>566</v>
+        <v>1179</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1185</v>
+        <v>1181</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1186</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.3">
@@ -14175,22 +14401,22 @@
         <v>1152</v>
       </c>
       <c r="B312" s="1" t="s">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C312" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D312" s="1" t="s">
-        <v>1188</v>
+        <v>566</v>
       </c>
       <c r="E312" s="1" t="s">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="F312" s="1" t="s">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="G312" s="1" t="s">
-        <v>1191</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
@@ -14198,22 +14424,22 @@
         <v>1152</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1192</v>
+        <v>1187</v>
       </c>
       <c r="C313" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>1193</v>
+        <v>1188</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1194</v>
+        <v>1189</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
@@ -14221,22 +14447,22 @@
         <v>1152</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="C314" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1199</v>
+        <v>1194</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.3">
@@ -14244,22 +14470,22 @@
         <v>1152</v>
       </c>
       <c r="B315" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="C315" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D315" s="1" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="E315" s="1" t="s">
-        <v>816</v>
+        <v>1199</v>
       </c>
       <c r="F315" s="1" t="s">
-        <v>1204</v>
+        <v>1200</v>
       </c>
       <c r="G315" s="1" t="s">
-        <v>1205</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.3">
@@ -14267,22 +14493,22 @@
         <v>1152</v>
       </c>
       <c r="B316" s="1" t="s">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="C316" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D316" s="1" t="s">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="E316" s="1" t="s">
-        <v>1208</v>
+        <v>816</v>
       </c>
       <c r="F316" s="1" t="s">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="G316" s="1" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
@@ -14290,22 +14516,22 @@
         <v>1152</v>
       </c>
       <c r="B317" s="1" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="C317" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D317" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="E317" s="1" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="F317" s="1" t="s">
-        <v>1214</v>
+        <v>1209</v>
       </c>
       <c r="G317" s="1" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
@@ -14313,22 +14539,22 @@
         <v>1152</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="C318" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>831</v>
+        <v>1212</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1218</v>
+        <v>1214</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1219</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
@@ -14336,22 +14562,22 @@
         <v>1152</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1220</v>
+        <v>1216</v>
       </c>
       <c r="C319" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>1221</v>
+        <v>831</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1224</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
@@ -14359,22 +14585,22 @@
         <v>1152</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1229</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
@@ -14382,22 +14608,22 @@
         <v>1152</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="C321" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
@@ -14405,22 +14631,22 @@
         <v>1152</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="C322" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1238</v>
+        <v>1233</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
@@ -14428,22 +14654,22 @@
         <v>1152</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="C323" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>1242</v>
+        <v>1237</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
@@ -14451,22 +14677,22 @@
         <v>1152</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="C324" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>1194</v>
+        <v>1242</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1247</v>
+        <v>1243</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
@@ -14474,22 +14700,22 @@
         <v>1152</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="C325" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>1250</v>
+        <v>1246</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>1251</v>
+        <v>1194</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
@@ -14497,22 +14723,22 @@
         <v>1152</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="C326" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>1255</v>
+        <v>1250</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
@@ -14520,22 +14746,22 @@
         <v>1152</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="C327" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>1260</v>
+        <v>1255</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>694</v>
+        <v>1256</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1261</v>
+        <v>1257</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>696</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
@@ -14543,22 +14769,22 @@
         <v>1152</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1262</v>
+        <v>1259</v>
       </c>
       <c r="C328" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>1263</v>
+        <v>1260</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>1264</v>
+        <v>694</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1265</v>
+        <v>1261</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>1266</v>
+        <v>696</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
@@ -14566,22 +14792,22 @@
         <v>1152</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="C329" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>1268</v>
+        <v>1263</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
@@ -14589,22 +14815,22 @@
         <v>1152</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1272</v>
+        <v>1267</v>
       </c>
       <c r="C330" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D330" s="1" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="E330" s="1" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="F330" s="1" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="G330" s="1" t="s">
-        <v>1276</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.3">
@@ -14612,22 +14838,22 @@
         <v>1152</v>
       </c>
       <c r="B331" s="1" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="C331" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D331" s="1" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="E331" s="1" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="F331" s="1" t="s">
-        <v>1280</v>
+        <v>1275</v>
       </c>
       <c r="G331" s="1" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="332" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14635,22 +14861,22 @@
         <v>1152</v>
       </c>
       <c r="B332" s="1" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="C332" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D332" s="1" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="E332" s="1" t="s">
-        <v>1284</v>
+        <v>1279</v>
       </c>
       <c r="F332" s="1" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="G332" s="1" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="333" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14658,22 +14884,22 @@
         <v>1152</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="C333" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>664</v>
+        <v>1283</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>1289</v>
+        <v>1285</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>1290</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="334" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14681,22 +14907,22 @@
         <v>1152</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>1291</v>
+        <v>1287</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>1292</v>
+        <v>664</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>1295</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="335" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14704,22 +14930,22 @@
         <v>1152</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>1299</v>
+        <v>1294</v>
       </c>
       <c r="G335" s="3" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="336" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14727,22 +14953,22 @@
         <v>1152</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="G336" s="3" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="337" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14750,22 +14976,22 @@
         <v>1152</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="338" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14773,22 +14999,22 @@
         <v>1152</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>1311</v>
+        <v>1306</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>1314</v>
+        <v>1309</v>
       </c>
       <c r="G338" s="3" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="339" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14796,22 +15022,22 @@
         <v>1152</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1318</v>
+        <v>1313</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="G339" s="3" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
     </row>
     <row r="340" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14819,91 +15045,91 @@
         <v>1152</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D340" s="3" t="s">
+        <v>1317</v>
+      </c>
+      <c r="E340" s="3" t="s">
+        <v>1318</v>
+      </c>
+      <c r="F340" s="3" t="s">
+        <v>1319</v>
+      </c>
+      <c r="G340" s="3" t="s">
+        <v>1320</v>
+      </c>
+    </row>
+    <row r="341" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A341" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B341" s="3" t="s">
+        <v>1321</v>
+      </c>
+      <c r="C341" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D341" s="3" t="s">
         <v>1322</v>
       </c>
-      <c r="E340" s="3" t="s">
+      <c r="E341" s="3" t="s">
         <v>1323</v>
       </c>
-      <c r="F340" s="3" t="s">
+      <c r="F341" s="3" t="s">
         <v>1324</v>
       </c>
-      <c r="G340" s="3" t="s">
+      <c r="G341" s="3" t="s">
         <v>1325</v>
       </c>
     </row>
-    <row r="341" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A341" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B341" s="4" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C341" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D341" s="4" t="s">
-        <v>2055</v>
-      </c>
-      <c r="E341" s="4" t="s">
-        <v>2056</v>
-      </c>
-      <c r="F341" s="4" t="s">
-        <v>2057</v>
-      </c>
-      <c r="G341" s="4" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A342" s="4" t="s">
         <v>1152</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>2074</v>
+        <v>2054</v>
       </c>
       <c r="C342" s="4" t="s">
         <v>33</v>
       </c>
       <c r="D342" s="4" t="s">
+        <v>2055</v>
+      </c>
+      <c r="E342" s="4" t="s">
+        <v>2056</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>2057</v>
+      </c>
+      <c r="G342" s="4" t="s">
+        <v>2058</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A343" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>2074</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D343" s="4" t="s">
         <v>2075</v>
       </c>
-      <c r="E342" s="4" t="s">
+      <c r="E343" s="4" t="s">
         <v>2076</v>
       </c>
-      <c r="F342" s="4" t="s">
+      <c r="F343" s="4" t="s">
         <v>2077</v>
       </c>
-      <c r="G342" s="4" t="s">
+      <c r="G343" s="4" t="s">
         <v>2078</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A343" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B343" s="3" t="s">
-        <v>1326</v>
-      </c>
-      <c r="C343" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D343" s="3" t="s">
-        <v>1327</v>
-      </c>
-      <c r="E343" s="3" t="s">
-        <v>1328</v>
-      </c>
-      <c r="F343" s="3" t="s">
-        <v>1329</v>
-      </c>
-      <c r="G343" s="3" t="s">
-        <v>1330</v>
       </c>
     </row>
     <row r="344" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14911,22 +15137,22 @@
         <v>1152</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="C344" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="F344" s="3" t="s">
-        <v>1334</v>
+        <v>1329</v>
       </c>
       <c r="G344" s="3" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="345" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14934,22 +15160,22 @@
         <v>1152</v>
       </c>
       <c r="B345" s="3" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="C345" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D345" s="3" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="E345" s="3" t="s">
-        <v>1338</v>
+        <v>1333</v>
       </c>
       <c r="F345" s="3" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="G345" s="3" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="346" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14957,22 +15183,22 @@
         <v>1152</v>
       </c>
       <c r="B346" s="6" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="C346" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D346" s="6" t="s">
-        <v>1342</v>
+        <v>1337</v>
       </c>
       <c r="E346" s="6" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="F346" s="6" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="G346" s="6" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
     </row>
     <row r="347" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -14980,22 +15206,22 @@
         <v>1152</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>1346</v>
+        <v>1341</v>
       </c>
       <c r="C347" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="G347" s="3" t="s">
-        <v>1350</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="348" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15003,22 +15229,22 @@
         <v>1152</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="C348" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1246</v>
+        <v>1347</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>1353</v>
+        <v>1349</v>
       </c>
       <c r="G348" s="3" t="s">
-        <v>1354</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="349" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15026,22 +15252,22 @@
         <v>1152</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="C349" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1833</v>
+        <v>1246</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1834</v>
+        <v>1352</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>1835</v>
+        <v>1353</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>1836</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="350" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15049,22 +15275,22 @@
         <v>1152</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>1357</v>
+        <v>1356</v>
       </c>
       <c r="C350" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1358</v>
+        <v>1833</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1359</v>
+        <v>1834</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>1360</v>
+        <v>1835</v>
       </c>
       <c r="G350" s="3" t="s">
-        <v>1361</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="351" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15072,22 +15298,22 @@
         <v>1152</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>1362</v>
+        <v>1357</v>
       </c>
       <c r="C351" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="G351" s="3" t="s">
-        <v>1366</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="352" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15095,22 +15321,22 @@
         <v>1152</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="C352" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>1370</v>
+        <v>1365</v>
       </c>
       <c r="G352" s="3" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="353" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15118,22 +15344,22 @@
         <v>1152</v>
       </c>
       <c r="B353" s="3" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="C353" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D353" s="3" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="E353" s="3" t="s">
-        <v>62</v>
+        <v>1369</v>
       </c>
       <c r="F353" s="3" t="s">
-        <v>1374</v>
+        <v>1370</v>
       </c>
       <c r="G353" s="3" t="s">
-        <v>1375</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="354" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15141,22 +15367,22 @@
         <v>1152</v>
       </c>
       <c r="B354" s="3" t="s">
-        <v>1376</v>
+        <v>1372</v>
       </c>
       <c r="C354" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D354" s="3" t="s">
-        <v>1377</v>
+        <v>1373</v>
       </c>
       <c r="E354" s="3" t="s">
-        <v>263</v>
+        <v>62</v>
       </c>
       <c r="F354" s="3" t="s">
-        <v>1378</v>
+        <v>1374</v>
       </c>
       <c r="G354" s="3" t="s">
-        <v>1379</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="355" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15164,22 +15390,22 @@
         <v>1152</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>1380</v>
+        <v>1376</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1381</v>
+        <v>1377</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>1382</v>
+        <v>263</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="G355" s="3" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="356" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15187,45 +15413,45 @@
         <v>1152</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D356" s="3" t="s">
+        <v>1381</v>
+      </c>
+      <c r="E356" s="3" t="s">
+        <v>1382</v>
+      </c>
+      <c r="F356" s="3" t="s">
+        <v>1383</v>
+      </c>
+      <c r="G356" s="3" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A357" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B357" s="3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="C357" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D357" s="3" t="s">
         <v>1386</v>
       </c>
-      <c r="E356" s="3" t="s">
+      <c r="E357" s="3" t="s">
         <v>1387</v>
       </c>
-      <c r="F356" s="3" t="s">
+      <c r="F357" s="3" t="s">
         <v>1388</v>
       </c>
-      <c r="G356" s="3" t="s">
+      <c r="G357" s="3" t="s">
         <v>1389</v>
-      </c>
-    </row>
-    <row r="357" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A357" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B357" s="4" t="s">
-        <v>1749</v>
-      </c>
-      <c r="C357" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D357" s="4" t="s">
-        <v>1750</v>
-      </c>
-      <c r="E357" s="4" t="s">
-        <v>1751</v>
-      </c>
-      <c r="F357" s="4" t="s">
-        <v>1752</v>
-      </c>
-      <c r="G357" s="4" t="s">
-        <v>1753</v>
       </c>
     </row>
     <row r="358" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -15233,68 +15459,68 @@
         <v>1152</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>2032</v>
+        <v>1749</v>
       </c>
       <c r="C358" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D358" s="4" t="s">
-        <v>500</v>
+        <v>1750</v>
       </c>
       <c r="E358" s="4" t="s">
-        <v>2033</v>
+        <v>1751</v>
       </c>
       <c r="F358" s="4" t="s">
-        <v>2034</v>
+        <v>1752</v>
       </c>
       <c r="G358" s="4" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A359" s="4" t="s">
         <v>1152</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>2064</v>
+        <v>2032</v>
       </c>
       <c r="C359" s="4" t="s">
         <v>66</v>
       </c>
       <c r="D359" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E359" s="4" t="s">
+        <v>2033</v>
+      </c>
+      <c r="F359" s="4" t="s">
+        <v>2034</v>
+      </c>
+      <c r="G359" s="4" t="s">
+        <v>2035</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A360" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B360" s="4" t="s">
+        <v>2064</v>
+      </c>
+      <c r="C360" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D360" s="4" t="s">
         <v>2065</v>
       </c>
-      <c r="E359" s="4" t="s">
+      <c r="E360" s="4" t="s">
         <v>2066</v>
       </c>
-      <c r="F359" s="4" t="s">
+      <c r="F360" s="4" t="s">
         <v>2067</v>
       </c>
-      <c r="G359" s="4" t="s">
+      <c r="G360" s="4" t="s">
         <v>2068</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A360" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B360" s="3" t="s">
-        <v>1390</v>
-      </c>
-      <c r="C360" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D360" s="3" t="s">
-        <v>763</v>
-      </c>
-      <c r="E360" s="3" t="s">
-        <v>1391</v>
-      </c>
-      <c r="F360" s="3" t="s">
-        <v>1392</v>
-      </c>
-      <c r="G360" s="3" t="s">
-        <v>1393</v>
       </c>
     </row>
     <row r="361" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15302,22 +15528,22 @@
         <v>1152</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>1394</v>
+        <v>1390</v>
       </c>
       <c r="C361" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>1395</v>
+        <v>763</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="G361" s="3" t="s">
-        <v>1398</v>
+        <v>1393</v>
       </c>
     </row>
     <row r="362" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15325,22 +15551,22 @@
         <v>1152</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="C362" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>831</v>
+        <v>1395</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>500</v>
+        <v>1396</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>1400</v>
+        <v>1397</v>
       </c>
       <c r="G362" s="3" t="s">
-        <v>1401</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="363" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15348,22 +15574,22 @@
         <v>1152</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>1402</v>
+        <v>1399</v>
       </c>
       <c r="C363" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>1403</v>
+        <v>831</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>1404</v>
+        <v>500</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="G363" s="3" t="s">
-        <v>1406</v>
+        <v>1401</v>
       </c>
     </row>
     <row r="364" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15371,22 +15597,22 @@
         <v>1152</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="C364" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>1410</v>
+        <v>1405</v>
       </c>
       <c r="G364" s="3" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="365" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15394,22 +15620,22 @@
         <v>1152</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="C365" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1414</v>
+        <v>1409</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="G365" s="3" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
     </row>
     <row r="366" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15417,22 +15643,22 @@
         <v>1152</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="C366" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1418</v>
+        <v>1413</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="G366" s="3" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="367" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15440,22 +15666,22 @@
         <v>1152</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>1422</v>
+        <v>1417</v>
       </c>
       <c r="C367" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="G367" s="3" t="s">
-        <v>1426</v>
+        <v>1421</v>
       </c>
     </row>
     <row r="368" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15463,22 +15689,22 @@
         <v>1152</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="C368" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>1430</v>
+        <v>1425</v>
       </c>
       <c r="G368" s="3" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="369" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15486,22 +15712,22 @@
         <v>1152</v>
       </c>
       <c r="B369" s="3" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="C369" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D369" s="3" t="s">
-        <v>1260</v>
+        <v>1428</v>
       </c>
       <c r="E369" s="3" t="s">
-        <v>1433</v>
+        <v>1429</v>
       </c>
       <c r="F369" s="3" t="s">
-        <v>1434</v>
+        <v>1430</v>
       </c>
       <c r="G369" s="3" t="s">
-        <v>1435</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="370" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15509,22 +15735,22 @@
         <v>1152</v>
       </c>
       <c r="B370" s="3" t="s">
-        <v>1436</v>
+        <v>1432</v>
       </c>
       <c r="C370" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D370" s="3" t="s">
-        <v>1437</v>
+        <v>1260</v>
       </c>
       <c r="E370" s="3" t="s">
-        <v>1438</v>
+        <v>1433</v>
       </c>
       <c r="F370" s="3" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="G370" s="3" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
     </row>
     <row r="371" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15532,22 +15758,22 @@
         <v>1152</v>
       </c>
       <c r="B371" s="3" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="C371" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D371" s="3" t="s">
-        <v>1442</v>
+        <v>1437</v>
       </c>
       <c r="E371" s="3" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="F371" s="3" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="G371" s="3" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="372" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15555,22 +15781,22 @@
         <v>1152</v>
       </c>
       <c r="B372" s="3" t="s">
-        <v>1446</v>
+        <v>1441</v>
       </c>
       <c r="C372" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D372" s="3" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="E372" s="3" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="F372" s="3" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="G372" s="3" t="s">
-        <v>1450</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="373" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15578,68 +15804,68 @@
         <v>1152</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D373" s="3" t="s">
+        <v>1447</v>
+      </c>
+      <c r="E373" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F373" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G373" s="3" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A374" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B374" s="3" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C374" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D374" s="3" t="s">
         <v>1452</v>
       </c>
-      <c r="E373" s="3" t="s">
+      <c r="E374" s="3" t="s">
         <v>1453</v>
       </c>
-      <c r="F373" s="3" t="s">
+      <c r="F374" s="3" t="s">
         <v>1454</v>
       </c>
-      <c r="G373" s="3" t="s">
+      <c r="G374" s="3" t="s">
         <v>1455</v>
       </c>
     </row>
-    <row r="374" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A374" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B374" s="4" t="s">
-        <v>1754</v>
-      </c>
-      <c r="C374" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D374" s="4" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E374" s="4" t="s">
-        <v>1755</v>
-      </c>
-      <c r="F374" s="4" t="s">
-        <v>1756</v>
-      </c>
-      <c r="G374" s="4" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A375" s="4" t="s">
         <v>1152</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1798</v>
+        <v>1754</v>
       </c>
       <c r="C375" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D375" s="4" t="s">
-        <v>1799</v>
+        <v>1758</v>
       </c>
       <c r="E375" s="4" t="s">
-        <v>1800</v>
+        <v>1755</v>
       </c>
       <c r="F375" s="4" t="s">
-        <v>1801</v>
+        <v>1756</v>
       </c>
       <c r="G375" s="4" t="s">
-        <v>1802</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="376" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -15647,22 +15873,22 @@
         <v>1152</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1872</v>
+        <v>1798</v>
       </c>
       <c r="C376" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D376" s="4" t="s">
-        <v>1873</v>
+        <v>1799</v>
       </c>
       <c r="E376" s="4" t="s">
-        <v>1874</v>
+        <v>1800</v>
       </c>
       <c r="F376" s="4" t="s">
-        <v>1875</v>
+        <v>1801</v>
       </c>
       <c r="G376" s="4" t="s">
-        <v>1876</v>
+        <v>1802</v>
       </c>
     </row>
     <row r="377" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -15670,22 +15896,22 @@
         <v>1152</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1962</v>
+        <v>1872</v>
       </c>
       <c r="C377" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D377" s="4" t="s">
-        <v>1963</v>
+        <v>1873</v>
       </c>
       <c r="E377" s="4" t="s">
-        <v>1964</v>
+        <v>1874</v>
       </c>
       <c r="F377" s="4" t="s">
-        <v>1965</v>
+        <v>1875</v>
       </c>
       <c r="G377" s="4" t="s">
-        <v>1966</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="378" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -15693,45 +15919,45 @@
         <v>1152</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>2036</v>
+        <v>1962</v>
       </c>
       <c r="C378" s="4" t="s">
         <v>129</v>
       </c>
       <c r="D378" s="4" t="s">
+        <v>1963</v>
+      </c>
+      <c r="E378" s="4" t="s">
+        <v>1964</v>
+      </c>
+      <c r="F378" s="4" t="s">
+        <v>1965</v>
+      </c>
+      <c r="G378" s="4" t="s">
+        <v>1966</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A379" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B379" s="4" t="s">
+        <v>2036</v>
+      </c>
+      <c r="C379" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D379" s="4" t="s">
         <v>2037</v>
       </c>
-      <c r="E378" s="4" t="s">
+      <c r="E379" s="4" t="s">
         <v>2038</v>
       </c>
-      <c r="F378" s="4" t="s">
+      <c r="F379" s="4" t="s">
         <v>2039</v>
       </c>
-      <c r="G378" s="4" t="s">
+      <c r="G379" s="4" t="s">
         <v>2040</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A379" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B379" s="3" t="s">
-        <v>1456</v>
-      </c>
-      <c r="C379" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="D379" s="3" t="s">
-        <v>1457</v>
-      </c>
-      <c r="E379" s="3" t="s">
-        <v>1458</v>
-      </c>
-      <c r="F379" s="3" t="s">
-        <v>1459</v>
-      </c>
-      <c r="G379" s="3" t="s">
-        <v>1460</v>
       </c>
     </row>
     <row r="380" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15739,22 +15965,22 @@
         <v>1152</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>1463</v>
+        <v>1456</v>
       </c>
       <c r="C380" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1464</v>
+        <v>1457</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1465</v>
+        <v>1458</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>1466</v>
+        <v>1459</v>
       </c>
       <c r="G380" s="3" t="s">
-        <v>1467</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="381" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15762,22 +15988,22 @@
         <v>1152</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="C381" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1469</v>
+        <v>1464</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="G381" s="3" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="382" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15785,22 +16011,22 @@
         <v>1152</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>1473</v>
+        <v>1468</v>
       </c>
       <c r="C382" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="G382" s="3" t="s">
-        <v>1477</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="383" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15808,22 +16034,22 @@
         <v>1152</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="C383" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1480</v>
+        <v>1475</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="G383" s="3" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="384" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15831,22 +16057,22 @@
         <v>1152</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="C384" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>911</v>
+        <v>1479</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1484</v>
+        <v>1480</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>1485</v>
+        <v>1481</v>
       </c>
       <c r="G384" s="3" t="s">
-        <v>1486</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="385" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15854,22 +16080,22 @@
         <v>1152</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>1487</v>
+        <v>1483</v>
       </c>
       <c r="C385" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>1488</v>
+        <v>911</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="G385" s="3" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="386" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -15877,45 +16103,45 @@
         <v>1152</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>1492</v>
+        <v>1487</v>
       </c>
       <c r="C386" s="3" t="s">
         <v>195</v>
       </c>
       <c r="D386" s="3" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E386" s="3" t="s">
+        <v>1489</v>
+      </c>
+      <c r="F386" s="3" t="s">
+        <v>1490</v>
+      </c>
+      <c r="G386" s="3" t="s">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A387" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B387" s="3" t="s">
+        <v>1492</v>
+      </c>
+      <c r="C387" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D387" s="3" t="s">
         <v>831</v>
       </c>
-      <c r="E386" s="3" t="s">
+      <c r="E387" s="3" t="s">
         <v>1493</v>
       </c>
-      <c r="F386" s="3" t="s">
+      <c r="F387" s="3" t="s">
         <v>1494</v>
       </c>
-      <c r="G386" s="3" t="s">
+      <c r="G387" s="3" t="s">
         <v>1495</v>
-      </c>
-    </row>
-    <row r="387" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A387" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B387" s="4" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C387" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D387" s="4" t="s">
-        <v>1626</v>
-      </c>
-      <c r="E387" s="4" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F387" s="4" t="s">
-        <v>1628</v>
-      </c>
-      <c r="G387" s="4" t="s">
-        <v>1629</v>
       </c>
     </row>
     <row r="388" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -15923,22 +16149,22 @@
         <v>1152</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1669</v>
+        <v>1625</v>
       </c>
       <c r="C388" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D388" s="4" t="s">
-        <v>1670</v>
+        <v>1626</v>
       </c>
       <c r="E388" s="4" t="s">
-        <v>1671</v>
+        <v>1627</v>
       </c>
       <c r="F388" s="4" t="s">
-        <v>1672</v>
+        <v>1628</v>
       </c>
       <c r="G388" s="4" t="s">
-        <v>1673</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="389" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -15946,22 +16172,22 @@
         <v>1152</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1696</v>
+        <v>1669</v>
       </c>
       <c r="C389" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D389" s="4" t="s">
-        <v>1697</v>
+        <v>1670</v>
       </c>
       <c r="E389" s="4" t="s">
-        <v>1698</v>
+        <v>1671</v>
       </c>
       <c r="F389" s="4" t="s">
-        <v>1699</v>
+        <v>1672</v>
       </c>
       <c r="G389" s="4" t="s">
-        <v>1700</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="390" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -15969,45 +16195,45 @@
         <v>1152</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1744</v>
+        <v>1696</v>
       </c>
       <c r="C390" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D390" s="4" t="s">
-        <v>1745</v>
+        <v>1697</v>
       </c>
       <c r="E390" s="4" t="s">
-        <v>1746</v>
+        <v>1698</v>
       </c>
       <c r="F390" s="4" t="s">
-        <v>1747</v>
+        <v>1699</v>
       </c>
       <c r="G390" s="4" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="391" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A391" s="4" t="s">
         <v>1152</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>2012</v>
+        <v>1744</v>
       </c>
       <c r="C391" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D391" s="4" t="s">
-        <v>2013</v>
+        <v>1745</v>
       </c>
       <c r="E391" s="4" t="s">
-        <v>2014</v>
+        <v>1746</v>
       </c>
       <c r="F391" s="4" t="s">
-        <v>2015</v>
+        <v>1747</v>
       </c>
       <c r="G391" s="4" t="s">
-        <v>2016</v>
+        <v>1748</v>
       </c>
     </row>
     <row r="392" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -16015,22 +16241,22 @@
         <v>1152</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C392" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D392" s="4" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="E392" s="4" t="s">
-        <v>2019</v>
+        <v>2014</v>
       </c>
       <c r="F392" s="4" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="G392" s="4" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="393" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
@@ -16038,91 +16264,91 @@
         <v>1152</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="C393" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D393" s="4" t="s">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="E393" s="4" t="s">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="F393" s="4" t="s">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="G393" s="4" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A394" s="4" t="s">
         <v>1152</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>2031</v>
+        <v>2022</v>
       </c>
       <c r="C394" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D394" s="4" t="s">
-        <v>2027</v>
+        <v>2023</v>
       </c>
       <c r="E394" s="4" t="s">
-        <v>2028</v>
+        <v>2024</v>
       </c>
       <c r="F394" s="4" t="s">
-        <v>2029</v>
+        <v>2025</v>
       </c>
       <c r="G394" s="4" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="395" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A395" s="4" t="s">
         <v>1152</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>2041</v>
+        <v>2031</v>
       </c>
       <c r="C395" s="4" t="s">
         <v>195</v>
       </c>
       <c r="D395" s="4" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E395" s="4" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F395" s="4" t="s">
+        <v>2029</v>
+      </c>
+      <c r="G395" s="4" t="s">
+        <v>2030</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A396" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B396" s="4" t="s">
+        <v>2041</v>
+      </c>
+      <c r="C396" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D396" s="4" t="s">
         <v>2042</v>
       </c>
-      <c r="E395" s="4" t="s">
+      <c r="E396" s="4" t="s">
         <v>2043</v>
       </c>
-      <c r="F395" s="4" t="s">
+      <c r="F396" s="4" t="s">
         <v>2044</v>
       </c>
-      <c r="G395" s="4" t="s">
+      <c r="G396" s="4" t="s">
         <v>2045</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A396" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B396" s="3" t="s">
-        <v>1496</v>
-      </c>
-      <c r="C396" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D396" s="3" t="s">
-        <v>1497</v>
-      </c>
-      <c r="E396" s="3" t="s">
-        <v>1498</v>
-      </c>
-      <c r="F396" s="3" t="s">
-        <v>1499</v>
-      </c>
-      <c r="G396" s="3" t="s">
-        <v>1500</v>
       </c>
     </row>
     <row r="397" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16130,22 +16356,22 @@
         <v>1152</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="C397" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>1504</v>
+        <v>1499</v>
       </c>
       <c r="G397" s="3" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="398" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16153,22 +16379,22 @@
         <v>1152</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="C398" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1058</v>
+        <v>1502</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1507</v>
+        <v>1503</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>1508</v>
+        <v>1504</v>
       </c>
       <c r="G398" s="3" t="s">
-        <v>1509</v>
+        <v>1505</v>
       </c>
     </row>
     <row r="399" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16176,22 +16402,22 @@
         <v>1152</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>1510</v>
+        <v>1506</v>
       </c>
       <c r="C399" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1511</v>
+        <v>1058</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1512</v>
+        <v>1507</v>
       </c>
       <c r="F399" s="3" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="G399" s="3" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
     </row>
     <row r="400" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16199,22 +16425,22 @@
         <v>1152</v>
       </c>
       <c r="B400" s="3" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="C400" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D400" s="3" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
       <c r="E400" s="3" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="F400" s="3" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="G400" s="3" t="s">
-        <v>1519</v>
+        <v>1514</v>
       </c>
     </row>
     <row r="401" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16222,22 +16448,22 @@
         <v>1152</v>
       </c>
       <c r="B401" s="3" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="C401" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D401" s="3" t="s">
-        <v>956</v>
+        <v>1516</v>
       </c>
       <c r="E401" s="3" t="s">
-        <v>1521</v>
+        <v>1517</v>
       </c>
       <c r="F401" s="3" t="s">
-        <v>1522</v>
+        <v>1518</v>
       </c>
       <c r="G401" s="3" t="s">
-        <v>1523</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="402" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16245,68 +16471,68 @@
         <v>1152</v>
       </c>
       <c r="B402" s="3" t="s">
-        <v>1524</v>
+        <v>1520</v>
       </c>
       <c r="C402" s="3" t="s">
         <v>236</v>
       </c>
       <c r="D402" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="E402" s="3" t="s">
+        <v>1521</v>
+      </c>
+      <c r="F402" s="3" t="s">
+        <v>1522</v>
+      </c>
+      <c r="G402" s="3" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A403" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B403" s="3" t="s">
+        <v>1524</v>
+      </c>
+      <c r="C403" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D403" s="3" t="s">
         <v>1525</v>
       </c>
-      <c r="E402" s="3" t="s">
+      <c r="E403" s="3" t="s">
         <v>1526</v>
       </c>
-      <c r="F402" s="3" t="s">
+      <c r="F403" s="3" t="s">
         <v>1527</v>
       </c>
-      <c r="G402" s="3" t="s">
+      <c r="G403" s="3" t="s">
         <v>1528</v>
       </c>
     </row>
-    <row r="403" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A403" s="4" t="s">
+    <row r="404" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A404" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="B403" s="4" t="s">
+      <c r="B404" s="4" t="s">
         <v>1793</v>
       </c>
-      <c r="C403" s="4" t="s">
+      <c r="C404" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D403" s="4" t="s">
+      <c r="D404" s="4" t="s">
         <v>1794</v>
       </c>
-      <c r="E403" s="4" t="s">
+      <c r="E404" s="4" t="s">
         <v>1795</v>
       </c>
-      <c r="F403" s="4" t="s">
+      <c r="F404" s="4" t="s">
         <v>1796</v>
       </c>
-      <c r="G403" s="4" t="s">
+      <c r="G404" s="4" t="s">
         <v>1797</v>
-      </c>
-    </row>
-    <row r="404" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A404" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B404" s="3" t="s">
-        <v>1461</v>
-      </c>
-      <c r="C404" s="3" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D404" s="3" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E404" s="3" t="s">
-        <v>2048</v>
-      </c>
-      <c r="F404" s="3" t="s">
-        <v>2047</v>
-      </c>
-      <c r="G404" s="3" t="s">
-        <v>2046</v>
       </c>
     </row>
     <row r="405" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16314,91 +16540,91 @@
         <v>1152</v>
       </c>
       <c r="B405" s="3" t="s">
-        <v>1355</v>
+        <v>1461</v>
       </c>
       <c r="C405" s="3" t="s">
         <v>1828</v>
       </c>
       <c r="D405" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="E405" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="F405" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="G405" s="3" t="s">
+        <v>2046</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A406" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B406" s="3" t="s">
+        <v>1355</v>
+      </c>
+      <c r="C406" s="3" t="s">
+        <v>1828</v>
+      </c>
+      <c r="D406" s="3" t="s">
         <v>1829</v>
       </c>
-      <c r="E405" s="3" t="s">
+      <c r="E406" s="3" t="s">
         <v>1830</v>
       </c>
-      <c r="F405" s="3" t="s">
+      <c r="F406" s="3" t="s">
         <v>1831</v>
       </c>
-      <c r="G405" s="3" t="s">
+      <c r="G406" s="3" t="s">
         <v>1832</v>
       </c>
     </row>
-    <row r="406" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A406" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B406" s="4" t="s">
-        <v>1686</v>
-      </c>
-      <c r="C406" s="4" t="s">
-        <v>297</v>
-      </c>
-      <c r="D406" s="4" t="s">
-        <v>1687</v>
-      </c>
-      <c r="E406" s="4" t="s">
-        <v>1688</v>
-      </c>
-      <c r="F406" s="4" t="s">
-        <v>1689</v>
-      </c>
-      <c r="G406" s="4" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="407" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
         <v>1152</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1823</v>
+        <v>1686</v>
       </c>
       <c r="C407" s="4" t="s">
         <v>297</v>
       </c>
       <c r="D407" s="4" t="s">
+        <v>1687</v>
+      </c>
+      <c r="E407" s="4" t="s">
+        <v>1688</v>
+      </c>
+      <c r="F407" s="4" t="s">
+        <v>1689</v>
+      </c>
+      <c r="G407" s="4" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="408" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A408" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B408" s="4" t="s">
+        <v>1823</v>
+      </c>
+      <c r="C408" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D408" s="4" t="s">
         <v>1824</v>
       </c>
-      <c r="E407" s="4" t="s">
+      <c r="E408" s="4" t="s">
         <v>1825</v>
       </c>
-      <c r="F407" s="4" t="s">
+      <c r="F408" s="4" t="s">
         <v>1826</v>
       </c>
-      <c r="G407" s="4" t="s">
+      <c r="G408" s="4" t="s">
         <v>1827</v>
-      </c>
-    </row>
-    <row r="408" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A408" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B408" s="3" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C408" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D408" s="3" t="s">
-        <v>1530</v>
-      </c>
-      <c r="E408" s="3" t="s">
-        <v>1531</v>
-      </c>
-      <c r="F408" s="3" t="s">
-        <v>1532</v>
-      </c>
-      <c r="G408" s="3" t="s">
-        <v>1533</v>
       </c>
     </row>
     <row r="409" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16406,22 +16632,22 @@
         <v>1152</v>
       </c>
       <c r="B409" s="3" t="s">
-        <v>1534</v>
+        <v>1529</v>
       </c>
       <c r="C409" s="3" t="s">
         <v>343</v>
       </c>
       <c r="D409" s="3" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="E409" s="3" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="F409" s="3" t="s">
-        <v>1537</v>
+        <v>1532</v>
       </c>
       <c r="G409" s="3" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
     </row>
     <row r="410" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16429,22 +16655,22 @@
         <v>1152</v>
       </c>
       <c r="B410" s="3" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="C410" s="3" t="s">
         <v>343</v>
       </c>
       <c r="D410" s="3" t="s">
-        <v>1358</v>
+        <v>1535</v>
       </c>
       <c r="E410" s="3" t="s">
-        <v>1540</v>
+        <v>1536</v>
       </c>
       <c r="F410" s="3" t="s">
-        <v>1541</v>
+        <v>1537</v>
       </c>
       <c r="G410" s="3" t="s">
-        <v>1542</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="411" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16452,68 +16678,68 @@
         <v>1152</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>1543</v>
+        <v>1539</v>
       </c>
       <c r="C411" s="3" t="s">
         <v>343</v>
       </c>
       <c r="D411" s="3" t="s">
+        <v>1358</v>
+      </c>
+      <c r="E411" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="F411" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="G411" s="3" t="s">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="412" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A412" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B412" s="3" t="s">
+        <v>1543</v>
+      </c>
+      <c r="C412" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D412" s="3" t="s">
         <v>1544</v>
       </c>
-      <c r="E411" s="3" t="s">
+      <c r="E412" s="3" t="s">
         <v>1545</v>
       </c>
-      <c r="F411" s="3" t="s">
+      <c r="F412" s="3" t="s">
         <v>1546</v>
       </c>
-      <c r="G411" s="3" t="s">
+      <c r="G412" s="3" t="s">
         <v>1547</v>
       </c>
     </row>
-    <row r="412" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A412" s="4" t="s">
+    <row r="413" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A413" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="B412" s="4" t="s">
+      <c r="B413" s="4" t="s">
         <v>1852</v>
       </c>
-      <c r="C412" s="4" t="s">
+      <c r="C413" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="D412" s="4" t="s">
+      <c r="D413" s="4" t="s">
         <v>1853</v>
       </c>
-      <c r="E412" s="4" t="s">
+      <c r="E413" s="4" t="s">
         <v>1854</v>
       </c>
-      <c r="F412" s="4" t="s">
+      <c r="F413" s="4" t="s">
         <v>1855</v>
       </c>
-      <c r="G412" s="4" t="s">
+      <c r="G413" s="4" t="s">
         <v>1856</v>
-      </c>
-    </row>
-    <row r="413" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A413" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B413" s="3" t="s">
-        <v>1548</v>
-      </c>
-      <c r="C413" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="D413" s="3" t="s">
-        <v>1549</v>
-      </c>
-      <c r="E413" s="3" t="s">
-        <v>1550</v>
-      </c>
-      <c r="F413" s="3" t="s">
-        <v>1551</v>
-      </c>
-      <c r="G413" s="3" t="s">
-        <v>1552</v>
       </c>
     </row>
     <row r="414" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16521,68 +16747,68 @@
         <v>1152</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="C414" s="3" t="s">
         <v>364</v>
       </c>
       <c r="D414" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E414" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="F414" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="G414" s="3" t="s">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="415" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A415" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B415" s="3" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C415" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D415" s="3" t="s">
         <v>1554</v>
       </c>
-      <c r="E414" s="3" t="s">
+      <c r="E415" s="3" t="s">
         <v>1555</v>
       </c>
-      <c r="F414" s="3" t="s">
+      <c r="F415" s="3" t="s">
         <v>1556</v>
       </c>
-      <c r="G414" s="3" t="s">
+      <c r="G415" s="3" t="s">
         <v>1557</v>
       </c>
     </row>
-    <row r="415" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A415" s="4" t="s">
+    <row r="416" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A416" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="B415" s="4" t="s">
+      <c r="B416" s="4" t="s">
         <v>1769</v>
       </c>
-      <c r="C415" s="4" t="s">
+      <c r="C416" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="D415" s="4" t="s">
+      <c r="D416" s="4" t="s">
         <v>1770</v>
       </c>
-      <c r="E415" s="4" t="s">
+      <c r="E416" s="4" t="s">
         <v>1771</v>
       </c>
-      <c r="F415" s="4" t="s">
+      <c r="F416" s="4" t="s">
         <v>1772</v>
       </c>
-      <c r="G415" s="4" t="s">
+      <c r="G416" s="4" t="s">
         <v>1773</v>
-      </c>
-    </row>
-    <row r="416" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A416" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B416" s="3" t="s">
-        <v>1558</v>
-      </c>
-      <c r="C416" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D416" s="3" t="s">
-        <v>1559</v>
-      </c>
-      <c r="E416" s="3" t="s">
-        <v>1560</v>
-      </c>
-      <c r="F416" s="3" t="s">
-        <v>1561</v>
-      </c>
-      <c r="G416" s="3" t="s">
-        <v>1562</v>
       </c>
     </row>
     <row r="417" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16590,22 +16816,22 @@
         <v>1152</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1563</v>
+        <v>1558</v>
       </c>
       <c r="C417" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1188</v>
+        <v>1559</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1564</v>
+        <v>1560</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>1565</v>
+        <v>1561</v>
       </c>
       <c r="G417" s="3" t="s">
-        <v>1566</v>
+        <v>1562</v>
       </c>
     </row>
     <row r="418" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16613,7 +16839,7 @@
         <v>1152</v>
       </c>
       <c r="B418" s="3" t="s">
-        <v>1567</v>
+        <v>1563</v>
       </c>
       <c r="C418" s="3" t="s">
         <v>405</v>
@@ -16622,13 +16848,13 @@
         <v>1188</v>
       </c>
       <c r="E418" s="3" t="s">
-        <v>1568</v>
+        <v>1564</v>
       </c>
       <c r="F418" s="3" t="s">
-        <v>1569</v>
+        <v>1565</v>
       </c>
       <c r="G418" s="3" t="s">
-        <v>1570</v>
+        <v>1566</v>
       </c>
     </row>
     <row r="419" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16636,22 +16862,22 @@
         <v>1152</v>
       </c>
       <c r="B419" s="3" t="s">
-        <v>1571</v>
+        <v>1567</v>
       </c>
       <c r="C419" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D419" s="3" t="s">
-        <v>1358</v>
+        <v>1188</v>
       </c>
       <c r="E419" s="3" t="s">
-        <v>1572</v>
+        <v>1568</v>
       </c>
       <c r="F419" s="3" t="s">
-        <v>1573</v>
+        <v>1569</v>
       </c>
       <c r="G419" s="3" t="s">
-        <v>1574</v>
+        <v>1570</v>
       </c>
     </row>
     <row r="420" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16659,22 +16885,22 @@
         <v>1152</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>1575</v>
+        <v>1571</v>
       </c>
       <c r="C420" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1576</v>
+        <v>1358</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="G420" s="3" t="s">
-        <v>1579</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="421" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16682,22 +16908,22 @@
         <v>1152</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="C421" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1582</v>
+        <v>1577</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="G421" s="3" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="422" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16705,68 +16931,68 @@
         <v>1152</v>
       </c>
       <c r="B422" s="3" t="s">
-        <v>1585</v>
+        <v>1580</v>
       </c>
       <c r="C422" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D422" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="E422" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="F422" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G422" s="3" t="s">
+        <v>1584</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A423" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B423" s="3" t="s">
+        <v>1585</v>
+      </c>
+      <c r="C423" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D423" s="3" t="s">
         <v>1586</v>
       </c>
-      <c r="E422" s="3" t="s">
+      <c r="E423" s="3" t="s">
         <v>1587</v>
       </c>
-      <c r="F422" s="3" t="s">
+      <c r="F423" s="3" t="s">
         <v>1588</v>
       </c>
-      <c r="G422" s="3" t="s">
+      <c r="G423" s="3" t="s">
         <v>1589</v>
       </c>
     </row>
-    <row r="423" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A423" s="4" t="s">
+    <row r="424" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A424" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="B423" s="4" t="s">
+      <c r="B424" s="4" t="s">
         <v>1857</v>
       </c>
-      <c r="C423" s="4" t="s">
+      <c r="C424" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="D423" s="4" t="s">
+      <c r="D424" s="4" t="s">
         <v>1858</v>
       </c>
-      <c r="E423" s="4" t="s">
+      <c r="E424" s="4" t="s">
         <v>1859</v>
       </c>
-      <c r="F423" s="4" t="s">
+      <c r="F424" s="4" t="s">
         <v>1860</v>
       </c>
-      <c r="G423" s="4" t="s">
+      <c r="G424" s="4" t="s">
         <v>1861</v>
-      </c>
-    </row>
-    <row r="424" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A424" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B424" s="3" t="s">
-        <v>1590</v>
-      </c>
-      <c r="C424" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="D424" s="3" t="s">
-        <v>1591</v>
-      </c>
-      <c r="E424" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F424" s="3" t="s">
-        <v>1592</v>
-      </c>
-      <c r="G424" s="3" t="s">
-        <v>1593</v>
       </c>
     </row>
     <row r="425" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16774,22 +17000,22 @@
         <v>1152</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>1594</v>
+        <v>1590</v>
       </c>
       <c r="C425" s="3" t="s">
         <v>441</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1188</v>
+        <v>1591</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>1595</v>
+        <v>376</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>1596</v>
+        <v>1592</v>
       </c>
       <c r="G425" s="3" t="s">
-        <v>1597</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="426" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -16797,75 +17023,444 @@
         <v>1152</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>1598</v>
+        <v>1594</v>
       </c>
       <c r="C426" s="3" t="s">
         <v>441</v>
       </c>
       <c r="D426" s="3" t="s">
+        <v>1188</v>
+      </c>
+      <c r="E426" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F426" s="3" t="s">
+        <v>1596</v>
+      </c>
+      <c r="G426" s="3" t="s">
+        <v>1597</v>
+      </c>
+    </row>
+    <row r="427" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A427" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B427" s="3" t="s">
+        <v>1598</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D427" s="3" t="s">
         <v>1599</v>
       </c>
-      <c r="E426" s="3" t="s">
+      <c r="E427" s="3" t="s">
         <v>1600</v>
       </c>
-      <c r="F426" s="3" t="s">
+      <c r="F427" s="3" t="s">
         <v>1601</v>
       </c>
-      <c r="G426" s="3" t="s">
+      <c r="G427" s="3" t="s">
         <v>1602</v>
       </c>
     </row>
-    <row r="427" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A427" s="4" t="s">
+    <row r="428" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A428" s="4" t="s">
         <v>1152</v>
       </c>
-      <c r="B427" s="4" t="s">
+      <c r="B428" s="4" t="s">
         <v>1774</v>
       </c>
-      <c r="C427" s="4" t="s">
+      <c r="C428" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="D427" s="4" t="s">
+      <c r="D428" s="4" t="s">
         <v>1775</v>
       </c>
-      <c r="E427" s="4" t="s">
+      <c r="E428" s="4" t="s">
         <v>1776</v>
       </c>
-      <c r="F427" s="4" t="s">
+      <c r="F428" s="4" t="s">
         <v>1777</v>
       </c>
-      <c r="G427" s="4" t="s">
+      <c r="G428" s="4" t="s">
         <v>1778</v>
       </c>
     </row>
-    <row r="428" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A428" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="B428" s="8" t="s">
-        <v>2104</v>
-      </c>
-      <c r="C428" s="8" t="s">
+    <row r="429" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A429" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B429" s="10" t="s">
+        <v>2181</v>
+      </c>
+      <c r="C429" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D429" s="10" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E429" s="10" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F429" s="10" t="s">
+        <v>2111</v>
+      </c>
+      <c r="G429" s="10" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A430" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B430" s="10" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C430" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="D430" s="10" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E430" s="10" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F430" s="10" t="s">
+        <v>2115</v>
+      </c>
+      <c r="G430" s="10" t="s">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A431" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B431" s="10" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C431" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D428" s="8" t="s">
-        <v>2105</v>
-      </c>
-      <c r="E428" s="8" t="s">
-        <v>2106</v>
-      </c>
-      <c r="F428" s="8" t="s">
-        <v>2107</v>
-      </c>
-      <c r="G428" s="8" t="s">
-        <v>2108</v>
+      <c r="D431" s="10" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E431" s="10" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F431" s="10" t="s">
+        <v>2120</v>
+      </c>
+      <c r="G431" s="10" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A432" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B432" s="10" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C432" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D432" s="10" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E432" s="10" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F432" s="10" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G432" s="10" t="s">
+        <v>2126</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A433" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B433" s="10" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C433" s="10" t="s">
+        <v>343</v>
+      </c>
+      <c r="D433" s="10" t="s">
+        <v>1010</v>
+      </c>
+      <c r="E433" s="10" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F433" s="10" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G433" s="10" t="s">
+        <v>2130</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A434" s="10" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B434" s="10" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C434" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D434" s="10" t="s">
+        <v>2131</v>
+      </c>
+      <c r="E434" s="10" t="s">
+        <v>2132</v>
+      </c>
+      <c r="F434" s="10" t="s">
+        <v>2133</v>
+      </c>
+      <c r="G434" s="10" t="s">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A435" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B435" s="10" t="s">
+        <v>2135</v>
+      </c>
+      <c r="C435" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="D435" s="10" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E435" s="10" t="s">
+        <v>2136</v>
+      </c>
+      <c r="F435" s="10" t="s">
+        <v>2137</v>
+      </c>
+      <c r="G435" s="10" t="s">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A436" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B436" s="10" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C436" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="D436" s="10" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E436" s="10" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F436" s="10" t="s">
+        <v>2142</v>
+      </c>
+      <c r="G436" s="10" t="s">
+        <v>2143</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A437" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B437" s="9" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C437" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D437" s="9" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E437" s="9" t="s">
+        <v>2146</v>
+      </c>
+      <c r="F437" s="9" t="s">
+        <v>2147</v>
+      </c>
+      <c r="G437" s="9" t="s">
+        <v>2148</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A438" s="10" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B438" s="10" t="s">
+        <v>2144</v>
+      </c>
+      <c r="C438" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D438" s="10" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E438" s="10" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F438" s="10" t="s">
+        <v>2151</v>
+      </c>
+      <c r="G438" s="10" t="s">
+        <v>2152</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A439" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B439" s="10" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C439" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D439" s="10" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E439" s="10" t="s">
+        <v>2155</v>
+      </c>
+      <c r="F439" s="10" t="s">
+        <v>2156</v>
+      </c>
+      <c r="G439" s="10" t="s">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A440" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B440" s="9" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C440" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D440" s="9" t="s">
+        <v>2159</v>
+      </c>
+      <c r="E440" s="9" t="s">
+        <v>2160</v>
+      </c>
+      <c r="F440" s="9" t="s">
+        <v>2161</v>
+      </c>
+      <c r="G440" s="9" t="s">
+        <v>2162</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A441" s="10" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B441" s="10" t="s">
+        <v>2158</v>
+      </c>
+      <c r="C441" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="D441" s="10" t="s">
+        <v>2163</v>
+      </c>
+      <c r="E441" s="10" t="s">
+        <v>2164</v>
+      </c>
+      <c r="F441" s="10" t="s">
+        <v>2165</v>
+      </c>
+      <c r="G441" s="10" t="s">
+        <v>2166</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A442" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B442" s="10" t="s">
+        <v>2167</v>
+      </c>
+      <c r="C442" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D442" s="10" t="s">
+        <v>2168</v>
+      </c>
+      <c r="E442" s="10" t="s">
+        <v>2169</v>
+      </c>
+      <c r="F442" s="10" t="s">
+        <v>2170</v>
+      </c>
+      <c r="G442" s="10" t="s">
+        <v>2171</v>
+      </c>
+    </row>
+    <row r="443" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A443" s="9" t="s">
+        <v>1152</v>
+      </c>
+      <c r="B443" s="9" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C443" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D443" s="9" t="s">
+        <v>2173</v>
+      </c>
+      <c r="E443" s="9" t="s">
+        <v>2174</v>
+      </c>
+      <c r="F443" s="9" t="s">
+        <v>2175</v>
+      </c>
+      <c r="G443" s="9" t="s">
+        <v>2176</v>
+      </c>
+    </row>
+    <row r="444" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A444" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="B444" s="10" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C444" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="D444" s="10" t="s">
+        <v>2177</v>
+      </c>
+      <c r="E444" s="10" t="s">
+        <v>2178</v>
+      </c>
+      <c r="F444" s="10" t="s">
+        <v>2179</v>
+      </c>
+      <c r="G444" s="10" t="s">
+        <v>2180</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>

--- a/backend/王侯將相最新版.xlsx
+++ b/backend/王侯將相最新版.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\piaget\Desktop\歷史名將\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D45F837A-64D9-45A7-975A-B34D2FB1857C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7ADD8B-5C20-4E11-A537-D18219550DAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{23607111-B237-4551-BBD0-59FB953E8041}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="王侯將相" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="外部資料_1" localSheetId="0" hidden="1">王侯將相!$A$1:$G$444</definedName>
+    <definedName name="外部資料_1" localSheetId="0" hidden="1">王侯將相!$A$1:$G$443</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3108" uniqueCount="2182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3101" uniqueCount="2179">
   <si>
     <t>帝王</t>
   </si>
@@ -3414,18 +3414,6 @@
   </si>
   <si>
     <t>唐生智</t>
-  </si>
-  <si>
-    <t>南京衛戍</t>
-  </si>
-  <si>
-    <t>棄城而逃</t>
-  </si>
-  <si>
-    <t>誓死守南京，結果率先逃跑，指揮混亂。</t>
-  </si>
-  <si>
-    <t>誓死守城先棄遁，金陵城下哭冤魂。</t>
   </si>
   <si>
     <t>李信</t>
@@ -6450,181 +6438,189 @@
     <t>杜聿明</t>
   </si>
   <si>
+    <t>裝甲先驅 / 愚忠誤國</t>
+  </si>
+  <si>
+    <t>國軍首支機械化部隊統帥，血戰崑崙關、四平街擊退林彪，具備頂級大兵團與裝甲指揮力。然政治性格極度懦弱，於野人山與淮海戰役中，兩度盲從最高統帥之災難微操，明知死局仍將數十萬精銳葬送，為「愚忠反噬實體」之極致悲劇。</t>
+  </si>
+  <si>
+    <t>崑崙關外揚兵威，中原雪滿將星頹。</t>
+  </si>
+  <si>
+    <t>陳誠</t>
+  </si>
+  <si>
+    <t>孤島磐石</t>
+  </si>
+  <si>
+    <t>土地改革 / 幣制重塑</t>
+  </si>
+  <si>
+    <t>退守台灣後展現頂級治國實效。以鐵腕推動新台幣發行阻絕惡性通膨；兵不血刃完成三七五減租與耕者有其田，徹底穩固底層社會結構，為台灣經濟奇蹟鑄造絕對之底層基石。</t>
+  </si>
+  <si>
+    <t>孤島風雷驚舊夢，減租放領定基根。</t>
+  </si>
+  <si>
+    <t>胡宗南</t>
+  </si>
+  <si>
+    <t>西北提款機 / 蘑菇戰術受害者</t>
+  </si>
+  <si>
+    <t>擁數十萬最精銳中央軍坐鎮西北，卻在陝北戰場遭彭德懷以絕對劣勢兵力「蘑菇戰術」徹底牽制並殲滅。奪取空城延安僅獲政治虛名，實體軍力卻遭全盤瓦解，為大兵團優勢作戰之絕對反面教材。</t>
+  </si>
+  <si>
+    <t>擁兵四十屯西北，蘑菇戰術化塵埃。</t>
+  </si>
+  <si>
+    <t>張學良</t>
+  </si>
+  <si>
+    <t>散財軍閥</t>
+  </si>
+  <si>
+    <t>丟失東北 / 實體歸零</t>
+  </si>
+  <si>
+    <t>繼承東亞頂級軍工體系與三十萬大軍。九一八事變下達不抵抗命令，將戰略重地與海量軍火拱手讓日，釀成抗戰極端劣勢；西安事變更致使自身軍隊實體遭徹底瓦解，為軍事資源轉化率絕對為零之統帥。</t>
+  </si>
+  <si>
+    <t>瀋陽兵工化劫灰，不發一槍棄重關。</t>
+  </si>
+  <si>
+    <t>傅作義</t>
+  </si>
+  <si>
+    <t>守城飛將</t>
+  </si>
+  <si>
+    <t>防禦大師 / 戰略遲疑</t>
+  </si>
+  <si>
+    <t>涿州孤城抗擊數萬大軍，百靈廟大捷重創日偽，為民國頂級防守反擊大腦。然平津戰役中因欲保全派系實力而戰略猶豫，致使核心主力第 35 軍覆滅，喪失大戰區博弈之最後籌碼。</t>
+  </si>
+  <si>
+    <t>涿州孤城揚威名，百靈廟前鎮胡塵。</t>
+  </si>
+  <si>
+    <t>實幹孤臣</t>
+  </si>
+  <si>
+    <t>保全古都 / 治水總管</t>
+  </si>
+  <si>
+    <t>於北平死局中摒棄愚忠，促成和平解放，實質保全千年古都之文明實體與百萬生靈。建國後任水利部長二十三年，踏遍大江大河推動實體基礎建設，以技術官僚之姿洗刷降將之名。</t>
+  </si>
+  <si>
+    <t>和平一局存燕京，半生戎馬半生水。</t>
+  </si>
+  <si>
+    <t>張作霖</t>
+  </si>
+  <si>
+    <t>東北王</t>
+  </si>
+  <si>
+    <t>軍工實體 / 地緣走鋼索</t>
+  </si>
+  <si>
+    <t>從綠林崛起，於日俄夾縫中締造擁有亞洲頂尖軍工體系與海空軍之奉系霸權。雖戰術思維陳舊敗於北伐，然大是大非前堅拒出賣國家核心主權，於皇姑屯殉身，為舊式軍閥實體建制之巔峰。</t>
+  </si>
+  <si>
+    <t>綠林拔劍起關東，喋血皇姑拒日鋒。</t>
+  </si>
+  <si>
+    <t>閻錫山</t>
+  </si>
+  <si>
+    <t>山西不倒翁</t>
+  </si>
+  <si>
+    <t>實體建軍 / 地緣平衡</t>
+  </si>
+  <si>
+    <t>統治山西三十八年，憑藉表裡山河據險而守。締造太原兵工廠實現軍備自給，於各方勢力中大玩平衡木；然部隊戰術僵化，缺乏外線機動與戰略破局能力，為極致之防禦自保型舊式統帥。</t>
+  </si>
+  <si>
+    <t>據險太原觀虎鬥，表裡山河鑄堅城。</t>
+  </si>
+  <si>
+    <t>模範督軍</t>
+  </si>
+  <si>
+    <t>閉環經濟 / 村本政治</t>
+  </si>
+  <si>
+    <t>於軍閥割據中推行實用主義治理。築窄軌鐵路以自保，建西北實業公司完善輕重工業體系；推行村本政治與六政三事，將山西打造成民國罕見之實體經濟閉環與模範省份。</t>
+  </si>
+  <si>
+    <t>窄軌綿延鎖晉地，實業六政惠三晉。</t>
+  </si>
+  <si>
+    <t>吳佩孚</t>
+  </si>
+  <si>
+    <t>悲情玉帥</t>
+  </si>
+  <si>
+    <t>戰術天才 / 實體虛無</t>
+  </si>
+  <si>
+    <t>直皖與第一次直奉戰爭中展現頂級野戰機動與大兵團指揮，為首位登上《時代》封面之中國軍閥。然極端排斥建立現代工業實體與穩固地緣基本盤；雖晚年拒作漢奸保全民族氣節，但在殘酷之實體絞肉機中，終因缺乏戰略縱深與後勤而全盤覆滅。</t>
+  </si>
+  <si>
+    <t>洛陽虎踞震北洋，空有將才無實疆。</t>
+  </si>
+  <si>
+    <t>陳炯明</t>
+  </si>
+  <si>
+    <t>聯省先驅</t>
+  </si>
+  <si>
+    <t>實體建制 / 廣東大治</t>
+  </si>
+  <si>
+    <t>拒絕武力盲目北伐，推動「聯省自治」。於廣東大舉興辦教育、修築公路、禁絕煙賭並確立現代司法框架，為近現代極具前瞻性之地方實體現代化締造者，惜藍圖遭大一統戰火摧毀。</t>
+  </si>
+  <si>
+    <t>聯省宏圖興百業，羊城舊夢碎干戈。</t>
+  </si>
+  <si>
+    <t>破產軍閥</t>
+  </si>
+  <si>
+    <t>理想碎裂 / 戰略失能</t>
+  </si>
+  <si>
+    <t>早年驅逐桂系統一嶺南。然軍隊組織與戰術思維停滯，於東征戰役中面對具備現代政戰體系之黃埔軍毫無招架之力，喪失根據地，武裝實體遭徹底瓦解，無法為政治理想提供暴力背書。</t>
+  </si>
+  <si>
+    <t>粵海雄兵終化土，空懷壯志恨黃埔。</t>
+  </si>
+  <si>
+    <t>趙括</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>悲情救火隊長</t>
-  </si>
-  <si>
-    <t>裝甲先驅 / 愚忠誤國</t>
-  </si>
-  <si>
-    <t>國軍首支機械化部隊統帥，血戰崑崙關、四平街擊退林彪，具備頂級大兵團與裝甲指揮力。然政治性格極度懦弱，於野人山與淮海戰役中，兩度盲從最高統帥之災難微操，明知死局仍將數十萬精銳葬送，為「愚忠反噬實體」之極致悲劇。</t>
-  </si>
-  <si>
-    <t>崑崙關外揚兵威，中原雪滿將星頹。</t>
-  </si>
-  <si>
-    <t>陳誠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>政治統帥</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>土木系 / 瞎指揮</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>土木系絕對核心，具備強大派系建軍力。然戰場微操與戰區宏觀指揮失能，東北剿總任內盲目裁撤偽滿軍隊，將數十萬即戰力推向敵營，釀成不可挽回之大兵團戰略災難。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>擁兵百萬圖雄據，白山黑水誤全盤。</t>
-  </si>
-  <si>
-    <t>孤島磐石</t>
-  </si>
-  <si>
-    <t>土地改革 / 幣制重塑</t>
-  </si>
-  <si>
-    <t>退守台灣後展現頂級治國實效。以鐵腕推動新台幣發行阻絕惡性通膨；兵不血刃完成三七五減租與耕者有其田，徹底穩固底層社會結構，為台灣經濟奇蹟鑄造絕對之底層基石。</t>
-  </si>
-  <si>
-    <t>孤島風雷驚舊夢，減租放領定基根。</t>
-  </si>
-  <si>
-    <t>胡宗南</t>
-  </si>
-  <si>
-    <t>西北提款機 / 蘑菇戰術受害者</t>
-  </si>
-  <si>
-    <t>擁數十萬最精銳中央軍坐鎮西北，卻在陝北戰場遭彭德懷以絕對劣勢兵力「蘑菇戰術」徹底牽制並殲滅。奪取空城延安僅獲政治虛名，實體軍力卻遭全盤瓦解，為大兵團優勢作戰之絕對反面教材。</t>
-  </si>
-  <si>
-    <t>擁兵四十屯西北，蘑菇戰術化塵埃。</t>
-  </si>
-  <si>
-    <t>張學良</t>
-  </si>
-  <si>
-    <t>散財軍閥</t>
-  </si>
-  <si>
-    <t>丟失東北 / 實體歸零</t>
-  </si>
-  <si>
-    <t>繼承東亞頂級軍工體系與三十萬大軍。九一八事變下達不抵抗命令，將戰略重地與海量軍火拱手讓日，釀成抗戰極端劣勢；西安事變更致使自身軍隊實體遭徹底瓦解，為軍事資源轉化率絕對為零之統帥。</t>
-  </si>
-  <si>
-    <t>瀋陽兵工化劫灰，不發一槍棄重關。</t>
-  </si>
-  <si>
-    <t>傅作義</t>
-  </si>
-  <si>
-    <t>守城飛將</t>
-  </si>
-  <si>
-    <t>防禦大師 / 戰略遲疑</t>
-  </si>
-  <si>
-    <t>涿州孤城抗擊數萬大軍，百靈廟大捷重創日偽，為民國頂級防守反擊大腦。然平津戰役中因欲保全派系實力而戰略猶豫，致使核心主力第 35 軍覆滅，喪失大戰區博弈之最後籌碼。</t>
-  </si>
-  <si>
-    <t>涿州孤城揚威名，百靈廟前鎮胡塵。</t>
-  </si>
-  <si>
-    <t>實幹孤臣</t>
-  </si>
-  <si>
-    <t>保全古都 / 治水總管</t>
-  </si>
-  <si>
-    <t>於北平死局中摒棄愚忠，促成和平解放，實質保全千年古都之文明實體與百萬生靈。建國後任水利部長二十三年，踏遍大江大河推動實體基礎建設，以技術官僚之姿洗刷降將之名。</t>
-  </si>
-  <si>
-    <t>和平一局存燕京，半生戎馬半生水。</t>
-  </si>
-  <si>
-    <t>張作霖</t>
-  </si>
-  <si>
-    <t>東北王</t>
-  </si>
-  <si>
-    <t>軍工實體 / 地緣走鋼索</t>
-  </si>
-  <si>
-    <t>從綠林崛起，於日俄夾縫中締造擁有亞洲頂尖軍工體系與海空軍之奉系霸權。雖戰術思維陳舊敗於北伐，然大是大非前堅拒出賣國家核心主權，於皇姑屯殉身，為舊式軍閥實體建制之巔峰。</t>
-  </si>
-  <si>
-    <t>綠林拔劍起關東，喋血皇姑拒日鋒。</t>
-  </si>
-  <si>
-    <t>閻錫山</t>
-  </si>
-  <si>
-    <t>山西不倒翁</t>
-  </si>
-  <si>
-    <t>實體建軍 / 地緣平衡</t>
-  </si>
-  <si>
-    <t>統治山西三十八年，憑藉表裡山河據險而守。締造太原兵工廠實現軍備自給，於各方勢力中大玩平衡木；然部隊戰術僵化，缺乏外線機動與戰略破局能力，為極致之防禦自保型舊式統帥。</t>
-  </si>
-  <si>
-    <t>據險太原觀虎鬥，表裡山河鑄堅城。</t>
-  </si>
-  <si>
-    <t>模範督軍</t>
-  </si>
-  <si>
-    <t>閉環經濟 / 村本政治</t>
-  </si>
-  <si>
-    <t>於軍閥割據中推行實用主義治理。築窄軌鐵路以自保，建西北實業公司完善輕重工業體系；推行村本政治與六政三事，將山西打造成民國罕見之實體經濟閉環與模範省份。</t>
-  </si>
-  <si>
-    <t>窄軌綿延鎖晉地，實業六政惠三晉。</t>
-  </si>
-  <si>
-    <t>吳佩孚</t>
-  </si>
-  <si>
-    <t>悲情玉帥</t>
-  </si>
-  <si>
-    <t>戰術天才 / 實體虛無</t>
-  </si>
-  <si>
-    <t>直皖與第一次直奉戰爭中展現頂級野戰機動與大兵團指揮，為首位登上《時代》封面之中國軍閥。然極端排斥建立現代工業實體與穩固地緣基本盤；雖晚年拒作漢奸保全民族氣節，但在殘酷之實體絞肉機中，終因缺乏戰略縱深與後勤而全盤覆滅。</t>
-  </si>
-  <si>
-    <t>洛陽虎踞震北洋，空有將才無實疆。</t>
-  </si>
-  <si>
-    <t>陳炯明</t>
-  </si>
-  <si>
-    <t>聯省先驅</t>
-  </si>
-  <si>
-    <t>實體建制 / 廣東大治</t>
-  </si>
-  <si>
-    <t>拒絕武力盲目北伐，推動「聯省自治」。於廣東大舉興辦教育、修築公路、禁絕煙賭並確立現代司法框架，為近現代極具前瞻性之地方實體現代化締造者，惜藍圖遭大一統戰火摧毀。</t>
-  </si>
-  <si>
-    <t>聯省宏圖興百業，羊城舊夢碎干戈。</t>
-  </si>
-  <si>
-    <t>破產軍閥</t>
-  </si>
-  <si>
-    <t>理想碎裂 / 戰略失能</t>
-  </si>
-  <si>
-    <t>早年驅逐桂系統一嶺南。然軍隊組織與戰術思維停滯，於東征戰役中面對具備現代政戰體系之黃埔軍毫無招架之力，喪失根據地，武裝實體遭徹底瓦解，無法為政治理想提供暴力背書。</t>
-  </si>
-  <si>
-    <t>粵海雄兵終化土，空懷壯志恨黃埔。</t>
-  </si>
-  <si>
-    <t>趙括</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -6719,7 +6715,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -6744,13 +6740,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6915,11 +6908,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}" name="王侯將相" displayName="王侯將相" ref="A1:G444" tableType="queryTable" totalsRowShown="0" dataDxfId="7">
-  <autoFilter ref="A1:G444" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G428">
-    <sortCondition ref="A2:A332" customList="帝王,將領,名臣"/>
-    <sortCondition ref="C2:C332" customList="S+,S,S-,A+,A,A-,B+,B,B-,C+,C,C-,D"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}" name="王侯將相" displayName="王侯將相" ref="A1:G443" tableType="queryTable" totalsRowShown="0" dataDxfId="7">
+  <autoFilter ref="A1:G443" xr:uid="{5820D99F-9E72-4217-BE71-A7C4C2D24C05}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G443">
+    <sortCondition ref="A2:A331" customList="帝王,將領,名臣"/>
+    <sortCondition ref="C2:C331" customList="S+,S,S-,A+,A,A-,B+,B,B-,C+,C,C-,D"/>
   </sortState>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{E4DF90F2-4BEE-46BA-8777-551EA3D5648C}" uniqueName="1" name="類型" queryTableFieldId="1" dataDxfId="6"/>
@@ -7231,7 +7224,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0685D331-C227-4B1A-8854-ADE1AFC8F58E}">
-  <dimension ref="A1:G444"/>
+  <dimension ref="A1:G443"/>
   <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.21875" bestFit="1" customWidth="1"/>
@@ -7245,25 +7238,25 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>1600</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E1" t="s">
         <v>1604</v>
       </c>
-      <c r="B1" t="s">
+      <c r="F1" t="s">
         <v>1605</v>
       </c>
-      <c r="C1" t="s">
+      <c r="G1" t="s">
         <v>1606</v>
-      </c>
-      <c r="D1" t="s">
-        <v>1607</v>
-      </c>
-      <c r="E1" t="s">
-        <v>1608</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1609</v>
-      </c>
-      <c r="G1" t="s">
-        <v>1610</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
@@ -7375,7 +7368,7 @@
         <v>25</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1603</v>
+        <v>1599</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>26</v>
@@ -7550,16 +7543,16 @@
         <v>100</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>1721</v>
+        <v>1717</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>101</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>1723</v>
+        <v>1719</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1724</v>
+        <v>1720</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>102</v>
@@ -7570,22 +7563,22 @@
         <v>0</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>1937</v>
+        <v>1933</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>1938</v>
+        <v>1934</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>1939</v>
+        <v>1935</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>1940</v>
+        <v>1936</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>1941</v>
+        <v>1937</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -7596,16 +7589,16 @@
         <v>43</v>
       </c>
       <c r="C16" s="1" t="s">
+        <v>1718</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>1721</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>1722</v>
       </c>
-      <c r="D16" s="1" t="s">
-        <v>1725</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>1726</v>
-      </c>
       <c r="F16" s="1" t="s">
-        <v>1727</v>
+        <v>1723</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>44</v>
@@ -7674,7 +7667,7 @@
         <v>78</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1728</v>
+        <v>1724</v>
       </c>
       <c r="G19" s="1" t="s">
         <v>79</v>
@@ -7892,22 +7885,22 @@
         <v>0</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>1716</v>
+        <v>1712</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>1717</v>
+        <v>1713</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>1718</v>
+        <v>1714</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>1719</v>
+        <v>1715</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>1720</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="30" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -7915,22 +7908,22 @@
         <v>0</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>1803</v>
+        <v>1799</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>1804</v>
+        <v>1800</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>1805</v>
+        <v>1801</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>1806</v>
+        <v>1802</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>1807</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="31" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -7938,22 +7931,22 @@
         <v>0</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>1882</v>
+        <v>1878</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>1883</v>
+        <v>1879</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>1884</v>
+        <v>1880</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>1885</v>
+        <v>1881</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>1886</v>
+        <v>1882</v>
       </c>
     </row>
     <row r="32" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -7961,22 +7954,22 @@
         <v>0</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>1892</v>
+        <v>1888</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>1893</v>
+        <v>1889</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>1894</v>
+        <v>1890</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>1895</v>
+        <v>1891</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>1896</v>
+        <v>1892</v>
       </c>
     </row>
     <row r="33" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -7984,22 +7977,22 @@
         <v>0</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>1942</v>
+        <v>1938</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>1943</v>
+        <v>1939</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>1944</v>
+        <v>1940</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>1945</v>
+        <v>1941</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>1946</v>
+        <v>1942</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -8007,22 +8000,22 @@
         <v>0</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>2049</v>
+        <v>2045</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>2050</v>
+        <v>2046</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>2051</v>
+        <v>2047</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>2052</v>
+        <v>2048</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>2053</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
@@ -8329,22 +8322,22 @@
         <v>0</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>1808</v>
+        <v>1804</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>1809</v>
+        <v>1805</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>1810</v>
+        <v>1806</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>1811</v>
+        <v>1807</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>1812</v>
+        <v>1808</v>
       </c>
     </row>
     <row r="49" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -8352,22 +8345,22 @@
         <v>0</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>1917</v>
+        <v>1913</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>1918</v>
+        <v>1914</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>1919</v>
+        <v>1915</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>1920</v>
+        <v>1916</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>1921</v>
+        <v>1917</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -8375,22 +8368,22 @@
         <v>0</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>1927</v>
+        <v>1923</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>1928</v>
+        <v>1924</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>1929</v>
+        <v>1925</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>1930</v>
+        <v>1926</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>1931</v>
+        <v>1927</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
@@ -8582,22 +8575,22 @@
         <v>0</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>1685</v>
+        <v>1681</v>
       </c>
       <c r="C59" s="5" t="s">
         <v>195</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>1676</v>
+        <v>1672</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>1677</v>
+        <v>1673</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>1678</v>
+        <v>1674</v>
       </c>
       <c r="G59" s="5" t="s">
-        <v>1679</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="60" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -8605,22 +8598,22 @@
         <v>0</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>1701</v>
+        <v>1697</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>1702</v>
+        <v>1698</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>1703</v>
+        <v>1699</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>1704</v>
+        <v>1700</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>1705</v>
+        <v>1701</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -8628,22 +8621,22 @@
         <v>0</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1764</v>
+        <v>1760</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>1766</v>
+        <v>1762</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>1767</v>
+        <v>1763</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>1768</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -8651,22 +8644,22 @@
         <v>0</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>1818</v>
+        <v>1814</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>1819</v>
+        <v>1815</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>1820</v>
+        <v>1816</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>1821</v>
+        <v>1817</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>1822</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -8674,22 +8667,22 @@
         <v>0</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>1907</v>
+        <v>1903</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>1908</v>
+        <v>1904</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>1909</v>
+        <v>1905</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>1910</v>
+        <v>1906</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>1911</v>
+        <v>1907</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -8697,22 +8690,22 @@
         <v>0</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>1922</v>
+        <v>1918</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>1923</v>
+        <v>1919</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>1924</v>
+        <v>1920</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>1925</v>
+        <v>1921</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>1926</v>
+        <v>1922</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -8720,22 +8713,22 @@
         <v>0</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>2008</v>
+        <v>2004</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>2009</v>
+        <v>2005</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>2010</v>
+        <v>2006</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>2011</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -8743,22 +8736,22 @@
         <v>0</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>2059</v>
+        <v>2055</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>2060</v>
+        <v>2056</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>2061</v>
+        <v>2057</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>2062</v>
+        <v>2058</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>2063</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
@@ -9042,22 +9035,22 @@
         <v>0</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>1680</v>
+        <v>1676</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>1681</v>
+        <v>1677</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>1682</v>
+        <v>1678</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>1683</v>
+        <v>1679</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>1684</v>
+        <v>1680</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -9065,22 +9058,22 @@
         <v>0</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>1729</v>
+        <v>1725</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>1730</v>
+        <v>1726</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>1731</v>
+        <v>1727</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>1732</v>
+        <v>1728</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>1733</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="81" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -9088,22 +9081,22 @@
         <v>0</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>1739</v>
+        <v>1735</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>1740</v>
+        <v>1736</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>1741</v>
+        <v>1737</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>1742</v>
+        <v>1738</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>1743</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -9111,22 +9104,22 @@
         <v>0</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>1788</v>
+        <v>1784</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>1789</v>
+        <v>1785</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>1790</v>
+        <v>1786</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>1791</v>
+        <v>1787</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>1792</v>
+        <v>1788</v>
       </c>
     </row>
     <row r="83" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -9134,22 +9127,22 @@
         <v>0</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>1881</v>
+        <v>1877</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>1877</v>
+        <v>1873</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>1878</v>
+        <v>1874</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>1879</v>
+        <v>1875</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>1880</v>
+        <v>1876</v>
       </c>
     </row>
     <row r="84" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -9157,22 +9150,22 @@
         <v>0</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>1912</v>
+        <v>1908</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>1913</v>
+        <v>1909</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>1914</v>
+        <v>1910</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>1915</v>
+        <v>1911</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>1916</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="85" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -9180,22 +9173,22 @@
         <v>0</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>1952</v>
+        <v>1948</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>1953</v>
+        <v>1949</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>1954</v>
+        <v>1950</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>1955</v>
+        <v>1951</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>1956</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="86" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -9203,22 +9196,22 @@
         <v>0</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>1957</v>
+        <v>1953</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>1958</v>
+        <v>1954</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>1959</v>
+        <v>1955</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>1960</v>
+        <v>1956</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>1961</v>
+        <v>1957</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
@@ -9433,22 +9426,22 @@
         <v>0</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>1706</v>
+        <v>1702</v>
       </c>
       <c r="C96" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>1707</v>
+        <v>1703</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>1708</v>
+        <v>1704</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>1709</v>
+        <v>1705</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>1710</v>
+        <v>1706</v>
       </c>
     </row>
     <row r="97" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -9456,22 +9449,22 @@
         <v>0</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>1813</v>
+        <v>1809</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>1814</v>
+        <v>1810</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>1815</v>
+        <v>1811</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>1816</v>
+        <v>1812</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>1817</v>
+        <v>1813</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
@@ -9571,22 +9564,22 @@
         <v>0</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>1887</v>
+        <v>1883</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>343</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>1888</v>
+        <v>1884</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>1889</v>
+        <v>1885</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>1890</v>
+        <v>1886</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>1891</v>
+        <v>1887</v>
       </c>
     </row>
     <row r="103" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -9594,22 +9587,22 @@
         <v>0</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>1932</v>
+        <v>1928</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>343</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>1933</v>
+        <v>1929</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>1934</v>
+        <v>1930</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>1935</v>
+        <v>1931</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>1936</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
@@ -9801,22 +9794,22 @@
         <v>0</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>1664</v>
+        <v>1660</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>364</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>1665</v>
+        <v>1661</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>1666</v>
+        <v>1662</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>1667</v>
+        <v>1663</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>1668</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="113" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -9824,22 +9817,22 @@
         <v>0</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>364</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>1848</v>
+        <v>1844</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>1849</v>
+        <v>1845</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>1850</v>
+        <v>1846</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>1851</v>
+        <v>1847</v>
       </c>
     </row>
     <row r="114" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -9847,22 +9840,22 @@
         <v>0</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>1862</v>
+        <v>1858</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>364</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>1863</v>
+        <v>1859</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>1864</v>
+        <v>1860</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>1865</v>
+        <v>1861</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>1866</v>
+        <v>1862</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
@@ -10031,22 +10024,22 @@
         <v>0</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>1691</v>
+        <v>1687</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>405</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>1692</v>
+        <v>1688</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>1693</v>
+        <v>1689</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>1694</v>
+        <v>1690</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>1695</v>
+        <v>1691</v>
       </c>
     </row>
     <row r="123" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -10054,22 +10047,22 @@
         <v>0</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>1779</v>
+        <v>1775</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>405</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>1780</v>
+        <v>1776</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>1782</v>
+        <v>1778</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>1783</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="124" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -10077,22 +10070,22 @@
         <v>0</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>1897</v>
+        <v>1893</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>405</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>1898</v>
+        <v>1894</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>1899</v>
+        <v>1895</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>1900</v>
+        <v>1896</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>1901</v>
+        <v>1897</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.3">
@@ -10215,22 +10208,22 @@
         <v>0</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>1711</v>
+        <v>1707</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>441</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>1712</v>
+        <v>1708</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>1713</v>
+        <v>1709</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>1714</v>
+        <v>1710</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>1715</v>
+        <v>1711</v>
       </c>
     </row>
     <row r="131" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -10238,22 +10231,22 @@
         <v>0</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>1837</v>
+        <v>1833</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>441</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>1838</v>
+        <v>1834</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>1839</v>
+        <v>1835</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>1840</v>
+        <v>1836</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
     </row>
     <row r="132" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -10261,22 +10254,22 @@
         <v>0</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>1902</v>
+        <v>1898</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>441</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>1903</v>
+        <v>1899</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>1904</v>
+        <v>1900</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>1905</v>
+        <v>1901</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>1906</v>
+        <v>1902</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.3">
@@ -10307,22 +10300,22 @@
         <v>0</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>467</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="135" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -10330,22 +10323,22 @@
         <v>0</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>1867</v>
+        <v>1863</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>467</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>1868</v>
+        <v>1864</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>1869</v>
+        <v>1865</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>1870</v>
+        <v>1866</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>1871</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.3">
@@ -11756,22 +11749,22 @@
         <v>472</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>1734</v>
+        <v>1730</v>
       </c>
       <c r="C197" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>1735</v>
+        <v>1731</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>1736</v>
+        <v>1732</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>1737</v>
+        <v>1733</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>1738</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="198" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -11779,22 +11772,22 @@
         <v>472</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>1992</v>
+        <v>1988</v>
       </c>
       <c r="C198" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>1993</v>
+        <v>1989</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>1994</v>
+        <v>1990</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>1995</v>
+        <v>1991</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>1996</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="199" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -11802,22 +11795,22 @@
         <v>472</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="C199" s="2" t="s">
         <v>66</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>2071</v>
+        <v>2067</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>2072</v>
+        <v>2068</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>2073</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="200" spans="1:7" x14ac:dyDescent="0.3">
@@ -12170,22 +12163,22 @@
         <v>472</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>1659</v>
+        <v>1655</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>1660</v>
+        <v>1656</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>1661</v>
+        <v>1657</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>1662</v>
+        <v>1658</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>1663</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="216" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -12193,7 +12186,7 @@
         <v>472</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>129</v>
@@ -12202,13 +12195,13 @@
         <v>431</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>1787</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="217" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -12216,22 +12209,22 @@
         <v>472</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>1972</v>
+        <v>1968</v>
       </c>
       <c r="C217" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>1974</v>
+        <v>1970</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>1975</v>
+        <v>1971</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>1976</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="218" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -12239,22 +12232,22 @@
         <v>472</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>129</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>1998</v>
+        <v>1994</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>1999</v>
+        <v>1995</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>2000</v>
+        <v>1996</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>2001</v>
+        <v>1997</v>
       </c>
     </row>
     <row r="219" spans="1:7" x14ac:dyDescent="0.3">
@@ -12791,22 +12784,22 @@
         <v>472</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>1620</v>
+        <v>1616</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>1621</v>
+        <v>1617</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>1622</v>
+        <v>1618</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>1623</v>
+        <v>1619</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>1624</v>
+        <v>1620</v>
       </c>
     </row>
     <row r="243" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -12814,22 +12807,22 @@
         <v>472</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>1640</v>
+        <v>1636</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>1641</v>
+        <v>1637</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>1642</v>
+        <v>1638</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>1643</v>
+        <v>1639</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>1644</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="244" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -12837,22 +12830,22 @@
         <v>472</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>1759</v>
+        <v>1755</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>1761</v>
+        <v>1757</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>1762</v>
+        <v>1758</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>1763</v>
+        <v>1759</v>
       </c>
     </row>
     <row r="245" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -12860,22 +12853,22 @@
         <v>472</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>1947</v>
+        <v>1943</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>1948</v>
+        <v>1944</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>1949</v>
+        <v>1945</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>1950</v>
+        <v>1946</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>1951</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="246" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -12883,22 +12876,22 @@
         <v>472</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>2002</v>
+        <v>1998</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>2003</v>
+        <v>1999</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>2004</v>
+        <v>2000</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>2005</v>
+        <v>2001</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>2006</v>
+        <v>2002</v>
       </c>
     </row>
     <row r="247" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -12906,22 +12899,22 @@
         <v>472</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>2085</v>
+        <v>2081</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>2086</v>
+        <v>2082</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>2088</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="248" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -12929,91 +12922,91 @@
         <v>472</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>2094</v>
+        <v>2090</v>
       </c>
       <c r="C248" s="2" t="s">
         <v>195</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>2095</v>
+        <v>2091</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>2096</v>
+        <v>2092</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>2097</v>
+        <v>2093</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>2098</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="249" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A249" s="8" t="s">
-        <v>472</v>
-      </c>
-      <c r="B249" s="8" t="s">
+      <c r="A249" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>2100</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>2101</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>2102</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>2103</v>
+      </c>
+      <c r="G249" s="2" t="s">
         <v>2104</v>
       </c>
-      <c r="C249" s="8" t="s">
+    </row>
+    <row r="250" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A250" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B250" s="9" t="s">
+        <v>2113</v>
+      </c>
+      <c r="C250" s="9" t="s">
         <v>195</v>
       </c>
-      <c r="D249" s="8" t="s">
-        <v>2105</v>
-      </c>
-      <c r="E249" s="8" t="s">
-        <v>2106</v>
-      </c>
-      <c r="F249" s="8" t="s">
-        <v>2107</v>
-      </c>
-      <c r="G249" s="8" t="s">
-        <v>2108</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A250" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B250" s="1" t="s">
-        <v>945</v>
-      </c>
-      <c r="C250" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D250" s="1" t="s">
-        <v>946</v>
-      </c>
-      <c r="E250" s="1" t="s">
-        <v>947</v>
-      </c>
-      <c r="F250" s="1" t="s">
-        <v>948</v>
-      </c>
-      <c r="G250" s="1" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A251" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B251" s="1" t="s">
-        <v>950</v>
-      </c>
-      <c r="C251" s="1" t="s">
-        <v>236</v>
-      </c>
-      <c r="D251" s="1" t="s">
-        <v>951</v>
-      </c>
-      <c r="E251" s="1" t="s">
-        <v>952</v>
-      </c>
-      <c r="F251" s="1" t="s">
-        <v>953</v>
-      </c>
-      <c r="G251" s="1" t="s">
-        <v>954</v>
+      <c r="D250" s="9" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E250" s="9" t="s">
+        <v>2115</v>
+      </c>
+      <c r="F250" s="9" t="s">
+        <v>2116</v>
+      </c>
+      <c r="G250" s="9" t="s">
+        <v>2117</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A251" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B251" s="9" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C251" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D251" s="9" t="s">
+        <v>2137</v>
+      </c>
+      <c r="E251" s="9" t="s">
+        <v>2138</v>
+      </c>
+      <c r="F251" s="9" t="s">
+        <v>2139</v>
+      </c>
+      <c r="G251" s="9" t="s">
+        <v>2140</v>
       </c>
     </row>
     <row r="252" spans="1:7" x14ac:dyDescent="0.3">
@@ -13021,22 +13014,22 @@
         <v>472</v>
       </c>
       <c r="B252" s="1" t="s">
-        <v>955</v>
+        <v>945</v>
       </c>
       <c r="C252" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>956</v>
+        <v>946</v>
       </c>
       <c r="E252" s="1" t="s">
-        <v>957</v>
+        <v>947</v>
       </c>
       <c r="F252" s="1" t="s">
-        <v>958</v>
+        <v>948</v>
       </c>
       <c r="G252" s="1" t="s">
-        <v>959</v>
+        <v>949</v>
       </c>
     </row>
     <row r="253" spans="1:7" x14ac:dyDescent="0.3">
@@ -13044,22 +13037,22 @@
         <v>472</v>
       </c>
       <c r="B253" s="1" t="s">
-        <v>960</v>
+        <v>950</v>
       </c>
       <c r="C253" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>961</v>
+        <v>951</v>
       </c>
       <c r="E253" s="1" t="s">
-        <v>962</v>
+        <v>952</v>
       </c>
       <c r="F253" s="1" t="s">
-        <v>963</v>
+        <v>953</v>
       </c>
       <c r="G253" s="1" t="s">
-        <v>964</v>
+        <v>954</v>
       </c>
     </row>
     <row r="254" spans="1:7" x14ac:dyDescent="0.3">
@@ -13067,22 +13060,22 @@
         <v>472</v>
       </c>
       <c r="B254" s="1" t="s">
-        <v>965</v>
+        <v>955</v>
       </c>
       <c r="C254" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>966</v>
+        <v>956</v>
       </c>
       <c r="E254" s="1" t="s">
-        <v>967</v>
+        <v>957</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>968</v>
+        <v>958</v>
       </c>
       <c r="G254" s="1" t="s">
-        <v>969</v>
+        <v>959</v>
       </c>
     </row>
     <row r="255" spans="1:7" x14ac:dyDescent="0.3">
@@ -13090,22 +13083,22 @@
         <v>472</v>
       </c>
       <c r="B255" s="1" t="s">
-        <v>970</v>
+        <v>960</v>
       </c>
       <c r="C255" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>971</v>
+        <v>961</v>
       </c>
       <c r="E255" s="1" t="s">
-        <v>972</v>
+        <v>962</v>
       </c>
       <c r="F255" s="1" t="s">
-        <v>973</v>
+        <v>963</v>
       </c>
       <c r="G255" s="1" t="s">
-        <v>974</v>
+        <v>964</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.3">
@@ -13113,22 +13106,22 @@
         <v>472</v>
       </c>
       <c r="B256" s="1" t="s">
-        <v>975</v>
+        <v>965</v>
       </c>
       <c r="C256" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D256" s="1" t="s">
-        <v>976</v>
+        <v>966</v>
       </c>
       <c r="E256" s="1" t="s">
-        <v>977</v>
+        <v>967</v>
       </c>
       <c r="F256" s="1" t="s">
-        <v>978</v>
+        <v>968</v>
       </c>
       <c r="G256" s="1" t="s">
-        <v>979</v>
+        <v>969</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.3">
@@ -13136,22 +13129,22 @@
         <v>472</v>
       </c>
       <c r="B257" s="1" t="s">
-        <v>980</v>
+        <v>970</v>
       </c>
       <c r="C257" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D257" s="1" t="s">
-        <v>841</v>
+        <v>971</v>
       </c>
       <c r="E257" s="1" t="s">
-        <v>981</v>
+        <v>972</v>
       </c>
       <c r="F257" s="1" t="s">
-        <v>982</v>
+        <v>973</v>
       </c>
       <c r="G257" s="1" t="s">
-        <v>983</v>
+        <v>974</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.3">
@@ -13159,22 +13152,22 @@
         <v>472</v>
       </c>
       <c r="B258" s="1" t="s">
-        <v>984</v>
+        <v>975</v>
       </c>
       <c r="C258" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>985</v>
+        <v>976</v>
       </c>
       <c r="E258" s="1" t="s">
-        <v>986</v>
+        <v>977</v>
       </c>
       <c r="F258" s="1" t="s">
-        <v>987</v>
+        <v>978</v>
       </c>
       <c r="G258" s="1" t="s">
-        <v>988</v>
+        <v>979</v>
       </c>
     </row>
     <row r="259" spans="1:7" x14ac:dyDescent="0.3">
@@ -13182,22 +13175,22 @@
         <v>472</v>
       </c>
       <c r="B259" s="1" t="s">
-        <v>989</v>
+        <v>980</v>
       </c>
       <c r="C259" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D259" s="1" t="s">
-        <v>990</v>
+        <v>841</v>
       </c>
       <c r="E259" s="1" t="s">
-        <v>991</v>
+        <v>981</v>
       </c>
       <c r="F259" s="1" t="s">
-        <v>992</v>
+        <v>982</v>
       </c>
       <c r="G259" s="1" t="s">
-        <v>993</v>
+        <v>983</v>
       </c>
     </row>
     <row r="260" spans="1:7" x14ac:dyDescent="0.3">
@@ -13205,22 +13198,22 @@
         <v>472</v>
       </c>
       <c r="B260" s="1" t="s">
-        <v>994</v>
+        <v>984</v>
       </c>
       <c r="C260" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>995</v>
+        <v>985</v>
       </c>
       <c r="E260" s="1" t="s">
-        <v>996</v>
+        <v>986</v>
       </c>
       <c r="F260" s="1" t="s">
-        <v>997</v>
+        <v>987</v>
       </c>
       <c r="G260" s="1" t="s">
-        <v>998</v>
+        <v>988</v>
       </c>
     </row>
     <row r="261" spans="1:7" x14ac:dyDescent="0.3">
@@ -13228,22 +13221,22 @@
         <v>472</v>
       </c>
       <c r="B261" s="1" t="s">
-        <v>999</v>
+        <v>989</v>
       </c>
       <c r="C261" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="E261" s="1" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
       <c r="F261" s="1" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
       <c r="G261" s="1" t="s">
-        <v>1003</v>
+        <v>993</v>
       </c>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.3">
@@ -13251,22 +13244,22 @@
         <v>472</v>
       </c>
       <c r="B262" s="1" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="C262" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
       <c r="E262" s="1" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
       <c r="F262" s="1" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
       <c r="G262" s="1" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
     </row>
     <row r="263" spans="1:7" x14ac:dyDescent="0.3">
@@ -13274,22 +13267,22 @@
         <v>472</v>
       </c>
       <c r="B263" s="1" t="s">
-        <v>242</v>
+        <v>999</v>
       </c>
       <c r="C263" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>1009</v>
+        <v>1000</v>
       </c>
       <c r="E263" s="1" t="s">
-        <v>1010</v>
+        <v>1001</v>
       </c>
       <c r="F263" s="1" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="G263" s="1" t="s">
-        <v>245</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.3">
@@ -13297,22 +13290,22 @@
         <v>472</v>
       </c>
       <c r="B264" s="1" t="s">
-        <v>1012</v>
+        <v>1004</v>
       </c>
       <c r="C264" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D264" s="1" t="s">
-        <v>1013</v>
+        <v>1005</v>
       </c>
       <c r="E264" s="1" t="s">
-        <v>1014</v>
+        <v>1006</v>
       </c>
       <c r="F264" s="1" t="s">
-        <v>1015</v>
+        <v>1007</v>
       </c>
       <c r="G264" s="1" t="s">
-        <v>1016</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="265" spans="1:7" x14ac:dyDescent="0.3">
@@ -13320,22 +13313,22 @@
         <v>472</v>
       </c>
       <c r="B265" s="1" t="s">
-        <v>1017</v>
+        <v>242</v>
       </c>
       <c r="C265" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
       <c r="E265" s="1" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="F265" s="1" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="G265" s="1" t="s">
-        <v>1021</v>
+        <v>245</v>
       </c>
     </row>
     <row r="266" spans="1:7" x14ac:dyDescent="0.3">
@@ -13343,22 +13336,22 @@
         <v>472</v>
       </c>
       <c r="B266" s="1" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
       <c r="C266" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="E266" s="1" t="s">
-        <v>1024</v>
+        <v>1014</v>
       </c>
       <c r="F266" s="1" t="s">
-        <v>1025</v>
+        <v>1015</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>1026</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="267" spans="1:7" x14ac:dyDescent="0.3">
@@ -13366,22 +13359,22 @@
         <v>472</v>
       </c>
       <c r="B267" s="1" t="s">
-        <v>1027</v>
+        <v>1017</v>
       </c>
       <c r="C267" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>1028</v>
+        <v>1018</v>
       </c>
       <c r="E267" s="1" t="s">
-        <v>1029</v>
+        <v>1019</v>
       </c>
       <c r="F267" s="1" t="s">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="G267" s="1" t="s">
-        <v>1031</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="268" spans="1:7" x14ac:dyDescent="0.3">
@@ -13389,22 +13382,22 @@
         <v>472</v>
       </c>
       <c r="B268" s="1" t="s">
-        <v>1032</v>
+        <v>1022</v>
       </c>
       <c r="C268" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D268" s="1" t="s">
-        <v>1033</v>
+        <v>1023</v>
       </c>
       <c r="E268" s="1" t="s">
-        <v>1034</v>
+        <v>1024</v>
       </c>
       <c r="F268" s="1" t="s">
-        <v>1035</v>
+        <v>1025</v>
       </c>
       <c r="G268" s="1" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="269" spans="1:7" x14ac:dyDescent="0.3">
@@ -13412,22 +13405,22 @@
         <v>472</v>
       </c>
       <c r="B269" s="1" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="C269" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>1038</v>
+        <v>1028</v>
       </c>
       <c r="E269" s="1" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="F269" s="1" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
       <c r="G269" s="1" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="270" spans="1:7" x14ac:dyDescent="0.3">
@@ -13435,22 +13428,22 @@
         <v>472</v>
       </c>
       <c r="B270" s="1" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
       <c r="C270" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D270" s="1" t="s">
-        <v>1043</v>
+        <v>1033</v>
       </c>
       <c r="E270" s="1" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
       <c r="F270" s="1" t="s">
-        <v>1045</v>
+        <v>1035</v>
       </c>
       <c r="G270" s="1" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="271" spans="1:7" x14ac:dyDescent="0.3">
@@ -13458,22 +13451,22 @@
         <v>472</v>
       </c>
       <c r="B271" s="1" t="s">
-        <v>1047</v>
+        <v>1037</v>
       </c>
       <c r="C271" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D271" s="1" t="s">
-        <v>1048</v>
+        <v>1038</v>
       </c>
       <c r="E271" s="1" t="s">
-        <v>1049</v>
+        <v>1039</v>
       </c>
       <c r="F271" s="1" t="s">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="G271" s="1" t="s">
-        <v>1051</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="272" spans="1:7" x14ac:dyDescent="0.3">
@@ -13481,91 +13474,91 @@
         <v>472</v>
       </c>
       <c r="B272" s="1" t="s">
-        <v>1052</v>
+        <v>1042</v>
       </c>
       <c r="C272" s="1" t="s">
         <v>236</v>
       </c>
       <c r="D272" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E272" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F272" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="G272" s="1" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A273" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B273" s="1" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C273" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D273" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="E273" s="1" t="s">
+        <v>1049</v>
+      </c>
+      <c r="F273" s="1" t="s">
+        <v>1050</v>
+      </c>
+      <c r="G273" s="1" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A274" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B274" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C274" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D274" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="E272" s="1" t="s">
+      <c r="E274" s="1" t="s">
         <v>1054</v>
       </c>
-      <c r="F272" s="1" t="s">
+      <c r="F274" s="1" t="s">
         <v>1055</v>
       </c>
-      <c r="G272" s="1" t="s">
+      <c r="G274" s="1" t="s">
         <v>1056</v>
       </c>
     </row>
-    <row r="273" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A273" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>1616</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D273" s="2" t="s">
-        <v>1617</v>
-      </c>
-      <c r="E273" s="2" t="s">
-        <v>1618</v>
-      </c>
-      <c r="F273" s="2" t="s">
-        <v>1619</v>
-      </c>
-      <c r="G273" s="2" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A274" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>1630</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="D274" s="2" t="s">
-        <v>1631</v>
-      </c>
-      <c r="E274" s="2" t="s">
-        <v>1632</v>
-      </c>
-      <c r="F274" s="2" t="s">
-        <v>1633</v>
-      </c>
-      <c r="G274" s="2" t="s">
-        <v>1634</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A275" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>1649</v>
+        <v>1612</v>
       </c>
       <c r="C275" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>1650</v>
+        <v>1613</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>1651</v>
+        <v>1614</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>1652</v>
+        <v>1615</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>1653</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="276" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13573,22 +13566,22 @@
         <v>472</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>1654</v>
+        <v>1626</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>1655</v>
+        <v>1627</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>1656</v>
+        <v>1628</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>1657</v>
+        <v>1629</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>1658</v>
+        <v>1630</v>
       </c>
     </row>
     <row r="277" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
@@ -13596,22 +13589,22 @@
         <v>472</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>1967</v>
+        <v>1645</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>1968</v>
+        <v>1646</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>1969</v>
+        <v>1647</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>1970</v>
+        <v>1648</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>1971</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="278" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13619,45 +13612,45 @@
         <v>472</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>1977</v>
+        <v>1650</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>1978</v>
+        <v>1651</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>1979</v>
+        <v>1652</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>1980</v>
+        <v>1653</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>1981</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A279" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>2089</v>
+        <v>1963</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>2090</v>
+        <v>1964</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>2091</v>
+        <v>1965</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>2092</v>
+        <v>1966</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>2093</v>
+        <v>1967</v>
       </c>
     </row>
     <row r="280" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
@@ -13665,137 +13658,137 @@
         <v>472</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>2099</v>
+        <v>1973</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>236</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>2100</v>
+        <v>1974</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>2101</v>
+        <v>1975</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>2102</v>
+        <v>1976</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A281" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B281" s="1" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C281" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D281" s="1" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E281" s="1" t="s">
-        <v>1059</v>
-      </c>
-      <c r="F281" s="1" t="s">
-        <v>1060</v>
-      </c>
-      <c r="G281" s="1" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A282" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B282" s="1" t="s">
-        <v>1062</v>
-      </c>
-      <c r="C282" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D282" s="1" t="s">
-        <v>1063</v>
-      </c>
-      <c r="E282" s="1" t="s">
-        <v>1064</v>
-      </c>
-      <c r="F282" s="1" t="s">
-        <v>1065</v>
-      </c>
-      <c r="G282" s="1" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A283" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B283" s="1" t="s">
-        <v>1067</v>
-      </c>
-      <c r="C283" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D283" s="1" t="s">
-        <v>1068</v>
-      </c>
-      <c r="E283" s="1" t="s">
-        <v>1069</v>
-      </c>
-      <c r="F283" s="1" t="s">
-        <v>1070</v>
-      </c>
-      <c r="G283" s="1" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A284" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B284" s="1" t="s">
-        <v>1072</v>
-      </c>
-      <c r="C284" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D284" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="E284" s="1" t="s">
-        <v>1074</v>
-      </c>
-      <c r="F284" s="1" t="s">
-        <v>1075</v>
-      </c>
-      <c r="G284" s="1" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A285" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B285" s="1" t="s">
-        <v>1077</v>
-      </c>
-      <c r="C285" s="1" t="s">
-        <v>297</v>
-      </c>
-      <c r="D285" s="1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="E285" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F285" s="1" t="s">
-        <v>1080</v>
-      </c>
-      <c r="G285" s="1" t="s">
-        <v>1081</v>
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A281" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B281" s="2" t="s">
+        <v>2085</v>
+      </c>
+      <c r="C281" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>2088</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A282" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B282" s="2" t="s">
+        <v>2095</v>
+      </c>
+      <c r="C282" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>2096</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>2097</v>
+      </c>
+      <c r="F282" s="2" t="s">
+        <v>2098</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>2099</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A283" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B283" s="9" t="s">
+        <v>2118</v>
+      </c>
+      <c r="C283" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D283" s="9" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E283" s="9" t="s">
+        <v>2119</v>
+      </c>
+      <c r="F283" s="9" t="s">
+        <v>2120</v>
+      </c>
+      <c r="G283" s="9" t="s">
+        <v>2121</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A284" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B284" s="9" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C284" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D284" s="9" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E284" s="9" t="s">
+        <v>2147</v>
+      </c>
+      <c r="F284" s="9" t="s">
+        <v>2148</v>
+      </c>
+      <c r="G284" s="9" t="s">
+        <v>2149</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A285" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B285" s="9" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C285" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="D285" s="9" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E285" s="9" t="s">
+        <v>2152</v>
+      </c>
+      <c r="F285" s="9" t="s">
+        <v>2153</v>
+      </c>
+      <c r="G285" s="9" t="s">
+        <v>2154</v>
       </c>
     </row>
     <row r="286" spans="1:7" x14ac:dyDescent="0.3">
@@ -13803,22 +13796,22 @@
         <v>472</v>
       </c>
       <c r="B286" s="1" t="s">
-        <v>1082</v>
+        <v>1057</v>
       </c>
       <c r="C286" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D286" s="1" t="s">
-        <v>1083</v>
+        <v>1058</v>
       </c>
       <c r="E286" s="1" t="s">
-        <v>1084</v>
+        <v>1059</v>
       </c>
       <c r="F286" s="1" t="s">
-        <v>1085</v>
+        <v>1060</v>
       </c>
       <c r="G286" s="1" t="s">
-        <v>1086</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="287" spans="1:7" x14ac:dyDescent="0.3">
@@ -13826,22 +13819,22 @@
         <v>472</v>
       </c>
       <c r="B287" s="1" t="s">
-        <v>1087</v>
+        <v>1062</v>
       </c>
       <c r="C287" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>1088</v>
+        <v>1063</v>
       </c>
       <c r="E287" s="1" t="s">
-        <v>1089</v>
+        <v>1064</v>
       </c>
       <c r="F287" s="1" t="s">
-        <v>1090</v>
+        <v>1065</v>
       </c>
       <c r="G287" s="1" t="s">
-        <v>1091</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="288" spans="1:7" x14ac:dyDescent="0.3">
@@ -13849,22 +13842,22 @@
         <v>472</v>
       </c>
       <c r="B288" s="1" t="s">
-        <v>1092</v>
+        <v>1067</v>
       </c>
       <c r="C288" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>1093</v>
+        <v>1068</v>
       </c>
       <c r="E288" s="1" t="s">
-        <v>1094</v>
+        <v>1069</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>1095</v>
+        <v>1070</v>
       </c>
       <c r="G288" s="1" t="s">
-        <v>1096</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="289" spans="1:7" x14ac:dyDescent="0.3">
@@ -13872,22 +13865,22 @@
         <v>472</v>
       </c>
       <c r="B289" s="1" t="s">
-        <v>1097</v>
+        <v>1072</v>
       </c>
       <c r="C289" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>1098</v>
+        <v>1073</v>
       </c>
       <c r="E289" s="1" t="s">
-        <v>1099</v>
+        <v>1074</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>1100</v>
+        <v>1075</v>
       </c>
       <c r="G289" s="1" t="s">
-        <v>1101</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="290" spans="1:7" x14ac:dyDescent="0.3">
@@ -13895,114 +13888,114 @@
         <v>472</v>
       </c>
       <c r="B290" s="1" t="s">
-        <v>1102</v>
+        <v>1077</v>
       </c>
       <c r="C290" s="1" t="s">
         <v>297</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>1103</v>
+        <v>1078</v>
       </c>
       <c r="E290" s="1" t="s">
-        <v>1104</v>
+        <v>1079</v>
       </c>
       <c r="F290" s="1" t="s">
-        <v>1105</v>
+        <v>1080</v>
       </c>
       <c r="G290" s="1" t="s">
-        <v>1106</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A291" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B291" s="2" t="s">
-        <v>1611</v>
-      </c>
-      <c r="C291" s="2" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="291" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A291" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B291" s="1" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C291" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D291" s="2" t="s">
-        <v>1612</v>
-      </c>
-      <c r="E291" s="2" t="s">
-        <v>1613</v>
-      </c>
-      <c r="F291" s="2" t="s">
-        <v>1614</v>
-      </c>
-      <c r="G291" s="2" t="s">
-        <v>1615</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A292" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B292" s="2" t="s">
-        <v>1675</v>
-      </c>
-      <c r="C292" s="2" t="s">
+      <c r="D291" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="E291" s="1" t="s">
+        <v>1084</v>
+      </c>
+      <c r="F291" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A292" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B292" s="1" t="s">
+        <v>1087</v>
+      </c>
+      <c r="C292" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D292" s="2" t="s">
-        <v>1645</v>
-      </c>
-      <c r="E292" s="2" t="s">
-        <v>1646</v>
-      </c>
-      <c r="F292" s="2" t="s">
-        <v>1647</v>
-      </c>
-      <c r="G292" s="2" t="s">
-        <v>1648</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A293" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>1982</v>
-      </c>
-      <c r="C293" s="2" t="s">
+      <c r="D292" s="1" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E292" s="1" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F292" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G292" s="1" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A293" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B293" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C293" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D293" s="2" t="s">
-        <v>1983</v>
-      </c>
-      <c r="E293" s="2" t="s">
-        <v>1984</v>
-      </c>
-      <c r="F293" s="2" t="s">
-        <v>1985</v>
-      </c>
-      <c r="G293" s="2" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A294" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B294" s="2" t="s">
-        <v>1987</v>
-      </c>
-      <c r="C294" s="2" t="s">
+      <c r="D293" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E293" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F293" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G293" s="1" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="294" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A294" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B294" s="1" t="s">
+        <v>1097</v>
+      </c>
+      <c r="C294" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="D294" s="2" t="s">
-        <v>1988</v>
-      </c>
-      <c r="E294" s="2" t="s">
-        <v>1989</v>
-      </c>
-      <c r="F294" s="2" t="s">
-        <v>1990</v>
-      </c>
-      <c r="G294" s="2" t="s">
-        <v>1991</v>
+      <c r="D294" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E294" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F294" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G294" s="1" t="s">
+        <v>1101</v>
       </c>
     </row>
     <row r="295" spans="1:7" x14ac:dyDescent="0.3">
@@ -14010,183 +14003,183 @@
         <v>472</v>
       </c>
       <c r="B295" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C295" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="D295" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="E295" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F295" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G295" s="1" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A296" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F296" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A297" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="F297" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="G297" s="2" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="298" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A298" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F298" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G298" s="2" t="s">
+        <v>1982</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A299" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F299" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="G299" s="2" t="s">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="300" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A300" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B300" s="9" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C300" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="D300" s="9" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E300" s="9" t="s">
+        <v>2161</v>
+      </c>
+      <c r="F300" s="9" t="s">
+        <v>2162</v>
+      </c>
+      <c r="G300" s="9" t="s">
+        <v>2163</v>
+      </c>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A301" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="B301" s="1" t="s">
         <v>1107</v>
       </c>
-      <c r="C295" s="1" t="s">
+      <c r="C301" s="1" t="s">
         <v>343</v>
       </c>
-      <c r="D295" s="1" t="s">
+      <c r="D301" s="1" t="s">
         <v>1108</v>
       </c>
-      <c r="E295" s="1" t="s">
+      <c r="E301" s="1" t="s">
         <v>1109</v>
       </c>
-      <c r="F295" s="1" t="s">
+      <c r="F301" s="1" t="s">
         <v>1110</v>
       </c>
-      <c r="G295" s="1" t="s">
+      <c r="G301" s="1" t="s">
         <v>1111</v>
       </c>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A296" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B296" s="1" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C296" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D296" s="1" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E296" s="1" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F296" s="1" t="s">
-        <v>1115</v>
-      </c>
-      <c r="G296" s="1" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A297" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B297" s="1" t="s">
-        <v>1117</v>
-      </c>
-      <c r="C297" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D297" s="1" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E297" s="1" t="s">
-        <v>1119</v>
-      </c>
-      <c r="F297" s="1" t="s">
-        <v>1120</v>
-      </c>
-      <c r="G297" s="1" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A298" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B298" s="1" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C298" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D298" s="1" t="s">
-        <v>1123</v>
-      </c>
-      <c r="E298" s="1" t="s">
-        <v>1124</v>
-      </c>
-      <c r="F298" s="1" t="s">
-        <v>1125</v>
-      </c>
-      <c r="G298" s="1" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A299" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B299" s="1" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C299" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="D299" s="1" t="s">
-        <v>1128</v>
-      </c>
-      <c r="E299" s="1" t="s">
-        <v>1129</v>
-      </c>
-      <c r="F299" s="1" t="s">
-        <v>1130</v>
-      </c>
-      <c r="G299" s="1" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A300" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>1635</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D300" s="2" t="s">
-        <v>1636</v>
-      </c>
-      <c r="E300" s="2" t="s">
-        <v>1637</v>
-      </c>
-      <c r="F300" s="2" t="s">
-        <v>1638</v>
-      </c>
-      <c r="G300" s="2" t="s">
-        <v>1639</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A301" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>2079</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="D301" s="2" t="s">
-        <v>2080</v>
-      </c>
-      <c r="E301" s="2" t="s">
-        <v>2081</v>
-      </c>
-      <c r="F301" s="2" t="s">
-        <v>2082</v>
-      </c>
-      <c r="G301" s="2" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A302" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="B302" s="1" t="s">
-        <v>1132</v>
-      </c>
-      <c r="C302" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>1133</v>
-      </c>
-      <c r="E302" s="1" t="s">
-        <v>1134</v>
-      </c>
-      <c r="F302" s="1" t="s">
-        <v>1135</v>
-      </c>
-      <c r="G302" s="1" t="s">
-        <v>1136</v>
+    <row r="302" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A302" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B302" s="9" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C302" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="D302" s="9" t="s">
+        <v>2175</v>
+      </c>
+      <c r="E302" s="9" t="s">
+        <v>2176</v>
+      </c>
+      <c r="F302" s="9" t="s">
+        <v>2177</v>
+      </c>
+      <c r="G302" s="9" t="s">
+        <v>2178</v>
       </c>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.3">
@@ -14194,22 +14187,22 @@
         <v>472</v>
       </c>
       <c r="B303" s="1" t="s">
-        <v>1137</v>
+        <v>1112</v>
       </c>
       <c r="C303" s="1" t="s">
-        <v>405</v>
+        <v>364</v>
       </c>
       <c r="D303" s="1" t="s">
-        <v>1138</v>
+        <v>1113</v>
       </c>
       <c r="E303" s="1" t="s">
-        <v>1139</v>
+        <v>1114</v>
       </c>
       <c r="F303" s="1" t="s">
-        <v>1140</v>
+        <v>1115</v>
       </c>
       <c r="G303" s="1" t="s">
-        <v>1141</v>
+        <v>1116</v>
       </c>
     </row>
     <row r="304" spans="1:7" x14ac:dyDescent="0.3">
@@ -14217,22 +14210,22 @@
         <v>472</v>
       </c>
       <c r="B304" s="1" t="s">
-        <v>1142</v>
+        <v>1117</v>
       </c>
       <c r="C304" s="1" t="s">
-        <v>441</v>
+        <v>364</v>
       </c>
       <c r="D304" s="1" t="s">
-        <v>1143</v>
+        <v>1118</v>
       </c>
       <c r="E304" s="1" t="s">
-        <v>1144</v>
+        <v>1119</v>
       </c>
       <c r="F304" s="1" t="s">
-        <v>1145</v>
+        <v>1120</v>
       </c>
       <c r="G304" s="1" t="s">
-        <v>1146</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.3">
@@ -14240,3219 +14233,3196 @@
         <v>472</v>
       </c>
       <c r="B305" s="1" t="s">
-        <v>1147</v>
+        <v>1123</v>
       </c>
       <c r="C305" s="1" t="s">
-        <v>441</v>
+        <v>364</v>
       </c>
       <c r="D305" s="1" t="s">
-        <v>1148</v>
+        <v>1124</v>
       </c>
       <c r="E305" s="1" t="s">
-        <v>1149</v>
+        <v>1125</v>
       </c>
       <c r="F305" s="1" t="s">
-        <v>1150</v>
+        <v>1126</v>
       </c>
       <c r="G305" s="1" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A306" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B306" s="1" t="s">
-        <v>1153</v>
-      </c>
-      <c r="C306" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>1154</v>
-      </c>
-      <c r="E306" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="F306" s="1" t="s">
-        <v>1156</v>
-      </c>
-      <c r="G306" s="1" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A307" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B307" s="1" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C307" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="E307" s="1" t="s">
-        <v>1160</v>
-      </c>
-      <c r="F307" s="1" t="s">
-        <v>1161</v>
-      </c>
-      <c r="G307" s="1" t="s">
-        <v>1162</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A308" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B308" s="1" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C308" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>1164</v>
-      </c>
-      <c r="E308" s="1" t="s">
-        <v>1165</v>
-      </c>
-      <c r="F308" s="1" t="s">
-        <v>1166</v>
-      </c>
-      <c r="G308" s="1" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A309" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B309" s="1" t="s">
-        <v>1168</v>
-      </c>
-      <c r="C309" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D309" s="1" t="s">
-        <v>1169</v>
-      </c>
-      <c r="E309" s="1" t="s">
-        <v>1170</v>
-      </c>
-      <c r="F309" s="1" t="s">
-        <v>1171</v>
-      </c>
-      <c r="G309" s="1" t="s">
-        <v>1172</v>
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A306" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B306" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="F306" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="G306" s="2" t="s">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A307" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B307" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C307" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="F307" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>2079</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A308" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B308" s="9" t="s">
+        <v>2173</v>
+      </c>
+      <c r="C308" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D308" s="9" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E308" s="9" t="s">
+        <v>2106</v>
+      </c>
+      <c r="F308" s="9" t="s">
+        <v>2107</v>
+      </c>
+      <c r="G308" s="9" t="s">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A309" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B309" s="9" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C309" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D309" s="9" t="s">
+        <v>2169</v>
+      </c>
+      <c r="E309" s="9" t="s">
+        <v>2170</v>
+      </c>
+      <c r="F309" s="9" t="s">
+        <v>2171</v>
+      </c>
+      <c r="G309" s="9" t="s">
+        <v>2172</v>
       </c>
     </row>
     <row r="310" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A310" s="1" t="s">
-        <v>1152</v>
+        <v>472</v>
       </c>
       <c r="B310" s="1" t="s">
-        <v>1173</v>
+        <v>1128</v>
       </c>
       <c r="C310" s="1" t="s">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="D310" s="1" t="s">
-        <v>1174</v>
+        <v>1129</v>
       </c>
       <c r="E310" s="1" t="s">
-        <v>1175</v>
+        <v>1130</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>1176</v>
+        <v>1131</v>
       </c>
       <c r="G310" s="1" t="s">
-        <v>1177</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A311" s="1" t="s">
-        <v>1152</v>
+        <v>472</v>
       </c>
       <c r="B311" s="1" t="s">
-        <v>1178</v>
+        <v>1133</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>18</v>
+        <v>405</v>
       </c>
       <c r="D311" s="1" t="s">
-        <v>1179</v>
+        <v>1134</v>
       </c>
       <c r="E311" s="1" t="s">
-        <v>1180</v>
+        <v>1135</v>
       </c>
       <c r="F311" s="1" t="s">
-        <v>1181</v>
+        <v>1136</v>
       </c>
       <c r="G311" s="1" t="s">
-        <v>1182</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A312" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B312" s="1" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D312" s="1" t="s">
-        <v>566</v>
-      </c>
-      <c r="E312" s="1" t="s">
-        <v>1184</v>
-      </c>
-      <c r="F312" s="1" t="s">
-        <v>1185</v>
-      </c>
-      <c r="G312" s="1" t="s">
-        <v>1186</v>
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A312" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B312" s="9" t="s">
+        <v>2127</v>
+      </c>
+      <c r="C312" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="D312" s="9" t="s">
+        <v>1578</v>
+      </c>
+      <c r="E312" s="9" t="s">
+        <v>2128</v>
+      </c>
+      <c r="F312" s="9" t="s">
+        <v>2129</v>
+      </c>
+      <c r="G312" s="9" t="s">
+        <v>2130</v>
       </c>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A313" s="1" t="s">
-        <v>1152</v>
+        <v>472</v>
       </c>
       <c r="B313" s="1" t="s">
-        <v>1187</v>
+        <v>1138</v>
       </c>
       <c r="C313" s="1" t="s">
-        <v>18</v>
+        <v>441</v>
       </c>
       <c r="D313" s="1" t="s">
-        <v>1188</v>
+        <v>1139</v>
       </c>
       <c r="E313" s="1" t="s">
-        <v>1189</v>
+        <v>1140</v>
       </c>
       <c r="F313" s="1" t="s">
-        <v>1190</v>
+        <v>1141</v>
       </c>
       <c r="G313" s="1" t="s">
-        <v>1191</v>
+        <v>1142</v>
       </c>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A314" s="1" t="s">
-        <v>1152</v>
+        <v>472</v>
       </c>
       <c r="B314" s="1" t="s">
-        <v>1192</v>
+        <v>1143</v>
       </c>
       <c r="C314" s="1" t="s">
-        <v>18</v>
+        <v>441</v>
       </c>
       <c r="D314" s="1" t="s">
-        <v>1193</v>
+        <v>1144</v>
       </c>
       <c r="E314" s="1" t="s">
-        <v>1194</v>
+        <v>1145</v>
       </c>
       <c r="F314" s="1" t="s">
-        <v>1195</v>
+        <v>1146</v>
       </c>
       <c r="G314" s="1" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A315" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B315" s="1" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C315" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D315" s="1" t="s">
-        <v>1198</v>
-      </c>
-      <c r="E315" s="1" t="s">
-        <v>1199</v>
-      </c>
-      <c r="F315" s="1" t="s">
-        <v>1200</v>
-      </c>
-      <c r="G315" s="1" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A316" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B316" s="1" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C316" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>1203</v>
-      </c>
-      <c r="E316" s="1" t="s">
-        <v>816</v>
-      </c>
-      <c r="F316" s="1" t="s">
-        <v>1204</v>
-      </c>
-      <c r="G316" s="1" t="s">
-        <v>1205</v>
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A315" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B315" s="9" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C315" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="D315" s="9" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E315" s="9" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F315" s="9" t="s">
+        <v>2111</v>
+      </c>
+      <c r="G315" s="9" t="s">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A316" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="B316" s="9" t="s">
+        <v>2131</v>
+      </c>
+      <c r="C316" s="9" t="s">
+        <v>467</v>
+      </c>
+      <c r="D316" s="9" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E316" s="9" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F316" s="9" t="s">
+        <v>2134</v>
+      </c>
+      <c r="G316" s="9" t="s">
+        <v>2135</v>
       </c>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A317" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B317" s="1" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C317" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D317" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E317" s="1" t="s">
+        <v>1151</v>
+      </c>
+      <c r="F317" s="1" t="s">
         <v>1152</v>
       </c>
-      <c r="B317" s="1" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C317" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>1207</v>
-      </c>
-      <c r="E317" s="1" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F317" s="1" t="s">
-        <v>1209</v>
-      </c>
       <c r="G317" s="1" t="s">
-        <v>1210</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A318" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B318" s="1" t="s">
-        <v>1211</v>
+        <v>1154</v>
       </c>
       <c r="C318" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D318" s="1" t="s">
-        <v>1212</v>
+        <v>1155</v>
       </c>
       <c r="E318" s="1" t="s">
-        <v>1213</v>
+        <v>1156</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>1214</v>
+        <v>1157</v>
       </c>
       <c r="G318" s="1" t="s">
-        <v>1215</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A319" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B319" s="1" t="s">
-        <v>1216</v>
+        <v>1159</v>
       </c>
       <c r="C319" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D319" s="1" t="s">
-        <v>831</v>
+        <v>1160</v>
       </c>
       <c r="E319" s="1" t="s">
-        <v>1217</v>
+        <v>1161</v>
       </c>
       <c r="F319" s="1" t="s">
-        <v>1218</v>
+        <v>1162</v>
       </c>
       <c r="G319" s="1" t="s">
-        <v>1219</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A320" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B320" s="1" t="s">
-        <v>1220</v>
+        <v>1164</v>
       </c>
       <c r="C320" s="1" t="s">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="D320" s="1" t="s">
-        <v>1221</v>
+        <v>1165</v>
       </c>
       <c r="E320" s="1" t="s">
-        <v>1222</v>
+        <v>1166</v>
       </c>
       <c r="F320" s="1" t="s">
-        <v>1223</v>
+        <v>1167</v>
       </c>
       <c r="G320" s="1" t="s">
-        <v>1224</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A321" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B321" s="1" t="s">
-        <v>1225</v>
+        <v>1169</v>
       </c>
       <c r="C321" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D321" s="1" t="s">
-        <v>1226</v>
+        <v>1170</v>
       </c>
       <c r="E321" s="1" t="s">
-        <v>1227</v>
+        <v>1171</v>
       </c>
       <c r="F321" s="1" t="s">
-        <v>1228</v>
+        <v>1172</v>
       </c>
       <c r="G321" s="1" t="s">
-        <v>1229</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A322" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B322" s="1" t="s">
-        <v>1230</v>
+        <v>1174</v>
       </c>
       <c r="C322" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D322" s="1" t="s">
-        <v>1231</v>
+        <v>1175</v>
       </c>
       <c r="E322" s="1" t="s">
-        <v>1232</v>
+        <v>1176</v>
       </c>
       <c r="F322" s="1" t="s">
-        <v>1233</v>
+        <v>1177</v>
       </c>
       <c r="G322" s="1" t="s">
-        <v>1234</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A323" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B323" s="1" t="s">
-        <v>1235</v>
+        <v>1179</v>
       </c>
       <c r="C323" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D323" s="1" t="s">
-        <v>1236</v>
+        <v>566</v>
       </c>
       <c r="E323" s="1" t="s">
-        <v>1237</v>
+        <v>1180</v>
       </c>
       <c r="F323" s="1" t="s">
-        <v>1238</v>
+        <v>1181</v>
       </c>
       <c r="G323" s="1" t="s">
-        <v>1239</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A324" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B324" s="1" t="s">
-        <v>1240</v>
+        <v>1183</v>
       </c>
       <c r="C324" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D324" s="1" t="s">
-        <v>1241</v>
+        <v>1184</v>
       </c>
       <c r="E324" s="1" t="s">
-        <v>1242</v>
+        <v>1185</v>
       </c>
       <c r="F324" s="1" t="s">
-        <v>1243</v>
+        <v>1186</v>
       </c>
       <c r="G324" s="1" t="s">
-        <v>1244</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A325" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B325" s="1" t="s">
-        <v>1245</v>
+        <v>1188</v>
       </c>
       <c r="C325" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D325" s="1" t="s">
-        <v>1246</v>
+        <v>1189</v>
       </c>
       <c r="E325" s="1" t="s">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="F325" s="1" t="s">
-        <v>1247</v>
+        <v>1191</v>
       </c>
       <c r="G325" s="1" t="s">
-        <v>1248</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A326" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B326" s="1" t="s">
-        <v>1249</v>
+        <v>1193</v>
       </c>
       <c r="C326" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D326" s="1" t="s">
-        <v>1250</v>
+        <v>1194</v>
       </c>
       <c r="E326" s="1" t="s">
-        <v>1251</v>
+        <v>1195</v>
       </c>
       <c r="F326" s="1" t="s">
-        <v>1252</v>
+        <v>1196</v>
       </c>
       <c r="G326" s="1" t="s">
-        <v>1253</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A327" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B327" s="1" t="s">
-        <v>1254</v>
+        <v>1198</v>
       </c>
       <c r="C327" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D327" s="1" t="s">
-        <v>1255</v>
+        <v>1199</v>
       </c>
       <c r="E327" s="1" t="s">
-        <v>1256</v>
+        <v>816</v>
       </c>
       <c r="F327" s="1" t="s">
-        <v>1257</v>
+        <v>1200</v>
       </c>
       <c r="G327" s="1" t="s">
-        <v>1258</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A328" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B328" s="1" t="s">
-        <v>1259</v>
+        <v>1202</v>
       </c>
       <c r="C328" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D328" s="1" t="s">
-        <v>1260</v>
+        <v>1203</v>
       </c>
       <c r="E328" s="1" t="s">
-        <v>694</v>
+        <v>1204</v>
       </c>
       <c r="F328" s="1" t="s">
-        <v>1261</v>
+        <v>1205</v>
       </c>
       <c r="G328" s="1" t="s">
-        <v>696</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A329" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B329" s="1" t="s">
-        <v>1262</v>
+        <v>1207</v>
       </c>
       <c r="C329" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="D329" s="1" t="s">
-        <v>1263</v>
+        <v>1208</v>
       </c>
       <c r="E329" s="1" t="s">
-        <v>1264</v>
+        <v>1209</v>
       </c>
       <c r="F329" s="1" t="s">
-        <v>1265</v>
+        <v>1210</v>
       </c>
       <c r="G329" s="1" t="s">
-        <v>1266</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A330" s="1" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B330" s="1" t="s">
-        <v>1267</v>
+        <v>1212</v>
       </c>
       <c r="C330" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D330" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="E330" s="1" t="s">
+        <v>1213</v>
+      </c>
+      <c r="F330" s="1" t="s">
+        <v>1214</v>
+      </c>
+      <c r="G330" s="1" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A331" s="1" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B331" s="1" t="s">
+        <v>1216</v>
+      </c>
+      <c r="C331" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D331" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E331" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F331" s="1" t="s">
+        <v>1219</v>
+      </c>
+      <c r="G331" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="332" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A332" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B332" s="3" t="s">
+        <v>1221</v>
+      </c>
+      <c r="C332" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D330" s="1" t="s">
-        <v>1268</v>
-      </c>
-      <c r="E330" s="1" t="s">
-        <v>1269</v>
-      </c>
-      <c r="F330" s="1" t="s">
-        <v>1270</v>
-      </c>
-      <c r="G330" s="1" t="s">
-        <v>1271</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A331" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B331" s="1" t="s">
-        <v>1272</v>
-      </c>
-      <c r="C331" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D331" s="1" t="s">
-        <v>1273</v>
-      </c>
-      <c r="E331" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="F331" s="1" t="s">
-        <v>1275</v>
-      </c>
-      <c r="G331" s="1" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A332" s="1" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B332" s="1" t="s">
-        <v>1277</v>
-      </c>
-      <c r="C332" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D332" s="1" t="s">
-        <v>1278</v>
-      </c>
-      <c r="E332" s="1" t="s">
-        <v>1279</v>
-      </c>
-      <c r="F332" s="1" t="s">
-        <v>1280</v>
-      </c>
-      <c r="G332" s="1" t="s">
-        <v>1281</v>
+      <c r="D332" s="3" t="s">
+        <v>1222</v>
+      </c>
+      <c r="E332" s="3" t="s">
+        <v>1223</v>
+      </c>
+      <c r="F332" s="3" t="s">
+        <v>1224</v>
+      </c>
+      <c r="G332" s="3" t="s">
+        <v>1225</v>
       </c>
     </row>
     <row r="333" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A333" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B333" s="3" t="s">
-        <v>1282</v>
+        <v>1226</v>
       </c>
       <c r="C333" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D333" s="3" t="s">
-        <v>1283</v>
+        <v>1227</v>
       </c>
       <c r="E333" s="3" t="s">
-        <v>1284</v>
+        <v>1228</v>
       </c>
       <c r="F333" s="3" t="s">
-        <v>1285</v>
+        <v>1229</v>
       </c>
       <c r="G333" s="3" t="s">
-        <v>1286</v>
+        <v>1230</v>
       </c>
     </row>
     <row r="334" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A334" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B334" s="3" t="s">
-        <v>1287</v>
+        <v>1231</v>
       </c>
       <c r="C334" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D334" s="3" t="s">
-        <v>664</v>
+        <v>1232</v>
       </c>
       <c r="E334" s="3" t="s">
-        <v>1288</v>
+        <v>1233</v>
       </c>
       <c r="F334" s="3" t="s">
-        <v>1289</v>
+        <v>1234</v>
       </c>
       <c r="G334" s="3" t="s">
-        <v>1290</v>
+        <v>1235</v>
       </c>
     </row>
     <row r="335" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A335" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B335" s="3" t="s">
-        <v>1291</v>
+        <v>1236</v>
       </c>
       <c r="C335" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D335" s="3" t="s">
-        <v>1292</v>
+        <v>1237</v>
       </c>
       <c r="E335" s="3" t="s">
-        <v>1293</v>
+        <v>1238</v>
       </c>
       <c r="F335" s="3" t="s">
-        <v>1294</v>
+        <v>1239</v>
       </c>
       <c r="G335" s="3" t="s">
-        <v>1295</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="336" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A336" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B336" s="3" t="s">
-        <v>1296</v>
+        <v>1241</v>
       </c>
       <c r="C336" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D336" s="3" t="s">
-        <v>1297</v>
+        <v>1242</v>
       </c>
       <c r="E336" s="3" t="s">
-        <v>1298</v>
+        <v>1190</v>
       </c>
       <c r="F336" s="3" t="s">
-        <v>1299</v>
+        <v>1243</v>
       </c>
       <c r="G336" s="3" t="s">
-        <v>1300</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="337" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A337" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B337" s="3" t="s">
-        <v>1301</v>
+        <v>1245</v>
       </c>
       <c r="C337" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D337" s="3" t="s">
-        <v>1302</v>
+        <v>1246</v>
       </c>
       <c r="E337" s="3" t="s">
-        <v>1303</v>
+        <v>1247</v>
       </c>
       <c r="F337" s="3" t="s">
-        <v>1304</v>
+        <v>1248</v>
       </c>
       <c r="G337" s="3" t="s">
-        <v>1305</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="338" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A338" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B338" s="3" t="s">
-        <v>1306</v>
+        <v>1250</v>
       </c>
       <c r="C338" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D338" s="3" t="s">
-        <v>1307</v>
+        <v>1251</v>
       </c>
       <c r="E338" s="3" t="s">
-        <v>1308</v>
+        <v>1252</v>
       </c>
       <c r="F338" s="3" t="s">
-        <v>1309</v>
+        <v>1253</v>
       </c>
       <c r="G338" s="3" t="s">
-        <v>1310</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="339" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A339" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B339" s="3" t="s">
-        <v>1311</v>
+        <v>1255</v>
       </c>
       <c r="C339" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D339" s="3" t="s">
-        <v>1312</v>
+        <v>1256</v>
       </c>
       <c r="E339" s="3" t="s">
-        <v>1313</v>
+        <v>694</v>
       </c>
       <c r="F339" s="3" t="s">
-        <v>1314</v>
+        <v>1257</v>
       </c>
       <c r="G339" s="3" t="s">
-        <v>1315</v>
+        <v>696</v>
       </c>
     </row>
     <row r="340" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A340" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B340" s="3" t="s">
-        <v>1316</v>
+        <v>1258</v>
       </c>
       <c r="C340" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D340" s="3" t="s">
-        <v>1317</v>
+        <v>1259</v>
       </c>
       <c r="E340" s="3" t="s">
-        <v>1318</v>
+        <v>1260</v>
       </c>
       <c r="F340" s="3" t="s">
-        <v>1319</v>
+        <v>1261</v>
       </c>
       <c r="G340" s="3" t="s">
-        <v>1320</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="341" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A341" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B341" s="3" t="s">
-        <v>1321</v>
+        <v>1263</v>
       </c>
       <c r="C341" s="3" t="s">
         <v>33</v>
       </c>
       <c r="D341" s="3" t="s">
-        <v>1322</v>
+        <v>1264</v>
       </c>
       <c r="E341" s="3" t="s">
-        <v>1323</v>
+        <v>1265</v>
       </c>
       <c r="F341" s="3" t="s">
-        <v>1324</v>
+        <v>1266</v>
       </c>
       <c r="G341" s="3" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A342" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B342" s="4" t="s">
-        <v>2054</v>
-      </c>
-      <c r="C342" s="4" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="342" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A342" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B342" s="3" t="s">
+        <v>1268</v>
+      </c>
+      <c r="C342" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D342" s="4" t="s">
-        <v>2055</v>
-      </c>
-      <c r="E342" s="4" t="s">
-        <v>2056</v>
-      </c>
-      <c r="F342" s="4" t="s">
-        <v>2057</v>
-      </c>
-      <c r="G342" s="4" t="s">
-        <v>2058</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A343" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B343" s="4" t="s">
-        <v>2074</v>
-      </c>
-      <c r="C343" s="4" t="s">
+      <c r="D342" s="3" t="s">
+        <v>1269</v>
+      </c>
+      <c r="E342" s="3" t="s">
+        <v>1270</v>
+      </c>
+      <c r="F342" s="3" t="s">
+        <v>1271</v>
+      </c>
+      <c r="G342" s="3" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="343" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A343" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B343" s="3" t="s">
+        <v>1273</v>
+      </c>
+      <c r="C343" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D343" s="4" t="s">
-        <v>2075</v>
-      </c>
-      <c r="E343" s="4" t="s">
-        <v>2076</v>
-      </c>
-      <c r="F343" s="4" t="s">
-        <v>2077</v>
-      </c>
-      <c r="G343" s="4" t="s">
-        <v>2078</v>
+      <c r="D343" s="3" t="s">
+        <v>1274</v>
+      </c>
+      <c r="E343" s="3" t="s">
+        <v>1275</v>
+      </c>
+      <c r="F343" s="3" t="s">
+        <v>1276</v>
+      </c>
+      <c r="G343" s="3" t="s">
+        <v>1277</v>
       </c>
     </row>
     <row r="344" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A344" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B344" s="3" t="s">
-        <v>1326</v>
+        <v>1278</v>
       </c>
       <c r="C344" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D344" s="3" t="s">
-        <v>1327</v>
+        <v>1279</v>
       </c>
       <c r="E344" s="3" t="s">
-        <v>1328</v>
+        <v>1280</v>
       </c>
       <c r="F344" s="3" t="s">
-        <v>1329</v>
+        <v>1281</v>
       </c>
       <c r="G344" s="3" t="s">
-        <v>1330</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="345" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A345" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B345" s="3" t="s">
-        <v>1331</v>
-      </c>
-      <c r="C345" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D345" s="3" t="s">
-        <v>1332</v>
-      </c>
-      <c r="E345" s="3" t="s">
-        <v>1333</v>
-      </c>
-      <c r="F345" s="3" t="s">
-        <v>1334</v>
-      </c>
-      <c r="G345" s="3" t="s">
-        <v>1335</v>
+      <c r="A345" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B345" s="6" t="s">
+        <v>1283</v>
+      </c>
+      <c r="C345" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="D345" s="6" t="s">
+        <v>664</v>
+      </c>
+      <c r="E345" s="6" t="s">
+        <v>1284</v>
+      </c>
+      <c r="F345" s="6" t="s">
+        <v>1285</v>
+      </c>
+      <c r="G345" s="6" t="s">
+        <v>1286</v>
       </c>
     </row>
     <row r="346" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A346" s="6" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B346" s="6" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C346" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D346" s="6" t="s">
-        <v>1337</v>
-      </c>
-      <c r="E346" s="6" t="s">
-        <v>1338</v>
-      </c>
-      <c r="F346" s="6" t="s">
-        <v>1339</v>
-      </c>
-      <c r="G346" s="6" t="s">
-        <v>1340</v>
+      <c r="A346" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B346" s="3" t="s">
+        <v>1287</v>
+      </c>
+      <c r="C346" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D346" s="3" t="s">
+        <v>1288</v>
+      </c>
+      <c r="E346" s="3" t="s">
+        <v>1289</v>
+      </c>
+      <c r="F346" s="3" t="s">
+        <v>1290</v>
+      </c>
+      <c r="G346" s="3" t="s">
+        <v>1291</v>
       </c>
     </row>
     <row r="347" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A347" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B347" s="3" t="s">
-        <v>1341</v>
+        <v>1292</v>
       </c>
       <c r="C347" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D347" s="3" t="s">
-        <v>1342</v>
+        <v>1293</v>
       </c>
       <c r="E347" s="3" t="s">
-        <v>1343</v>
+        <v>1294</v>
       </c>
       <c r="F347" s="3" t="s">
-        <v>1344</v>
+        <v>1295</v>
       </c>
       <c r="G347" s="3" t="s">
-        <v>1345</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="348" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A348" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B348" s="3" t="s">
-        <v>1346</v>
+        <v>1297</v>
       </c>
       <c r="C348" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D348" s="3" t="s">
-        <v>1347</v>
+        <v>1298</v>
       </c>
       <c r="E348" s="3" t="s">
-        <v>1348</v>
+        <v>1299</v>
       </c>
       <c r="F348" s="3" t="s">
-        <v>1349</v>
+        <v>1300</v>
       </c>
       <c r="G348" s="3" t="s">
-        <v>1350</v>
+        <v>1301</v>
       </c>
     </row>
     <row r="349" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A349" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B349" s="3" t="s">
-        <v>1351</v>
+        <v>1302</v>
       </c>
       <c r="C349" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D349" s="3" t="s">
-        <v>1246</v>
+        <v>1303</v>
       </c>
       <c r="E349" s="3" t="s">
-        <v>1352</v>
+        <v>1304</v>
       </c>
       <c r="F349" s="3" t="s">
-        <v>1353</v>
+        <v>1305</v>
       </c>
       <c r="G349" s="3" t="s">
-        <v>1354</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="350" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A350" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B350" s="3" t="s">
-        <v>1356</v>
+        <v>1307</v>
       </c>
       <c r="C350" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D350" s="3" t="s">
-        <v>1833</v>
+        <v>1308</v>
       </c>
       <c r="E350" s="3" t="s">
-        <v>1834</v>
+        <v>1309</v>
       </c>
       <c r="F350" s="3" t="s">
-        <v>1835</v>
+        <v>1310</v>
       </c>
       <c r="G350" s="3" t="s">
-        <v>1836</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="351" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A351" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B351" s="3" t="s">
-        <v>1357</v>
+        <v>1312</v>
       </c>
       <c r="C351" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D351" s="3" t="s">
-        <v>1358</v>
+        <v>1313</v>
       </c>
       <c r="E351" s="3" t="s">
-        <v>1359</v>
+        <v>1314</v>
       </c>
       <c r="F351" s="3" t="s">
-        <v>1360</v>
+        <v>1315</v>
       </c>
       <c r="G351" s="3" t="s">
-        <v>1361</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="352" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A352" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B352" s="3" t="s">
-        <v>1362</v>
+        <v>1317</v>
       </c>
       <c r="C352" s="3" t="s">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="D352" s="3" t="s">
-        <v>1363</v>
+        <v>1318</v>
       </c>
       <c r="E352" s="3" t="s">
-        <v>1364</v>
+        <v>1319</v>
       </c>
       <c r="F352" s="3" t="s">
-        <v>1365</v>
+        <v>1320</v>
       </c>
       <c r="G352" s="3" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A353" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B353" s="3" t="s">
-        <v>1367</v>
-      </c>
-      <c r="C353" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D353" s="3" t="s">
-        <v>1368</v>
-      </c>
-      <c r="E353" s="3" t="s">
-        <v>1369</v>
-      </c>
-      <c r="F353" s="3" t="s">
-        <v>1370</v>
-      </c>
-      <c r="G353" s="3" t="s">
-        <v>1371</v>
-      </c>
-    </row>
-    <row r="354" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A354" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B354" s="3" t="s">
-        <v>1372</v>
-      </c>
-      <c r="C354" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D354" s="3" t="s">
-        <v>1373</v>
-      </c>
-      <c r="E354" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="F354" s="3" t="s">
-        <v>1374</v>
-      </c>
-      <c r="G354" s="3" t="s">
-        <v>1375</v>
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A353" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B353" s="4" t="s">
+        <v>2050</v>
+      </c>
+      <c r="C353" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D353" s="4" t="s">
+        <v>2051</v>
+      </c>
+      <c r="E353" s="4" t="s">
+        <v>2052</v>
+      </c>
+      <c r="F353" s="4" t="s">
+        <v>2053</v>
+      </c>
+      <c r="G353" s="4" t="s">
+        <v>2054</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A354" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B354" s="4" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C354" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D354" s="4" t="s">
+        <v>2071</v>
+      </c>
+      <c r="E354" s="4" t="s">
+        <v>2072</v>
+      </c>
+      <c r="F354" s="4" t="s">
+        <v>2073</v>
+      </c>
+      <c r="G354" s="4" t="s">
+        <v>2074</v>
       </c>
     </row>
     <row r="355" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A355" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B355" s="3" t="s">
-        <v>1376</v>
+        <v>1322</v>
       </c>
       <c r="C355" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D355" s="3" t="s">
-        <v>1377</v>
+        <v>1323</v>
       </c>
       <c r="E355" s="3" t="s">
-        <v>263</v>
+        <v>1324</v>
       </c>
       <c r="F355" s="3" t="s">
-        <v>1378</v>
+        <v>1325</v>
       </c>
       <c r="G355" s="3" t="s">
-        <v>1379</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="356" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A356" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B356" s="3" t="s">
-        <v>1380</v>
+        <v>1327</v>
       </c>
       <c r="C356" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D356" s="3" t="s">
-        <v>1381</v>
+        <v>1328</v>
       </c>
       <c r="E356" s="3" t="s">
-        <v>1382</v>
+        <v>1329</v>
       </c>
       <c r="F356" s="3" t="s">
-        <v>1383</v>
+        <v>1330</v>
       </c>
       <c r="G356" s="3" t="s">
-        <v>1384</v>
+        <v>1331</v>
       </c>
     </row>
     <row r="357" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A357" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B357" s="3" t="s">
-        <v>1385</v>
+        <v>1332</v>
       </c>
       <c r="C357" s="3" t="s">
         <v>66</v>
       </c>
       <c r="D357" s="3" t="s">
-        <v>1386</v>
+        <v>1333</v>
       </c>
       <c r="E357" s="3" t="s">
-        <v>1387</v>
+        <v>1334</v>
       </c>
       <c r="F357" s="3" t="s">
-        <v>1388</v>
+        <v>1335</v>
       </c>
       <c r="G357" s="3" t="s">
-        <v>1389</v>
-      </c>
-    </row>
-    <row r="358" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A358" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B358" s="4" t="s">
-        <v>1749</v>
-      </c>
-      <c r="C358" s="4" t="s">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A358" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B358" s="3" t="s">
+        <v>1337</v>
+      </c>
+      <c r="C358" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D358" s="4" t="s">
-        <v>1750</v>
-      </c>
-      <c r="E358" s="4" t="s">
-        <v>1751</v>
-      </c>
-      <c r="F358" s="4" t="s">
-        <v>1752</v>
-      </c>
-      <c r="G358" s="4" t="s">
-        <v>1753</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A359" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B359" s="4" t="s">
-        <v>2032</v>
-      </c>
-      <c r="C359" s="4" t="s">
+      <c r="D358" s="3" t="s">
+        <v>1338</v>
+      </c>
+      <c r="E358" s="3" t="s">
+        <v>1339</v>
+      </c>
+      <c r="F358" s="3" t="s">
+        <v>1340</v>
+      </c>
+      <c r="G358" s="3" t="s">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A359" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B359" s="3" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C359" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D359" s="4" t="s">
-        <v>500</v>
-      </c>
-      <c r="E359" s="4" t="s">
-        <v>2033</v>
-      </c>
-      <c r="F359" s="4" t="s">
-        <v>2034</v>
-      </c>
-      <c r="G359" s="4" t="s">
-        <v>2035</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A360" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B360" s="4" t="s">
-        <v>2064</v>
-      </c>
-      <c r="C360" s="4" t="s">
+      <c r="D359" s="3" t="s">
+        <v>1343</v>
+      </c>
+      <c r="E359" s="3" t="s">
+        <v>1344</v>
+      </c>
+      <c r="F359" s="3" t="s">
+        <v>1345</v>
+      </c>
+      <c r="G359" s="3" t="s">
+        <v>1346</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A360" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B360" s="3" t="s">
+        <v>1347</v>
+      </c>
+      <c r="C360" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D360" s="4" t="s">
-        <v>2065</v>
-      </c>
-      <c r="E360" s="4" t="s">
-        <v>2066</v>
-      </c>
-      <c r="F360" s="4" t="s">
-        <v>2067</v>
-      </c>
-      <c r="G360" s="4" t="s">
-        <v>2068</v>
+      <c r="D360" s="3" t="s">
+        <v>1242</v>
+      </c>
+      <c r="E360" s="3" t="s">
+        <v>1348</v>
+      </c>
+      <c r="F360" s="3" t="s">
+        <v>1349</v>
+      </c>
+      <c r="G360" s="3" t="s">
+        <v>1350</v>
       </c>
     </row>
     <row r="361" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A361" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B361" s="3" t="s">
-        <v>1390</v>
+        <v>1352</v>
       </c>
       <c r="C361" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D361" s="3" t="s">
-        <v>763</v>
+        <v>1829</v>
       </c>
       <c r="E361" s="3" t="s">
-        <v>1391</v>
+        <v>1830</v>
       </c>
       <c r="F361" s="3" t="s">
-        <v>1392</v>
+        <v>1831</v>
       </c>
       <c r="G361" s="3" t="s">
-        <v>1393</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="362" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A362" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B362" s="3" t="s">
-        <v>1394</v>
+        <v>1353</v>
       </c>
       <c r="C362" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D362" s="3" t="s">
-        <v>1395</v>
+        <v>1354</v>
       </c>
       <c r="E362" s="3" t="s">
-        <v>1396</v>
+        <v>1355</v>
       </c>
       <c r="F362" s="3" t="s">
-        <v>1397</v>
+        <v>1356</v>
       </c>
       <c r="G362" s="3" t="s">
-        <v>1398</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="363" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A363" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B363" s="3" t="s">
-        <v>1399</v>
+        <v>1358</v>
       </c>
       <c r="C363" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D363" s="3" t="s">
-        <v>831</v>
+        <v>1359</v>
       </c>
       <c r="E363" s="3" t="s">
-        <v>500</v>
+        <v>1360</v>
       </c>
       <c r="F363" s="3" t="s">
-        <v>1400</v>
+        <v>1361</v>
       </c>
       <c r="G363" s="3" t="s">
-        <v>1401</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="364" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A364" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B364" s="3" t="s">
-        <v>1402</v>
+        <v>1363</v>
       </c>
       <c r="C364" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D364" s="3" t="s">
-        <v>1403</v>
+        <v>1364</v>
       </c>
       <c r="E364" s="3" t="s">
-        <v>1404</v>
+        <v>1365</v>
       </c>
       <c r="F364" s="3" t="s">
-        <v>1405</v>
+        <v>1366</v>
       </c>
       <c r="G364" s="3" t="s">
-        <v>1406</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="365" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A365" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B365" s="3" t="s">
-        <v>1407</v>
+        <v>1368</v>
       </c>
       <c r="C365" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D365" s="3" t="s">
-        <v>1408</v>
+        <v>1369</v>
       </c>
       <c r="E365" s="3" t="s">
-        <v>1409</v>
+        <v>62</v>
       </c>
       <c r="F365" s="3" t="s">
-        <v>1410</v>
+        <v>1370</v>
       </c>
       <c r="G365" s="3" t="s">
-        <v>1411</v>
+        <v>1371</v>
       </c>
     </row>
     <row r="366" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A366" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B366" s="3" t="s">
-        <v>1412</v>
+        <v>1372</v>
       </c>
       <c r="C366" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D366" s="3" t="s">
-        <v>1413</v>
+        <v>1373</v>
       </c>
       <c r="E366" s="3" t="s">
-        <v>1414</v>
+        <v>263</v>
       </c>
       <c r="F366" s="3" t="s">
-        <v>1415</v>
+        <v>1374</v>
       </c>
       <c r="G366" s="3" t="s">
-        <v>1416</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="367" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A367" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B367" s="3" t="s">
-        <v>1417</v>
+        <v>1376</v>
       </c>
       <c r="C367" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D367" s="3" t="s">
-        <v>1418</v>
+        <v>1377</v>
       </c>
       <c r="E367" s="3" t="s">
-        <v>1419</v>
+        <v>1378</v>
       </c>
       <c r="F367" s="3" t="s">
-        <v>1420</v>
+        <v>1379</v>
       </c>
       <c r="G367" s="3" t="s">
-        <v>1421</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="368" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A368" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B368" s="3" t="s">
-        <v>1422</v>
+        <v>1381</v>
       </c>
       <c r="C368" s="3" t="s">
-        <v>129</v>
+        <v>66</v>
       </c>
       <c r="D368" s="3" t="s">
-        <v>1423</v>
+        <v>1382</v>
       </c>
       <c r="E368" s="3" t="s">
-        <v>1424</v>
+        <v>1383</v>
       </c>
       <c r="F368" s="3" t="s">
-        <v>1425</v>
+        <v>1384</v>
       </c>
       <c r="G368" s="3" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A369" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B369" s="3" t="s">
-        <v>1427</v>
-      </c>
-      <c r="C369" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D369" s="3" t="s">
-        <v>1428</v>
-      </c>
-      <c r="E369" s="3" t="s">
-        <v>1429</v>
-      </c>
-      <c r="F369" s="3" t="s">
-        <v>1430</v>
-      </c>
-      <c r="G369" s="3" t="s">
-        <v>1431</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A370" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B370" s="3" t="s">
-        <v>1432</v>
-      </c>
-      <c r="C370" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D370" s="3" t="s">
-        <v>1260</v>
-      </c>
-      <c r="E370" s="3" t="s">
-        <v>1433</v>
-      </c>
-      <c r="F370" s="3" t="s">
-        <v>1434</v>
-      </c>
-      <c r="G370" s="3" t="s">
-        <v>1435</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A371" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B371" s="3" t="s">
-        <v>1436</v>
-      </c>
-      <c r="C371" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D371" s="3" t="s">
-        <v>1437</v>
-      </c>
-      <c r="E371" s="3" t="s">
-        <v>1438</v>
-      </c>
-      <c r="F371" s="3" t="s">
-        <v>1439</v>
-      </c>
-      <c r="G371" s="3" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A372" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B372" s="3" t="s">
-        <v>1441</v>
-      </c>
-      <c r="C372" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="D372" s="3" t="s">
-        <v>1442</v>
-      </c>
-      <c r="E372" s="3" t="s">
-        <v>1443</v>
-      </c>
-      <c r="F372" s="3" t="s">
-        <v>1444</v>
-      </c>
-      <c r="G372" s="3" t="s">
-        <v>1445</v>
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A369" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B369" s="4" t="s">
+        <v>1745</v>
+      </c>
+      <c r="C369" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D369" s="4" t="s">
+        <v>1746</v>
+      </c>
+      <c r="E369" s="4" t="s">
+        <v>1747</v>
+      </c>
+      <c r="F369" s="4" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G369" s="4" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A370" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B370" s="4" t="s">
+        <v>2028</v>
+      </c>
+      <c r="C370" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D370" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="E370" s="4" t="s">
+        <v>2029</v>
+      </c>
+      <c r="F370" s="4" t="s">
+        <v>2030</v>
+      </c>
+      <c r="G370" s="4" t="s">
+        <v>2031</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A371" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B371" s="4" t="s">
+        <v>2060</v>
+      </c>
+      <c r="C371" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D371" s="4" t="s">
+        <v>2061</v>
+      </c>
+      <c r="E371" s="4" t="s">
+        <v>2062</v>
+      </c>
+      <c r="F371" s="4" t="s">
+        <v>2063</v>
+      </c>
+      <c r="G371" s="4" t="s">
+        <v>2064</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A372" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B372" s="4" t="s">
+        <v>2122</v>
+      </c>
+      <c r="C372" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="D372" s="4" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E372" s="4" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F372" s="4" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G372" s="4" t="s">
+        <v>2126</v>
       </c>
     </row>
     <row r="373" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A373" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B373" s="3" t="s">
-        <v>1446</v>
+        <v>1386</v>
       </c>
       <c r="C373" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D373" s="3" t="s">
-        <v>1447</v>
+        <v>763</v>
       </c>
       <c r="E373" s="3" t="s">
-        <v>1448</v>
+        <v>1387</v>
       </c>
       <c r="F373" s="3" t="s">
-        <v>1449</v>
+        <v>1388</v>
       </c>
       <c r="G373" s="3" t="s">
-        <v>1450</v>
+        <v>1389</v>
       </c>
     </row>
     <row r="374" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A374" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B374" s="3" t="s">
-        <v>1451</v>
+        <v>1390</v>
       </c>
       <c r="C374" s="3" t="s">
         <v>129</v>
       </c>
       <c r="D374" s="3" t="s">
-        <v>1452</v>
+        <v>1391</v>
       </c>
       <c r="E374" s="3" t="s">
-        <v>1453</v>
+        <v>1392</v>
       </c>
       <c r="F374" s="3" t="s">
-        <v>1454</v>
+        <v>1393</v>
       </c>
       <c r="G374" s="3" t="s">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A375" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B375" s="4" t="s">
-        <v>1754</v>
-      </c>
-      <c r="C375" s="4" t="s">
+        <v>1394</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A375" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B375" s="3" t="s">
+        <v>1395</v>
+      </c>
+      <c r="C375" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D375" s="4" t="s">
-        <v>1758</v>
-      </c>
-      <c r="E375" s="4" t="s">
-        <v>1755</v>
-      </c>
-      <c r="F375" s="4" t="s">
-        <v>1756</v>
-      </c>
-      <c r="G375" s="4" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="376" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A376" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B376" s="4" t="s">
-        <v>1798</v>
-      </c>
-      <c r="C376" s="4" t="s">
+      <c r="D375" s="3" t="s">
+        <v>831</v>
+      </c>
+      <c r="E375" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="F375" s="3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="G375" s="3" t="s">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="376" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A376" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B376" s="3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="C376" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D376" s="4" t="s">
-        <v>1799</v>
-      </c>
-      <c r="E376" s="4" t="s">
-        <v>1800</v>
-      </c>
-      <c r="F376" s="4" t="s">
-        <v>1801</v>
-      </c>
-      <c r="G376" s="4" t="s">
-        <v>1802</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A377" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B377" s="4" t="s">
-        <v>1872</v>
-      </c>
-      <c r="C377" s="4" t="s">
+      <c r="D376" s="3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="E376" s="3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="F376" s="3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="G376" s="3" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="377" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A377" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B377" s="3" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C377" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D377" s="4" t="s">
-        <v>1873</v>
-      </c>
-      <c r="E377" s="4" t="s">
-        <v>1874</v>
-      </c>
-      <c r="F377" s="4" t="s">
-        <v>1875</v>
-      </c>
-      <c r="G377" s="4" t="s">
-        <v>1876</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A378" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B378" s="4" t="s">
-        <v>1962</v>
-      </c>
-      <c r="C378" s="4" t="s">
+      <c r="D377" s="3" t="s">
+        <v>1404</v>
+      </c>
+      <c r="E377" s="3" t="s">
+        <v>1405</v>
+      </c>
+      <c r="F377" s="3" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G377" s="3" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A378" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B378" s="3" t="s">
+        <v>1408</v>
+      </c>
+      <c r="C378" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D378" s="4" t="s">
-        <v>1963</v>
-      </c>
-      <c r="E378" s="4" t="s">
-        <v>1964</v>
-      </c>
-      <c r="F378" s="4" t="s">
-        <v>1965</v>
-      </c>
-      <c r="G378" s="4" t="s">
-        <v>1966</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A379" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B379" s="4" t="s">
-        <v>2036</v>
-      </c>
-      <c r="C379" s="4" t="s">
+      <c r="D378" s="3" t="s">
+        <v>1409</v>
+      </c>
+      <c r="E378" s="3" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F378" s="3" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G378" s="3" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A379" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B379" s="3" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C379" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D379" s="4" t="s">
-        <v>2037</v>
-      </c>
-      <c r="E379" s="4" t="s">
-        <v>2038</v>
-      </c>
-      <c r="F379" s="4" t="s">
-        <v>2039</v>
-      </c>
-      <c r="G379" s="4" t="s">
-        <v>2040</v>
+      <c r="D379" s="3" t="s">
+        <v>1414</v>
+      </c>
+      <c r="E379" s="3" t="s">
+        <v>1415</v>
+      </c>
+      <c r="F379" s="3" t="s">
+        <v>1416</v>
+      </c>
+      <c r="G379" s="3" t="s">
+        <v>1417</v>
       </c>
     </row>
     <row r="380" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A380" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B380" s="3" t="s">
-        <v>1456</v>
+        <v>1418</v>
       </c>
       <c r="C380" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="D380" s="3" t="s">
-        <v>1457</v>
+        <v>1419</v>
       </c>
       <c r="E380" s="3" t="s">
-        <v>1458</v>
+        <v>1420</v>
       </c>
       <c r="F380" s="3" t="s">
-        <v>1459</v>
+        <v>1421</v>
       </c>
       <c r="G380" s="3" t="s">
-        <v>1460</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="381" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A381" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B381" s="3" t="s">
-        <v>1463</v>
+        <v>1423</v>
       </c>
       <c r="C381" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="D381" s="3" t="s">
-        <v>1464</v>
+        <v>1424</v>
       </c>
       <c r="E381" s="3" t="s">
-        <v>1465</v>
+        <v>1425</v>
       </c>
       <c r="F381" s="3" t="s">
-        <v>1466</v>
+        <v>1426</v>
       </c>
       <c r="G381" s="3" t="s">
-        <v>1467</v>
+        <v>1427</v>
       </c>
     </row>
     <row r="382" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A382" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B382" s="3" t="s">
-        <v>1468</v>
+        <v>1428</v>
       </c>
       <c r="C382" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="D382" s="3" t="s">
-        <v>1469</v>
+        <v>1256</v>
       </c>
       <c r="E382" s="3" t="s">
-        <v>1470</v>
+        <v>1429</v>
       </c>
       <c r="F382" s="3" t="s">
-        <v>1471</v>
+        <v>1430</v>
       </c>
       <c r="G382" s="3" t="s">
-        <v>1472</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="383" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A383" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B383" s="3" t="s">
-        <v>1473</v>
+        <v>1432</v>
       </c>
       <c r="C383" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="D383" s="3" t="s">
-        <v>1474</v>
+        <v>1433</v>
       </c>
       <c r="E383" s="3" t="s">
-        <v>1475</v>
+        <v>1434</v>
       </c>
       <c r="F383" s="3" t="s">
-        <v>1476</v>
+        <v>1435</v>
       </c>
       <c r="G383" s="3" t="s">
-        <v>1477</v>
+        <v>1436</v>
       </c>
     </row>
     <row r="384" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A384" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B384" s="3" t="s">
-        <v>1478</v>
+        <v>1437</v>
       </c>
       <c r="C384" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="D384" s="3" t="s">
-        <v>1479</v>
+        <v>1438</v>
       </c>
       <c r="E384" s="3" t="s">
-        <v>1480</v>
+        <v>1439</v>
       </c>
       <c r="F384" s="3" t="s">
-        <v>1481</v>
+        <v>1440</v>
       </c>
       <c r="G384" s="3" t="s">
-        <v>1482</v>
+        <v>1441</v>
       </c>
     </row>
     <row r="385" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A385" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B385" s="3" t="s">
-        <v>1483</v>
+        <v>1442</v>
       </c>
       <c r="C385" s="3" t="s">
-        <v>195</v>
+        <v>129</v>
       </c>
       <c r="D385" s="3" t="s">
-        <v>911</v>
+        <v>1443</v>
       </c>
       <c r="E385" s="3" t="s">
-        <v>1484</v>
+        <v>1444</v>
       </c>
       <c r="F385" s="3" t="s">
-        <v>1485</v>
+        <v>1445</v>
       </c>
       <c r="G385" s="3" t="s">
-        <v>1486</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="386" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A386" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B386" s="3" t="s">
-        <v>1487</v>
+        <v>1447</v>
       </c>
       <c r="C386" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D386" s="3" t="s">
+        <v>1448</v>
+      </c>
+      <c r="E386" s="3" t="s">
+        <v>1449</v>
+      </c>
+      <c r="F386" s="3" t="s">
+        <v>1450</v>
+      </c>
+      <c r="G386" s="3" t="s">
+        <v>1451</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A387" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B387" s="4" t="s">
+        <v>1750</v>
+      </c>
+      <c r="C387" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D387" s="4" t="s">
+        <v>1754</v>
+      </c>
+      <c r="E387" s="4" t="s">
+        <v>1751</v>
+      </c>
+      <c r="F387" s="4" t="s">
+        <v>1752</v>
+      </c>
+      <c r="G387" s="4" t="s">
+        <v>1753</v>
+      </c>
+    </row>
+    <row r="388" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A388" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B388" s="4" t="s">
+        <v>1794</v>
+      </c>
+      <c r="C388" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D388" s="4" t="s">
+        <v>1795</v>
+      </c>
+      <c r="E388" s="4" t="s">
+        <v>1796</v>
+      </c>
+      <c r="F388" s="4" t="s">
+        <v>1797</v>
+      </c>
+      <c r="G388" s="4" t="s">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A389" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B389" s="4" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C389" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D389" s="4" t="s">
+        <v>1869</v>
+      </c>
+      <c r="E389" s="4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="F389" s="4" t="s">
+        <v>1871</v>
+      </c>
+      <c r="G389" s="4" t="s">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A390" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B390" s="4" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C390" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D390" s="4" t="s">
+        <v>1959</v>
+      </c>
+      <c r="E390" s="4" t="s">
+        <v>1960</v>
+      </c>
+      <c r="F390" s="4" t="s">
+        <v>1961</v>
+      </c>
+      <c r="G390" s="4" t="s">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="391" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A391" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B391" s="4" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C391" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D391" s="4" t="s">
+        <v>2033</v>
+      </c>
+      <c r="E391" s="4" t="s">
+        <v>2034</v>
+      </c>
+      <c r="F391" s="4" t="s">
+        <v>2035</v>
+      </c>
+      <c r="G391" s="4" t="s">
+        <v>2036</v>
+      </c>
+    </row>
+    <row r="392" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A392" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B392" s="3" t="s">
+        <v>1452</v>
+      </c>
+      <c r="C392" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D386" s="3" t="s">
-        <v>1488</v>
-      </c>
-      <c r="E386" s="3" t="s">
-        <v>1489</v>
-      </c>
-      <c r="F386" s="3" t="s">
-        <v>1490</v>
-      </c>
-      <c r="G386" s="3" t="s">
-        <v>1491</v>
-      </c>
-    </row>
-    <row r="387" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A387" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B387" s="3" t="s">
-        <v>1492</v>
-      </c>
-      <c r="C387" s="3" t="s">
+      <c r="D392" s="3" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E392" s="3" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F392" s="3" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G392" s="3" t="s">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="393" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A393" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B393" s="3" t="s">
+        <v>1459</v>
+      </c>
+      <c r="C393" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D387" s="3" t="s">
-        <v>831</v>
-      </c>
-      <c r="E387" s="3" t="s">
-        <v>1493</v>
-      </c>
-      <c r="F387" s="3" t="s">
-        <v>1494</v>
-      </c>
-      <c r="G387" s="3" t="s">
-        <v>1495</v>
-      </c>
-    </row>
-    <row r="388" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A388" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B388" s="4" t="s">
-        <v>1625</v>
-      </c>
-      <c r="C388" s="4" t="s">
+      <c r="D393" s="3" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E393" s="3" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F393" s="3" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G393" s="3" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="394" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A394" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B394" s="3" t="s">
+        <v>1464</v>
+      </c>
+      <c r="C394" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D388" s="4" t="s">
-        <v>1626</v>
-      </c>
-      <c r="E388" s="4" t="s">
-        <v>1627</v>
-      </c>
-      <c r="F388" s="4" t="s">
-        <v>1628</v>
-      </c>
-      <c r="G388" s="4" t="s">
-        <v>1629</v>
-      </c>
-    </row>
-    <row r="389" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A389" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B389" s="4" t="s">
-        <v>1669</v>
-      </c>
-      <c r="C389" s="4" t="s">
+      <c r="D394" s="3" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E394" s="3" t="s">
+        <v>1466</v>
+      </c>
+      <c r="F394" s="3" t="s">
+        <v>1467</v>
+      </c>
+      <c r="G394" s="3" t="s">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="395" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A395" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B395" s="3" t="s">
+        <v>1469</v>
+      </c>
+      <c r="C395" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D389" s="4" t="s">
-        <v>1670</v>
-      </c>
-      <c r="E389" s="4" t="s">
-        <v>1671</v>
-      </c>
-      <c r="F389" s="4" t="s">
-        <v>1672</v>
-      </c>
-      <c r="G389" s="4" t="s">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="390" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A390" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B390" s="4" t="s">
-        <v>1696</v>
-      </c>
-      <c r="C390" s="4" t="s">
+      <c r="D395" s="3" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E395" s="3" t="s">
+        <v>1471</v>
+      </c>
+      <c r="F395" s="3" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G395" s="3" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="396" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A396" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B396" s="3" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C396" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D390" s="4" t="s">
-        <v>1697</v>
-      </c>
-      <c r="E390" s="4" t="s">
-        <v>1698</v>
-      </c>
-      <c r="F390" s="4" t="s">
-        <v>1699</v>
-      </c>
-      <c r="G390" s="4" t="s">
-        <v>1700</v>
-      </c>
-    </row>
-    <row r="391" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A391" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B391" s="4" t="s">
-        <v>1744</v>
-      </c>
-      <c r="C391" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D391" s="4" t="s">
-        <v>1745</v>
-      </c>
-      <c r="E391" s="4" t="s">
-        <v>1746</v>
-      </c>
-      <c r="F391" s="4" t="s">
-        <v>1747</v>
-      </c>
-      <c r="G391" s="4" t="s">
-        <v>1748</v>
-      </c>
-    </row>
-    <row r="392" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A392" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B392" s="4" t="s">
-        <v>2012</v>
-      </c>
-      <c r="C392" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D392" s="4" t="s">
-        <v>2013</v>
-      </c>
-      <c r="E392" s="4" t="s">
-        <v>2014</v>
-      </c>
-      <c r="F392" s="4" t="s">
-        <v>2015</v>
-      </c>
-      <c r="G392" s="4" t="s">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="393" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A393" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B393" s="4" t="s">
-        <v>2017</v>
-      </c>
-      <c r="C393" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D393" s="4" t="s">
-        <v>2018</v>
-      </c>
-      <c r="E393" s="4" t="s">
-        <v>2019</v>
-      </c>
-      <c r="F393" s="4" t="s">
-        <v>2020</v>
-      </c>
-      <c r="G393" s="4" t="s">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A394" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B394" s="4" t="s">
-        <v>2022</v>
-      </c>
-      <c r="C394" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D394" s="4" t="s">
-        <v>2023</v>
-      </c>
-      <c r="E394" s="4" t="s">
-        <v>2024</v>
-      </c>
-      <c r="F394" s="4" t="s">
-        <v>2025</v>
-      </c>
-      <c r="G394" s="4" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="395" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A395" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B395" s="4" t="s">
-        <v>2031</v>
-      </c>
-      <c r="C395" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D395" s="4" t="s">
-        <v>2027</v>
-      </c>
-      <c r="E395" s="4" t="s">
-        <v>2028</v>
-      </c>
-      <c r="F395" s="4" t="s">
-        <v>2029</v>
-      </c>
-      <c r="G395" s="4" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A396" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B396" s="4" t="s">
-        <v>2041</v>
-      </c>
-      <c r="C396" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="D396" s="4" t="s">
-        <v>2042</v>
-      </c>
-      <c r="E396" s="4" t="s">
-        <v>2043</v>
-      </c>
-      <c r="F396" s="4" t="s">
-        <v>2044</v>
-      </c>
-      <c r="G396" s="4" t="s">
-        <v>2045</v>
+      <c r="D396" s="3" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E396" s="3" t="s">
+        <v>1476</v>
+      </c>
+      <c r="F396" s="3" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G396" s="3" t="s">
+        <v>1478</v>
       </c>
     </row>
     <row r="397" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A397" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B397" s="3" t="s">
-        <v>1496</v>
+        <v>1479</v>
       </c>
       <c r="C397" s="3" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D397" s="3" t="s">
-        <v>1497</v>
+        <v>911</v>
       </c>
       <c r="E397" s="3" t="s">
-        <v>1498</v>
+        <v>1480</v>
       </c>
       <c r="F397" s="3" t="s">
-        <v>1499</v>
+        <v>1481</v>
       </c>
       <c r="G397" s="3" t="s">
-        <v>1500</v>
+        <v>1482</v>
       </c>
     </row>
     <row r="398" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A398" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B398" s="3" t="s">
-        <v>1501</v>
+        <v>1483</v>
       </c>
       <c r="C398" s="3" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D398" s="3" t="s">
-        <v>1502</v>
+        <v>1484</v>
       </c>
       <c r="E398" s="3" t="s">
-        <v>1503</v>
+        <v>1485</v>
       </c>
       <c r="F398" s="3" t="s">
-        <v>1504</v>
+        <v>1486</v>
       </c>
       <c r="G398" s="3" t="s">
-        <v>1505</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="399" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A399" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B399" s="3" t="s">
-        <v>1506</v>
+        <v>1488</v>
       </c>
       <c r="C399" s="3" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D399" s="3" t="s">
-        <v>1058</v>
+        <v>831</v>
       </c>
       <c r="E399" s="3" t="s">
-        <v>1507</v>
+        <v>1489</v>
       </c>
       <c r="F399" s="3" t="s">
-        <v>1508</v>
+        <v>1490</v>
       </c>
       <c r="G399" s="3" t="s">
-        <v>1509</v>
-      </c>
-    </row>
-    <row r="400" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A400" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B400" s="3" t="s">
-        <v>1510</v>
-      </c>
-      <c r="C400" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D400" s="3" t="s">
-        <v>1511</v>
-      </c>
-      <c r="E400" s="3" t="s">
-        <v>1512</v>
-      </c>
-      <c r="F400" s="3" t="s">
-        <v>1513</v>
-      </c>
-      <c r="G400" s="3" t="s">
-        <v>1514</v>
-      </c>
-    </row>
-    <row r="401" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A401" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B401" s="3" t="s">
-        <v>1515</v>
-      </c>
-      <c r="C401" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D401" s="3" t="s">
-        <v>1516</v>
-      </c>
-      <c r="E401" s="3" t="s">
-        <v>1517</v>
-      </c>
-      <c r="F401" s="3" t="s">
-        <v>1518</v>
-      </c>
-      <c r="G401" s="3" t="s">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="402" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A402" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B402" s="3" t="s">
-        <v>1520</v>
-      </c>
-      <c r="C402" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D402" s="3" t="s">
-        <v>956</v>
-      </c>
-      <c r="E402" s="3" t="s">
-        <v>1521</v>
-      </c>
-      <c r="F402" s="3" t="s">
-        <v>1522</v>
-      </c>
-      <c r="G402" s="3" t="s">
-        <v>1523</v>
-      </c>
-    </row>
-    <row r="403" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A403" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B403" s="3" t="s">
-        <v>1524</v>
-      </c>
-      <c r="C403" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D403" s="3" t="s">
-        <v>1525</v>
-      </c>
-      <c r="E403" s="3" t="s">
-        <v>1526</v>
-      </c>
-      <c r="F403" s="3" t="s">
-        <v>1527</v>
-      </c>
-      <c r="G403" s="3" t="s">
-        <v>1528</v>
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="400" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A400" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B400" s="4" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C400" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D400" s="4" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E400" s="4" t="s">
+        <v>1623</v>
+      </c>
+      <c r="F400" s="4" t="s">
+        <v>1624</v>
+      </c>
+      <c r="G400" s="4" t="s">
+        <v>1625</v>
+      </c>
+    </row>
+    <row r="401" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A401" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B401" s="4" t="s">
+        <v>1665</v>
+      </c>
+      <c r="C401" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D401" s="4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E401" s="4" t="s">
+        <v>1667</v>
+      </c>
+      <c r="F401" s="4" t="s">
+        <v>1668</v>
+      </c>
+      <c r="G401" s="4" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="402" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A402" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B402" s="4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="C402" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D402" s="4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E402" s="4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F402" s="4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G402" s="4" t="s">
+        <v>1696</v>
+      </c>
+    </row>
+    <row r="403" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A403" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B403" s="4" t="s">
+        <v>1740</v>
+      </c>
+      <c r="C403" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D403" s="4" t="s">
+        <v>1741</v>
+      </c>
+      <c r="E403" s="4" t="s">
+        <v>1742</v>
+      </c>
+      <c r="F403" s="4" t="s">
+        <v>1743</v>
+      </c>
+      <c r="G403" s="4" t="s">
+        <v>1744</v>
       </c>
     </row>
     <row r="404" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A404" s="4" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1793</v>
+        <v>2008</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>236</v>
+        <v>195</v>
       </c>
       <c r="D404" s="4" t="s">
-        <v>1794</v>
+        <v>2009</v>
       </c>
       <c r="E404" s="4" t="s">
-        <v>1795</v>
+        <v>2010</v>
       </c>
       <c r="F404" s="4" t="s">
-        <v>1796</v>
+        <v>2011</v>
       </c>
       <c r="G404" s="4" t="s">
-        <v>1797</v>
-      </c>
-    </row>
-    <row r="405" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A405" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B405" s="3" t="s">
-        <v>1461</v>
-      </c>
-      <c r="C405" s="3" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D405" s="3" t="s">
-        <v>1462</v>
-      </c>
-      <c r="E405" s="3" t="s">
-        <v>2048</v>
-      </c>
-      <c r="F405" s="3" t="s">
-        <v>2047</v>
-      </c>
-      <c r="G405" s="3" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="406" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A406" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B406" s="3" t="s">
-        <v>1355</v>
-      </c>
-      <c r="C406" s="3" t="s">
-        <v>1828</v>
-      </c>
-      <c r="D406" s="3" t="s">
-        <v>1829</v>
-      </c>
-      <c r="E406" s="3" t="s">
-        <v>1830</v>
-      </c>
-      <c r="F406" s="3" t="s">
-        <v>1831</v>
-      </c>
-      <c r="G406" s="3" t="s">
-        <v>1832</v>
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="405" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A405" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B405" s="4" t="s">
+        <v>2013</v>
+      </c>
+      <c r="C405" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D405" s="4" t="s">
+        <v>2014</v>
+      </c>
+      <c r="E405" s="4" t="s">
+        <v>2015</v>
+      </c>
+      <c r="F405" s="4" t="s">
+        <v>2016</v>
+      </c>
+      <c r="G405" s="4" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="406" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A406" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B406" s="4" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C406" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D406" s="4" t="s">
+        <v>2019</v>
+      </c>
+      <c r="E406" s="4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="F406" s="4" t="s">
+        <v>2021</v>
+      </c>
+      <c r="G406" s="4" t="s">
+        <v>2022</v>
       </c>
     </row>
     <row r="407" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A407" s="4" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1686</v>
+        <v>2027</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="D407" s="4" t="s">
-        <v>1687</v>
+        <v>2023</v>
       </c>
       <c r="E407" s="4" t="s">
-        <v>1688</v>
+        <v>2024</v>
       </c>
       <c r="F407" s="4" t="s">
-        <v>1689</v>
+        <v>2025</v>
       </c>
       <c r="G407" s="4" t="s">
-        <v>1690</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="408" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A408" s="4" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1823</v>
+        <v>2037</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>297</v>
+        <v>195</v>
       </c>
       <c r="D408" s="4" t="s">
-        <v>1824</v>
+        <v>2038</v>
       </c>
       <c r="E408" s="4" t="s">
-        <v>1825</v>
+        <v>2039</v>
       </c>
       <c r="F408" s="4" t="s">
-        <v>1826</v>
+        <v>2040</v>
       </c>
       <c r="G408" s="4" t="s">
-        <v>1827</v>
-      </c>
-    </row>
-    <row r="409" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A409" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B409" s="3" t="s">
-        <v>1529</v>
-      </c>
-      <c r="C409" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D409" s="3" t="s">
-        <v>1530</v>
-      </c>
-      <c r="E409" s="3" t="s">
-        <v>1531</v>
-      </c>
-      <c r="F409" s="3" t="s">
-        <v>1532</v>
-      </c>
-      <c r="G409" s="3" t="s">
-        <v>1533</v>
-      </c>
-    </row>
-    <row r="410" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A410" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B410" s="3" t="s">
-        <v>1534</v>
-      </c>
-      <c r="C410" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="D410" s="3" t="s">
-        <v>1535</v>
-      </c>
-      <c r="E410" s="3" t="s">
-        <v>1536</v>
-      </c>
-      <c r="F410" s="3" t="s">
-        <v>1537</v>
-      </c>
-      <c r="G410" s="3" t="s">
-        <v>1538</v>
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="409" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A409" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B409" s="4" t="s">
+        <v>2136</v>
+      </c>
+      <c r="C409" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D409" s="4" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E409" s="4" t="s">
+        <v>2142</v>
+      </c>
+      <c r="F409" s="4" t="s">
+        <v>2143</v>
+      </c>
+      <c r="G409" s="4" t="s">
+        <v>2144</v>
+      </c>
+    </row>
+    <row r="410" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A410" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B410" s="4" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C410" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="D410" s="4" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E410" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="F410" s="4" t="s">
+        <v>2157</v>
+      </c>
+      <c r="G410" s="4" t="s">
+        <v>2158</v>
       </c>
     </row>
     <row r="411" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A411" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B411" s="3" t="s">
-        <v>1539</v>
+        <v>1492</v>
       </c>
       <c r="C411" s="3" t="s">
-        <v>343</v>
+        <v>236</v>
       </c>
       <c r="D411" s="3" t="s">
-        <v>1358</v>
+        <v>1493</v>
       </c>
       <c r="E411" s="3" t="s">
-        <v>1540</v>
+        <v>1494</v>
       </c>
       <c r="F411" s="3" t="s">
-        <v>1541</v>
+        <v>1495</v>
       </c>
       <c r="G411" s="3" t="s">
-        <v>1542</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="412" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A412" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B412" s="3" t="s">
-        <v>1543</v>
+        <v>1497</v>
       </c>
       <c r="C412" s="3" t="s">
-        <v>343</v>
+        <v>236</v>
       </c>
       <c r="D412" s="3" t="s">
-        <v>1544</v>
+        <v>1498</v>
       </c>
       <c r="E412" s="3" t="s">
-        <v>1545</v>
+        <v>1499</v>
       </c>
       <c r="F412" s="3" t="s">
-        <v>1546</v>
+        <v>1500</v>
       </c>
       <c r="G412" s="3" t="s">
-        <v>1547</v>
-      </c>
-    </row>
-    <row r="413" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A413" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B413" s="4" t="s">
-        <v>1852</v>
-      </c>
-      <c r="C413" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D413" s="4" t="s">
-        <v>1853</v>
-      </c>
-      <c r="E413" s="4" t="s">
-        <v>1854</v>
-      </c>
-      <c r="F413" s="4" t="s">
-        <v>1855</v>
-      </c>
-      <c r="G413" s="4" t="s">
-        <v>1856</v>
+        <v>1501</v>
+      </c>
+    </row>
+    <row r="413" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A413" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B413" s="3" t="s">
+        <v>1502</v>
+      </c>
+      <c r="C413" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D413" s="3" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E413" s="3" t="s">
+        <v>1503</v>
+      </c>
+      <c r="F413" s="3" t="s">
+        <v>1504</v>
+      </c>
+      <c r="G413" s="3" t="s">
+        <v>1505</v>
       </c>
     </row>
     <row r="414" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A414" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B414" s="3" t="s">
-        <v>1548</v>
+        <v>1506</v>
       </c>
       <c r="C414" s="3" t="s">
-        <v>364</v>
+        <v>236</v>
       </c>
       <c r="D414" s="3" t="s">
-        <v>1549</v>
+        <v>1507</v>
       </c>
       <c r="E414" s="3" t="s">
-        <v>1550</v>
+        <v>1508</v>
       </c>
       <c r="F414" s="3" t="s">
-        <v>1551</v>
+        <v>1509</v>
       </c>
       <c r="G414" s="3" t="s">
-        <v>1552</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="415" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A415" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B415" s="3" t="s">
-        <v>1553</v>
+        <v>1511</v>
       </c>
       <c r="C415" s="3" t="s">
-        <v>364</v>
+        <v>236</v>
       </c>
       <c r="D415" s="3" t="s">
-        <v>1554</v>
+        <v>1512</v>
       </c>
       <c r="E415" s="3" t="s">
-        <v>1555</v>
+        <v>1513</v>
       </c>
       <c r="F415" s="3" t="s">
-        <v>1556</v>
+        <v>1514</v>
       </c>
       <c r="G415" s="3" t="s">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="416" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A416" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B416" s="4" t="s">
-        <v>1769</v>
-      </c>
-      <c r="C416" s="4" t="s">
-        <v>364</v>
-      </c>
-      <c r="D416" s="4" t="s">
-        <v>1770</v>
-      </c>
-      <c r="E416" s="4" t="s">
-        <v>1771</v>
-      </c>
-      <c r="F416" s="4" t="s">
-        <v>1772</v>
-      </c>
-      <c r="G416" s="4" t="s">
-        <v>1773</v>
+        <v>1515</v>
+      </c>
+    </row>
+    <row r="416" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A416" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B416" s="3" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C416" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="D416" s="3" t="s">
+        <v>956</v>
+      </c>
+      <c r="E416" s="3" t="s">
+        <v>1517</v>
+      </c>
+      <c r="F416" s="3" t="s">
+        <v>1518</v>
+      </c>
+      <c r="G416" s="3" t="s">
+        <v>1519</v>
       </c>
     </row>
     <row r="417" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A417" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B417" s="3" t="s">
-        <v>1558</v>
+        <v>1520</v>
       </c>
       <c r="C417" s="3" t="s">
-        <v>405</v>
+        <v>236</v>
       </c>
       <c r="D417" s="3" t="s">
-        <v>1559</v>
+        <v>1521</v>
       </c>
       <c r="E417" s="3" t="s">
-        <v>1560</v>
+        <v>1522</v>
       </c>
       <c r="F417" s="3" t="s">
-        <v>1561</v>
+        <v>1523</v>
       </c>
       <c r="G417" s="3" t="s">
-        <v>1562</v>
-      </c>
-    </row>
-    <row r="418" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A418" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B418" s="3" t="s">
-        <v>1563</v>
-      </c>
-      <c r="C418" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D418" s="3" t="s">
-        <v>1188</v>
-      </c>
-      <c r="E418" s="3" t="s">
-        <v>1564</v>
-      </c>
-      <c r="F418" s="3" t="s">
-        <v>1565</v>
-      </c>
-      <c r="G418" s="3" t="s">
-        <v>1566</v>
-      </c>
-    </row>
-    <row r="419" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A419" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B419" s="3" t="s">
-        <v>1567</v>
-      </c>
-      <c r="C419" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D419" s="3" t="s">
-        <v>1188</v>
-      </c>
-      <c r="E419" s="3" t="s">
-        <v>1568</v>
-      </c>
-      <c r="F419" s="3" t="s">
-        <v>1569</v>
-      </c>
-      <c r="G419" s="3" t="s">
-        <v>1570</v>
+        <v>1524</v>
+      </c>
+    </row>
+    <row r="418" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A418" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B418" s="4" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C418" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D418" s="4" t="s">
+        <v>1790</v>
+      </c>
+      <c r="E418" s="4" t="s">
+        <v>1791</v>
+      </c>
+      <c r="F418" s="4" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G418" s="4" t="s">
+        <v>1793</v>
+      </c>
+    </row>
+    <row r="419" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A419" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B419" s="4" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C419" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D419" s="4" t="s">
+        <v>2165</v>
+      </c>
+      <c r="E419" s="4" t="s">
+        <v>2166</v>
+      </c>
+      <c r="F419" s="4" t="s">
+        <v>2167</v>
+      </c>
+      <c r="G419" s="4" t="s">
+        <v>2168</v>
       </c>
     </row>
     <row r="420" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A420" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B420" s="3" t="s">
-        <v>1571</v>
+        <v>1457</v>
       </c>
       <c r="C420" s="3" t="s">
-        <v>405</v>
+        <v>1824</v>
       </c>
       <c r="D420" s="3" t="s">
-        <v>1358</v>
+        <v>1458</v>
       </c>
       <c r="E420" s="3" t="s">
-        <v>1572</v>
+        <v>2044</v>
       </c>
       <c r="F420" s="3" t="s">
-        <v>1573</v>
+        <v>2043</v>
       </c>
       <c r="G420" s="3" t="s">
-        <v>1574</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="421" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A421" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B421" s="3" t="s">
-        <v>1575</v>
+        <v>1351</v>
       </c>
       <c r="C421" s="3" t="s">
-        <v>405</v>
+        <v>1824</v>
       </c>
       <c r="D421" s="3" t="s">
-        <v>1576</v>
+        <v>1825</v>
       </c>
       <c r="E421" s="3" t="s">
-        <v>1577</v>
+        <v>1826</v>
       </c>
       <c r="F421" s="3" t="s">
-        <v>1578</v>
+        <v>1827</v>
       </c>
       <c r="G421" s="3" t="s">
-        <v>1579</v>
-      </c>
-    </row>
-    <row r="422" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A422" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B422" s="3" t="s">
-        <v>1580</v>
-      </c>
-      <c r="C422" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D422" s="3" t="s">
-        <v>1581</v>
-      </c>
-      <c r="E422" s="3" t="s">
-        <v>1582</v>
-      </c>
-      <c r="F422" s="3" t="s">
-        <v>1583</v>
-      </c>
-      <c r="G422" s="3" t="s">
-        <v>1584</v>
-      </c>
-    </row>
-    <row r="423" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A423" s="3" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B423" s="3" t="s">
-        <v>1585</v>
-      </c>
-      <c r="C423" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D423" s="3" t="s">
-        <v>1586</v>
-      </c>
-      <c r="E423" s="3" t="s">
-        <v>1587</v>
-      </c>
-      <c r="F423" s="3" t="s">
-        <v>1588</v>
-      </c>
-      <c r="G423" s="3" t="s">
-        <v>1589</v>
-      </c>
-    </row>
-    <row r="424" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A424" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B424" s="4" t="s">
-        <v>1857</v>
-      </c>
-      <c r="C424" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="D424" s="4" t="s">
-        <v>1858</v>
-      </c>
-      <c r="E424" s="4" t="s">
-        <v>1859</v>
-      </c>
-      <c r="F424" s="4" t="s">
-        <v>1860</v>
-      </c>
-      <c r="G424" s="4" t="s">
-        <v>1861</v>
+        <v>1828</v>
+      </c>
+    </row>
+    <row r="422" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A422" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B422" s="4" t="s">
+        <v>1682</v>
+      </c>
+      <c r="C422" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D422" s="4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E422" s="4" t="s">
+        <v>1684</v>
+      </c>
+      <c r="F422" s="4" t="s">
+        <v>1685</v>
+      </c>
+      <c r="G422" s="4" t="s">
+        <v>1686</v>
+      </c>
+    </row>
+    <row r="423" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A423" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B423" s="4" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C423" s="4" t="s">
+        <v>297</v>
+      </c>
+      <c r="D423" s="4" t="s">
+        <v>1820</v>
+      </c>
+      <c r="E423" s="4" t="s">
+        <v>1821</v>
+      </c>
+      <c r="F423" s="4" t="s">
+        <v>1822</v>
+      </c>
+      <c r="G423" s="4" t="s">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="424" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A424" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B424" s="3" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C424" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D424" s="3" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E424" s="3" t="s">
+        <v>1527</v>
+      </c>
+      <c r="F424" s="3" t="s">
+        <v>1528</v>
+      </c>
+      <c r="G424" s="3" t="s">
+        <v>1529</v>
       </c>
     </row>
     <row r="425" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A425" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B425" s="3" t="s">
-        <v>1590</v>
+        <v>1530</v>
       </c>
       <c r="C425" s="3" t="s">
-        <v>441</v>
+        <v>343</v>
       </c>
       <c r="D425" s="3" t="s">
-        <v>1591</v>
+        <v>1531</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>376</v>
+        <v>1532</v>
       </c>
       <c r="F425" s="3" t="s">
-        <v>1592</v>
+        <v>1533</v>
       </c>
       <c r="G425" s="3" t="s">
-        <v>1593</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="426" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A426" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B426" s="3" t="s">
-        <v>1594</v>
+        <v>1535</v>
       </c>
       <c r="C426" s="3" t="s">
-        <v>441</v>
+        <v>343</v>
       </c>
       <c r="D426" s="3" t="s">
-        <v>1188</v>
+        <v>1354</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>1595</v>
+        <v>1536</v>
       </c>
       <c r="F426" s="3" t="s">
-        <v>1596</v>
+        <v>1537</v>
       </c>
       <c r="G426" s="3" t="s">
-        <v>1597</v>
+        <v>1538</v>
       </c>
     </row>
     <row r="427" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A427" s="3" t="s">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="B427" s="3" t="s">
+        <v>1539</v>
+      </c>
+      <c r="C427" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="D427" s="3" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E427" s="3" t="s">
+        <v>1541</v>
+      </c>
+      <c r="F427" s="3" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G427" s="3" t="s">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="428" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A428" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B428" s="4" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C428" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D428" s="4" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E428" s="4" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F428" s="4" t="s">
+        <v>1851</v>
+      </c>
+      <c r="G428" s="4" t="s">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="429" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A429" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B429" s="3" t="s">
+        <v>1544</v>
+      </c>
+      <c r="C429" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D429" s="3" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E429" s="3" t="s">
+        <v>1546</v>
+      </c>
+      <c r="F429" s="3" t="s">
+        <v>1547</v>
+      </c>
+      <c r="G429" s="3" t="s">
+        <v>1548</v>
+      </c>
+    </row>
+    <row r="430" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A430" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B430" s="3" t="s">
+        <v>1549</v>
+      </c>
+      <c r="C430" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="D430" s="3" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E430" s="3" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F430" s="3" t="s">
+        <v>1552</v>
+      </c>
+      <c r="G430" s="3" t="s">
+        <v>1553</v>
+      </c>
+    </row>
+    <row r="431" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A431" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B431" s="4" t="s">
+        <v>1765</v>
+      </c>
+      <c r="C431" s="4" t="s">
+        <v>364</v>
+      </c>
+      <c r="D431" s="4" t="s">
+        <v>1766</v>
+      </c>
+      <c r="E431" s="4" t="s">
+        <v>1767</v>
+      </c>
+      <c r="F431" s="4" t="s">
+        <v>1768</v>
+      </c>
+      <c r="G431" s="4" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="432" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A432" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B432" s="3" t="s">
+        <v>1554</v>
+      </c>
+      <c r="C432" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D432" s="3" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E432" s="3" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F432" s="3" t="s">
+        <v>1557</v>
+      </c>
+      <c r="G432" s="3" t="s">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="433" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A433" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B433" s="3" t="s">
+        <v>1559</v>
+      </c>
+      <c r="C433" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D433" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E433" s="3" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F433" s="3" t="s">
+        <v>1561</v>
+      </c>
+      <c r="G433" s="3" t="s">
+        <v>1562</v>
+      </c>
+    </row>
+    <row r="434" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A434" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B434" s="3" t="s">
+        <v>1563</v>
+      </c>
+      <c r="C434" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D434" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E434" s="3" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F434" s="3" t="s">
+        <v>1565</v>
+      </c>
+      <c r="G434" s="3" t="s">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="435" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A435" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B435" s="3" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C435" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D435" s="3" t="s">
+        <v>1354</v>
+      </c>
+      <c r="E435" s="3" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F435" s="3" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G435" s="3" t="s">
+        <v>1570</v>
+      </c>
+    </row>
+    <row r="436" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A436" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B436" s="6" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C436" s="6" t="s">
+        <v>405</v>
+      </c>
+      <c r="D436" s="6" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E436" s="6" t="s">
+        <v>1573</v>
+      </c>
+      <c r="F436" s="6" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G436" s="6" t="s">
+        <v>1575</v>
+      </c>
+    </row>
+    <row r="437" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A437" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B437" s="3" t="s">
+        <v>1576</v>
+      </c>
+      <c r="C437" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D437" s="3" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E437" s="3" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F437" s="3" t="s">
+        <v>1579</v>
+      </c>
+      <c r="G437" s="3" t="s">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="438" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A438" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B438" s="3" t="s">
+        <v>1581</v>
+      </c>
+      <c r="C438" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D438" s="3" t="s">
+        <v>1582</v>
+      </c>
+      <c r="E438" s="3" t="s">
+        <v>1583</v>
+      </c>
+      <c r="F438" s="3" t="s">
+        <v>1584</v>
+      </c>
+      <c r="G438" s="3" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="439" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A439" s="8" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B439" s="8" t="s">
+        <v>1853</v>
+      </c>
+      <c r="C439" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="D439" s="8" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E439" s="8" t="s">
+        <v>1855</v>
+      </c>
+      <c r="F439" s="8" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G439" s="8" t="s">
+        <v>1857</v>
+      </c>
+    </row>
+    <row r="440" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A440" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B440" s="3" t="s">
+        <v>1586</v>
+      </c>
+      <c r="C440" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D440" s="3" t="s">
+        <v>1587</v>
+      </c>
+      <c r="E440" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F440" s="3" t="s">
+        <v>1588</v>
+      </c>
+      <c r="G440" s="3" t="s">
+        <v>1589</v>
+      </c>
+    </row>
+    <row r="441" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A441" s="3" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B441" s="3" t="s">
+        <v>1590</v>
+      </c>
+      <c r="C441" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="D441" s="3" t="s">
+        <v>1184</v>
+      </c>
+      <c r="E441" s="3" t="s">
+        <v>1591</v>
+      </c>
+      <c r="F441" s="3" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G441" s="3" t="s">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="442" spans="1:7" ht="16.8" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A442" s="6" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B442" s="6" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C442" s="6" t="s">
+        <v>441</v>
+      </c>
+      <c r="D442" s="6" t="s">
+        <v>1595</v>
+      </c>
+      <c r="E442" s="6" t="s">
+        <v>1596</v>
+      </c>
+      <c r="F442" s="6" t="s">
+        <v>1597</v>
+      </c>
+      <c r="G442" s="6" t="s">
         <v>1598</v>
       </c>
-      <c r="C427" s="3" t="s">
+    </row>
+    <row r="443" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A443" s="4" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B443" s="4" t="s">
+        <v>1770</v>
+      </c>
+      <c r="C443" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="D427" s="3" t="s">
-        <v>1599</v>
-      </c>
-      <c r="E427" s="3" t="s">
-        <v>1600</v>
-      </c>
-      <c r="F427" s="3" t="s">
-        <v>1601</v>
-      </c>
-      <c r="G427" s="3" t="s">
-        <v>1602</v>
-      </c>
-    </row>
-    <row r="428" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A428" s="4" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B428" s="4" t="s">
+      <c r="D443" s="4" t="s">
+        <v>1771</v>
+      </c>
+      <c r="E443" s="4" t="s">
+        <v>1772</v>
+      </c>
+      <c r="F443" s="4" t="s">
+        <v>1773</v>
+      </c>
+      <c r="G443" s="4" t="s">
         <v>1774</v>
-      </c>
-      <c r="C428" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="D428" s="4" t="s">
-        <v>1775</v>
-      </c>
-      <c r="E428" s="4" t="s">
-        <v>1776</v>
-      </c>
-      <c r="F428" s="4" t="s">
-        <v>1777</v>
-      </c>
-      <c r="G428" s="4" t="s">
-        <v>1778</v>
-      </c>
-    </row>
-    <row r="429" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A429" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B429" s="10" t="s">
-        <v>2181</v>
-      </c>
-      <c r="C429" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D429" s="10" t="s">
-        <v>2109</v>
-      </c>
-      <c r="E429" s="10" t="s">
-        <v>2110</v>
-      </c>
-      <c r="F429" s="10" t="s">
-        <v>2111</v>
-      </c>
-      <c r="G429" s="10" t="s">
-        <v>2112</v>
-      </c>
-    </row>
-    <row r="430" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A430" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B430" s="10" t="s">
-        <v>1122</v>
-      </c>
-      <c r="C430" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="D430" s="10" t="s">
-        <v>2113</v>
-      </c>
-      <c r="E430" s="10" t="s">
-        <v>2114</v>
-      </c>
-      <c r="F430" s="10" t="s">
-        <v>2115</v>
-      </c>
-      <c r="G430" s="10" t="s">
-        <v>2116</v>
-      </c>
-    </row>
-    <row r="431" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A431" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B431" s="10" t="s">
-        <v>2117</v>
-      </c>
-      <c r="C431" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D431" s="10" t="s">
-        <v>2118</v>
-      </c>
-      <c r="E431" s="10" t="s">
-        <v>2119</v>
-      </c>
-      <c r="F431" s="10" t="s">
-        <v>2120</v>
-      </c>
-      <c r="G431" s="10" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="432" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A432" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B432" s="10" t="s">
-        <v>2122</v>
-      </c>
-      <c r="C432" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D432" s="10" t="s">
-        <v>2123</v>
-      </c>
-      <c r="E432" s="10" t="s">
-        <v>2124</v>
-      </c>
-      <c r="F432" s="10" t="s">
-        <v>2125</v>
-      </c>
-      <c r="G432" s="10" t="s">
-        <v>2126</v>
-      </c>
-    </row>
-    <row r="433" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A433" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B433" s="10" t="s">
-        <v>2127</v>
-      </c>
-      <c r="C433" s="10" t="s">
-        <v>343</v>
-      </c>
-      <c r="D433" s="10" t="s">
-        <v>1010</v>
-      </c>
-      <c r="E433" s="10" t="s">
-        <v>2128</v>
-      </c>
-      <c r="F433" s="10" t="s">
-        <v>2129</v>
-      </c>
-      <c r="G433" s="10" t="s">
-        <v>2130</v>
-      </c>
-    </row>
-    <row r="434" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A434" s="10" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B434" s="10" t="s">
-        <v>2127</v>
-      </c>
-      <c r="C434" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D434" s="10" t="s">
-        <v>2131</v>
-      </c>
-      <c r="E434" s="10" t="s">
-        <v>2132</v>
-      </c>
-      <c r="F434" s="10" t="s">
-        <v>2133</v>
-      </c>
-      <c r="G434" s="10" t="s">
-        <v>2134</v>
-      </c>
-    </row>
-    <row r="435" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A435" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B435" s="10" t="s">
-        <v>2135</v>
-      </c>
-      <c r="C435" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="D435" s="10" t="s">
-        <v>1582</v>
-      </c>
-      <c r="E435" s="10" t="s">
-        <v>2136</v>
-      </c>
-      <c r="F435" s="10" t="s">
-        <v>2137</v>
-      </c>
-      <c r="G435" s="10" t="s">
-        <v>2138</v>
-      </c>
-    </row>
-    <row r="436" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A436" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B436" s="10" t="s">
-        <v>2139</v>
-      </c>
-      <c r="C436" s="10" t="s">
-        <v>467</v>
-      </c>
-      <c r="D436" s="10" t="s">
-        <v>2140</v>
-      </c>
-      <c r="E436" s="10" t="s">
-        <v>2141</v>
-      </c>
-      <c r="F436" s="10" t="s">
-        <v>2142</v>
-      </c>
-      <c r="G436" s="10" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="437" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A437" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="B437" s="9" t="s">
-        <v>2144</v>
-      </c>
-      <c r="C437" s="9" t="s">
-        <v>195</v>
-      </c>
-      <c r="D437" s="9" t="s">
-        <v>2145</v>
-      </c>
-      <c r="E437" s="9" t="s">
-        <v>2146</v>
-      </c>
-      <c r="F437" s="9" t="s">
-        <v>2147</v>
-      </c>
-      <c r="G437" s="9" t="s">
-        <v>2148</v>
-      </c>
-    </row>
-    <row r="438" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A438" s="10" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B438" s="10" t="s">
-        <v>2144</v>
-      </c>
-      <c r="C438" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D438" s="10" t="s">
-        <v>2149</v>
-      </c>
-      <c r="E438" s="10" t="s">
-        <v>2150</v>
-      </c>
-      <c r="F438" s="10" t="s">
-        <v>2151</v>
-      </c>
-      <c r="G438" s="10" t="s">
-        <v>2152</v>
-      </c>
-    </row>
-    <row r="439" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A439" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B439" s="10" t="s">
-        <v>2153</v>
-      </c>
-      <c r="C439" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="D439" s="10" t="s">
-        <v>2154</v>
-      </c>
-      <c r="E439" s="10" t="s">
-        <v>2155</v>
-      </c>
-      <c r="F439" s="10" t="s">
-        <v>2156</v>
-      </c>
-      <c r="G439" s="10" t="s">
-        <v>2157</v>
-      </c>
-    </row>
-    <row r="440" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A440" s="9" t="s">
-        <v>472</v>
-      </c>
-      <c r="B440" s="9" t="s">
-        <v>2158</v>
-      </c>
-      <c r="C440" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D440" s="9" t="s">
-        <v>2159</v>
-      </c>
-      <c r="E440" s="9" t="s">
-        <v>2160</v>
-      </c>
-      <c r="F440" s="9" t="s">
-        <v>2161</v>
-      </c>
-      <c r="G440" s="9" t="s">
-        <v>2162</v>
-      </c>
-    </row>
-    <row r="441" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A441" s="10" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B441" s="10" t="s">
-        <v>2158</v>
-      </c>
-      <c r="C441" s="10" t="s">
-        <v>195</v>
-      </c>
-      <c r="D441" s="10" t="s">
-        <v>2163</v>
-      </c>
-      <c r="E441" s="10" t="s">
-        <v>2164</v>
-      </c>
-      <c r="F441" s="10" t="s">
-        <v>2165</v>
-      </c>
-      <c r="G441" s="10" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="442" spans="1:7" ht="42" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A442" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B442" s="10" t="s">
-        <v>2167</v>
-      </c>
-      <c r="C442" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="D442" s="10" t="s">
-        <v>2168</v>
-      </c>
-      <c r="E442" s="10" t="s">
-        <v>2169</v>
-      </c>
-      <c r="F442" s="10" t="s">
-        <v>2170</v>
-      </c>
-      <c r="G442" s="10" t="s">
-        <v>2171</v>
-      </c>
-    </row>
-    <row r="443" spans="1:7" ht="28.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A443" s="9" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B443" s="9" t="s">
-        <v>2172</v>
-      </c>
-      <c r="C443" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="D443" s="9" t="s">
-        <v>2173</v>
-      </c>
-      <c r="E443" s="9" t="s">
-        <v>2174</v>
-      </c>
-      <c r="F443" s="9" t="s">
-        <v>2175</v>
-      </c>
-      <c r="G443" s="9" t="s">
-        <v>2176</v>
-      </c>
-    </row>
-    <row r="444" spans="1:7" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A444" s="10" t="s">
-        <v>472</v>
-      </c>
-      <c r="B444" s="10" t="s">
-        <v>2172</v>
-      </c>
-      <c r="C444" s="10" t="s">
-        <v>364</v>
-      </c>
-      <c r="D444" s="10" t="s">
-        <v>2177</v>
-      </c>
-      <c r="E444" s="10" t="s">
-        <v>2178</v>
-      </c>
-      <c r="F444" s="10" t="s">
-        <v>2179</v>
-      </c>
-      <c r="G444" s="10" t="s">
-        <v>2180</v>
       </c>
     </row>
   </sheetData>
